--- a/Hardware/Matériel.xlsx
+++ b/Hardware/Matériel.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
   <si>
     <t>Nom</t>
   </si>
@@ -36,18 +36,30 @@
   </si>
   <si>
     <t xml:space="preserve">Module SBC-RFID-RC522</t>
+  </si>
+  <si>
+    <t>Alimentation</t>
+  </si>
+  <si>
+    <t>TR10S05</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <sz val="11.000000"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11.000000"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="2">
@@ -70,8 +82,9 @@
   <cellStyleXfs count="1">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
+    <xf fontId="1" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -604,7 +617,18 @@
         <v>5</v>
       </c>
     </row>
+    <row r="6" ht="14.25">
+      <c r="B6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink r:id="rId1" ref="C6" tooltip=""/>
+  </hyperlinks>
   <printOptions headings="0" gridLines="0"/>
   <pageMargins left="0.70078740157480324" right="0.70078740157480324" top="0.75196850393700787" bottom="0.75196850393700787" header="0.29999999999999999" footer="0.29999999999999999"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>

--- a/Hardware/Matériel.xlsx
+++ b/Hardware/Matériel.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
   <si>
     <t>Nom</t>
   </si>
@@ -26,10 +26,25 @@
     <t>Ref</t>
   </si>
   <si>
+    <t>Fournisseur</t>
+  </si>
+  <si>
+    <t>prix</t>
+  </si>
+  <si>
+    <t>nombre</t>
+  </si>
+  <si>
+    <t>tot</t>
+  </si>
+  <si>
     <t>ESP32</t>
   </si>
   <si>
-    <t>ESP32-WROOM-32E</t>
+    <t>XIAO-ESP32-S3</t>
+  </si>
+  <si>
+    <t>Mouser</t>
   </si>
   <si>
     <t xml:space="preserve">Module RFID</t>
@@ -38,17 +53,53 @@
     <t xml:space="preserve">Module SBC-RFID-RC522</t>
   </si>
   <si>
+    <t>Inconnu</t>
+  </si>
+  <si>
     <t>Alimentation</t>
   </si>
   <si>
     <t>TR10S05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LED RGB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">APA102 - 150505M173300</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Level Shifter</t>
+  </si>
+  <si>
+    <t>SN74LVC1G17DBVR</t>
+  </si>
+  <si>
+    <t>Bornier</t>
+  </si>
+  <si>
+    <t>TB0011-350-04GR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">transceiver UART &lt;-&gt; RS485</t>
+  </si>
+  <si>
+    <t>MAX3485CSA+T</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Switch horizontal</t>
+  </si>
+  <si>
+    <t>SLW-874744-6A-RA-N-D</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="2">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="_-* #,##0.00\ [$CHF-100C]_-;\-* #,##0.00\ [$CHF-100C]_-;_-* &quot;-&quot;??\ [$CHF-100C]_-;_-@_-"/>
+  </numFmts>
+  <fonts count="4">
     <font>
       <sz val="11.000000"/>
       <color theme="1"/>
@@ -61,13 +112,25 @@
       <color theme="10"/>
       <name val="Calibri"/>
     </font>
+    <font>
+      <sz val="11.000000"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11.000000"/>
+      <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="none"/>
     </fill>
   </fills>
   <borders count="1">
@@ -79,15 +142,40 @@
       <diagonal style="none"/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="2" borderId="0" numFmtId="44" applyNumberFormat="1" applyFont="0" applyFill="0" applyBorder="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="11">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf fontId="1" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf fontId="2" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="164" xfId="1" applyNumberFormat="1"/>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="164" xfId="1" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf fontId="3" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="164" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Currency" xfId="1" builtinId="4"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -589,45 +677,218 @@
   </sheetPr>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col customWidth="1" min="2" max="2" width="13.7109375"/>
+    <col bestFit="1" customWidth="1" min="2" max="2" width="24.390625"/>
     <col customWidth="1" min="3" max="3" width="25.57421875"/>
+    <col bestFit="1" customWidth="1" min="4" max="4" width="10.86328125"/>
+    <col bestFit="1" min="5" max="6" width="9.58203125"/>
+    <col bestFit="1" min="7" max="7" width="10.6328125"/>
+    <col bestFit="1" min="9" max="9" width="11.69140625"/>
+    <col bestFit="1" min="10" max="10" width="10.6328125"/>
   </cols>
   <sheetData>
     <row r="3" ht="14.25">
-      <c r="B3" t="s">
+      <c r="B3" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="1" t="s">
         <v>1</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="4" ht="14.25">
       <c r="B4" t="s">
-        <v>2</v>
-      </c>
-      <c r="C4" t="s">
-        <v>3</v>
+        <v>6</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="E4" s="7">
+        <v>5.9400000000000004</v>
+      </c>
+      <c r="F4" s="3">
+        <v>1</v>
+      </c>
+      <c r="G4" s="8">
+        <f>F4*E4</f>
+        <v>5.9400000000000004</v>
       </c>
     </row>
     <row r="5" ht="14.25">
       <c r="B5" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C5" t="s">
-        <v>5</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="D5" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E5" s="7">
+        <v>8</v>
+      </c>
+      <c r="F5" s="3">
+        <v>1</v>
+      </c>
+      <c r="G5" s="8">
+        <f>F5*E5</f>
+        <v>8</v>
+      </c>
+      <c r="J5" s="10"/>
     </row>
     <row r="6" ht="14.25">
       <c r="B6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>7</v>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="E6" s="7">
+        <v>3.29</v>
+      </c>
+      <c r="F6" s="3">
+        <v>1</v>
+      </c>
+      <c r="G6" s="8">
+        <f>F6*E6</f>
+        <v>3.29</v>
+      </c>
+      <c r="I6" s="10"/>
+    </row>
+    <row r="7" ht="14.25">
+      <c r="B7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="E7" s="7">
+        <v>0.5</v>
+      </c>
+      <c r="F7" s="3">
+        <v>1</v>
+      </c>
+      <c r="G7" s="8">
+        <f>F7*E7</f>
+        <v>0.5</v>
+      </c>
+      <c r="I7" s="10"/>
+    </row>
+    <row r="8" ht="14.25">
+      <c r="B8" t="s">
+        <v>16</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="E8" s="7">
+        <v>0.20000000000000001</v>
+      </c>
+      <c r="F8" s="3">
+        <v>2</v>
+      </c>
+      <c r="G8" s="8">
+        <f>F8*E8</f>
+        <v>0.40000000000000002</v>
+      </c>
+    </row>
+    <row r="9" ht="14.25">
+      <c r="B9" t="s">
+        <v>18</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="E9" s="7">
+        <v>0.70999999999999996</v>
+      </c>
+      <c r="F9" s="3">
+        <v>2</v>
+      </c>
+      <c r="G9" s="8">
+        <f>F9*E9</f>
+        <v>1.4199999999999999</v>
+      </c>
+    </row>
+    <row r="10" ht="14.25">
+      <c r="B10" t="s">
+        <v>20</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="E10" s="7">
+        <v>5.0700000000000003</v>
+      </c>
+      <c r="F10" s="3">
+        <v>1</v>
+      </c>
+      <c r="G10" s="8">
+        <f>F10*E10</f>
+        <v>5.0700000000000003</v>
+      </c>
+    </row>
+    <row r="11" ht="14.25">
+      <c r="B11" t="s">
+        <v>22</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="E11" s="7">
+        <v>0.40999999999999998</v>
+      </c>
+      <c r="F11" s="3">
+        <v>1</v>
+      </c>
+      <c r="G11" s="8">
+        <f>F11*E11</f>
+        <v>0.40999999999999998</v>
+      </c>
+    </row>
+    <row r="14" ht="14.25">
+      <c r="G14" s="10"/>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink r:id="rId1" ref="C6" tooltip=""/>
+    <hyperlink r:id="rId1" ref="C4" tooltip=""/>
+    <hyperlink r:id="rId2" ref="C6" tooltip=""/>
+    <hyperlink r:id="rId3" ref="C7" tooltip=""/>
+    <hyperlink r:id="rId4" ref="C8" tooltip=""/>
+    <hyperlink r:id="rId5" ref="C9" tooltip=""/>
+    <hyperlink r:id="rId6" ref="C10" tooltip=""/>
+    <hyperlink r:id="rId7" ref="C11" tooltip=""/>
   </hyperlinks>
   <printOptions headings="0" gridLines="0"/>
   <pageMargins left="0.70078740157480324" right="0.70078740157480324" top="0.75196850393700787" bottom="0.75196850393700787" header="0.29999999999999999" footer="0.29999999999999999"/>

--- a/Hardware/Matériel.xlsx
+++ b/Hardware/Matériel.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
   <si>
     <t>Nom</t>
   </si>
@@ -62,16 +62,10 @@
     <t>TR10S05</t>
   </si>
   <si>
-    <t xml:space="preserve">LED RGB</t>
-  </si>
-  <si>
-    <t xml:space="preserve">APA102 - 150505M173300</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Level Shifter</t>
-  </si>
-  <si>
-    <t>SN74LVC1G17DBVR</t>
+    <t xml:space="preserve">Écran OLED</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DST-015 (OLED based SSD1305)</t>
   </si>
   <si>
     <t>Bornier</t>
@@ -146,13 +140,10 @@
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf fontId="0" fillId="2" borderId="0" numFmtId="44" applyNumberFormat="1" applyFont="0" applyFill="0" applyBorder="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="10">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -678,7 +669,7 @@
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col bestFit="1" customWidth="1" min="2" max="2" width="24.390625"/>
-    <col customWidth="1" min="3" max="3" width="25.57421875"/>
+    <col bestFit="1" customWidth="1" min="3" max="3" width="27.7734375"/>
     <col bestFit="1" customWidth="1" min="4" max="4" width="10.86328125"/>
     <col bestFit="1" min="5" max="6" width="9.58203125"/>
     <col bestFit="1" min="7" max="7" width="10.6328125"/>
@@ -696,13 +687,13 @@
       <c r="D3" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="E3" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="F3" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="G3" s="4" t="s">
+      <c r="G3" s="3" t="s">
         <v>5</v>
       </c>
     </row>
@@ -710,20 +701,20 @@
       <c r="B4" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="C4" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="D4" s="6" t="s">
+      <c r="D4" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="E4" s="7">
+      <c r="E4" s="6">
         <v>5.9400000000000004</v>
       </c>
-      <c r="F4" s="3">
+      <c r="F4" s="2">
         <v>1</v>
       </c>
-      <c r="G4" s="8">
-        <f>F4*E4</f>
+      <c r="G4" s="7">
+        <f t="shared" ref="G4:G6" si="0">F4*E4</f>
         <v>5.9400000000000004</v>
       </c>
     </row>
@@ -734,151 +725,130 @@
       <c r="C5" t="s">
         <v>10</v>
       </c>
-      <c r="D5" s="9" t="s">
+      <c r="D5" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="E5" s="7">
+      <c r="E5" s="6">
         <v>8</v>
       </c>
-      <c r="F5" s="3">
+      <c r="F5" s="2">
         <v>1</v>
       </c>
-      <c r="G5" s="8">
-        <f>F5*E5</f>
+      <c r="G5" s="7">
+        <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="J5" s="10"/>
+      <c r="J5" s="9"/>
     </row>
     <row r="6" ht="14.25">
       <c r="B6" t="s">
         <v>12</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="C6" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="D6" s="6" t="s">
+      <c r="D6" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="E6" s="7">
+      <c r="E6" s="6">
         <v>3.29</v>
       </c>
-      <c r="F6" s="3">
+      <c r="F6" s="2">
         <v>1</v>
       </c>
-      <c r="G6" s="8">
-        <f>F6*E6</f>
+      <c r="G6" s="7">
+        <f t="shared" si="0"/>
         <v>3.29</v>
       </c>
-      <c r="I6" s="10"/>
+      <c r="I6" s="9"/>
     </row>
     <row r="7" ht="14.25">
       <c r="B7" t="s">
         <v>14</v>
       </c>
-      <c r="C7" s="5" t="s">
+      <c r="C7" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="D7" s="6" t="s">
+      <c r="D7" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="E7" s="7">
-        <v>0.5</v>
-      </c>
-      <c r="F7" s="3">
+      <c r="E7" s="6">
+        <v>5.3600000000000003</v>
+      </c>
+      <c r="F7" s="2">
         <v>1</v>
       </c>
-      <c r="G7" s="8">
+      <c r="G7" s="7">
         <f>F7*E7</f>
-        <v>0.5</v>
-      </c>
-      <c r="I7" s="10"/>
+        <v>5.3600000000000003</v>
+      </c>
+      <c r="I7" s="9"/>
     </row>
     <row r="8" ht="14.25">
       <c r="B8" t="s">
         <v>16</v>
       </c>
-      <c r="C8" s="5" t="s">
+      <c r="C8" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="D8" s="6" t="s">
+      <c r="D8" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="E8" s="7">
-        <v>0.20000000000000001</v>
-      </c>
-      <c r="F8" s="3">
+      <c r="E8" s="6">
+        <v>0.70999999999999996</v>
+      </c>
+      <c r="F8" s="2">
         <v>2</v>
       </c>
-      <c r="G8" s="8">
+      <c r="G8" s="7">
         <f>F8*E8</f>
-        <v>0.40000000000000002</v>
+        <v>1.4199999999999999</v>
       </c>
     </row>
     <row r="9" ht="14.25">
       <c r="B9" t="s">
         <v>18</v>
       </c>
-      <c r="C9" s="5" t="s">
+      <c r="C9" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="D9" s="6" t="s">
+      <c r="D9" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="E9" s="7">
-        <v>0.70999999999999996</v>
-      </c>
-      <c r="F9" s="3">
-        <v>2</v>
-      </c>
-      <c r="G9" s="8">
+      <c r="E9" s="6">
+        <v>5.0700000000000003</v>
+      </c>
+      <c r="F9" s="2">
+        <v>1</v>
+      </c>
+      <c r="G9" s="7">
         <f>F9*E9</f>
-        <v>1.4199999999999999</v>
+        <v>5.0700000000000003</v>
       </c>
     </row>
     <row r="10" ht="14.25">
       <c r="B10" t="s">
         <v>20</v>
       </c>
-      <c r="C10" s="5" t="s">
+      <c r="C10" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="D10" s="6" t="s">
+      <c r="D10" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="E10" s="7">
-        <v>5.0700000000000003</v>
-      </c>
-      <c r="F10" s="3">
+      <c r="E10" s="6">
+        <v>0.40999999999999998</v>
+      </c>
+      <c r="F10" s="2">
         <v>1</v>
       </c>
-      <c r="G10" s="8">
+      <c r="G10" s="7">
         <f>F10*E10</f>
-        <v>5.0700000000000003</v>
-      </c>
-    </row>
-    <row r="11" ht="14.25">
-      <c r="B11" t="s">
-        <v>22</v>
-      </c>
-      <c r="C11" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="D11" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="E11" s="7">
-        <v>0.40999999999999998</v>
-      </c>
-      <c r="F11" s="3">
-        <v>1</v>
-      </c>
-      <c r="G11" s="8">
-        <f>F11*E11</f>
         <v>0.40999999999999998</v>
       </c>
     </row>
     <row r="14" ht="14.25">
-      <c r="G14" s="10"/>
+      <c r="G14" s="9"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -888,7 +858,6 @@
     <hyperlink r:id="rId4" ref="C8" tooltip=""/>
     <hyperlink r:id="rId5" ref="C9" tooltip=""/>
     <hyperlink r:id="rId6" ref="C10" tooltip=""/>
-    <hyperlink r:id="rId7" ref="C11" tooltip=""/>
   </hyperlinks>
   <printOptions headings="0" gridLines="0"/>
   <pageMargins left="0.70078740157480324" right="0.70078740157480324" top="0.75196850393700787" bottom="0.75196850393700787" header="0.29999999999999999" footer="0.29999999999999999"/>

--- a/Hardware/Matériel.xlsx
+++ b/Hardware/Matériel.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="35">
   <si>
     <t>Nom</t>
   </si>
@@ -35,7 +35,7 @@
     <t>nombre</t>
   </si>
   <si>
-    <t>tot</t>
+    <t>somme</t>
   </si>
   <si>
     <t>ESP32</t>
@@ -59,7 +59,7 @@
     <t>Alimentation</t>
   </si>
   <si>
-    <t>TR10S05</t>
+    <t>TR10S3V3</t>
   </si>
   <si>
     <t xml:space="preserve">Écran OLED</t>
@@ -84,6 +84,45 @@
   </si>
   <si>
     <t>SLW-874744-6A-RA-N-D</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Diode Schottky</t>
+  </si>
+  <si>
+    <t>1N5822-T</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LED (ambre)</t>
+  </si>
+  <si>
+    <t>LTST-C150AKT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Résistance 68R</t>
+  </si>
+  <si>
+    <t>AC1206JR-0768RL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Résistance 120R</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> RC1206JR-07120RL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Résistance 4k7</t>
+  </si>
+  <si>
+    <t>RC1206JR-104K7L</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Condensateur  22 uF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Condensateur  47 uF</t>
+  </si>
+  <si>
+    <t>total</t>
   </si>
 </sst>
 </file>
@@ -140,7 +179,7 @@
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf fontId="0" fillId="2" borderId="0" numFmtId="44" applyNumberFormat="1" applyFont="0" applyFill="0" applyBorder="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="12">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -163,6 +202,8 @@
       <alignment horizontal="center"/>
     </xf>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="164" xfId="0" applyNumberFormat="1"/>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
+    <xf fontId="1" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -714,7 +755,7 @@
         <v>1</v>
       </c>
       <c r="G4" s="7">
-        <f t="shared" ref="G4:G6" si="0">F4*E4</f>
+        <f t="shared" ref="G4:G9" si="0">F4*E4</f>
         <v>5.9400000000000004</v>
       </c>
     </row>
@@ -779,7 +820,7 @@
         <v>1</v>
       </c>
       <c r="G7" s="7">
-        <f>F7*E7</f>
+        <f t="shared" si="0"/>
         <v>5.3600000000000003</v>
       </c>
       <c r="I7" s="9"/>
@@ -801,7 +842,7 @@
         <v>2</v>
       </c>
       <c r="G8" s="7">
-        <f>F8*E8</f>
+        <f t="shared" si="0"/>
         <v>1.4199999999999999</v>
       </c>
     </row>
@@ -822,7 +863,7 @@
         <v>1</v>
       </c>
       <c r="G9" s="7">
-        <f>F9*E9</f>
+        <f t="shared" si="0"/>
         <v>5.0700000000000003</v>
       </c>
     </row>
@@ -847,8 +888,163 @@
         <v>0.40999999999999998</v>
       </c>
     </row>
+    <row r="11" ht="14.25">
+      <c r="B11" t="s">
+        <v>22</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E11" s="6">
+        <v>0.87</v>
+      </c>
+      <c r="F11" s="2">
+        <v>1</v>
+      </c>
+      <c r="G11" s="7">
+        <f>F11*E11</f>
+        <v>0.87</v>
+      </c>
+    </row>
+    <row r="12" ht="14.25">
+      <c r="B12" t="s">
+        <v>24</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E12" s="6">
+        <v>0.11</v>
+      </c>
+      <c r="F12" s="2">
+        <v>2</v>
+      </c>
+      <c r="G12" s="7">
+        <f>F12*E12</f>
+        <v>0.22</v>
+      </c>
+    </row>
+    <row r="13" ht="14.25">
+      <c r="B13" t="s">
+        <v>26</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E13" s="6">
+        <v>8.0000000000000002e-002</v>
+      </c>
+      <c r="F13" s="2">
+        <v>2</v>
+      </c>
+      <c r="G13" s="7">
+        <f>F13*E13</f>
+        <v>0.16</v>
+      </c>
+    </row>
     <row r="14" ht="14.25">
-      <c r="G14" s="9"/>
+      <c r="B14" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="C14" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E14" s="6">
+        <v>8.0000000000000002e-002</v>
+      </c>
+      <c r="F14" s="2">
+        <v>1</v>
+      </c>
+      <c r="G14" s="7">
+        <f>F14*E14</f>
+        <v>8.0000000000000002e-002</v>
+      </c>
+    </row>
+    <row r="15" ht="14.25">
+      <c r="B15" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="C15" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="D15" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E15" s="6">
+        <v>8.0000000000000002e-002</v>
+      </c>
+      <c r="F15" s="2">
+        <v>2</v>
+      </c>
+      <c r="G15" s="7">
+        <f>F15*E15</f>
+        <v>0.16</v>
+      </c>
+    </row>
+    <row r="16" ht="14.25">
+      <c r="B16" t="s">
+        <v>32</v>
+      </c>
+      <c r="C16" s="11" t="str">
+        <f>"860010272001"</f>
+        <v>860010272001</v>
+      </c>
+      <c r="D16" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E16" s="6">
+        <v>8.0000000000000002e-002</v>
+      </c>
+      <c r="F16" s="2">
+        <v>1</v>
+      </c>
+      <c r="G16" s="7">
+        <f>F16*E16</f>
+        <v>8.0000000000000002e-002</v>
+      </c>
+    </row>
+    <row r="17" ht="14.25">
+      <c r="B17" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="C17" s="11" t="str">
+        <f>"860010272003"</f>
+        <v>860010272003</v>
+      </c>
+      <c r="D17" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E17" s="6">
+        <v>8.0000000000000002e-002</v>
+      </c>
+      <c r="F17" s="2">
+        <v>1</v>
+      </c>
+      <c r="G17" s="7">
+        <f>F17*E17</f>
+        <v>8.0000000000000002e-002</v>
+      </c>
+    </row>
+    <row r="19" ht="14.25">
+      <c r="F19" t="s">
+        <v>34</v>
+      </c>
+      <c r="G19" s="9">
+        <f>SUM(G4:G17)</f>
+        <v>31.139999999999993</v>
+      </c>
     </row>
   </sheetData>
   <hyperlinks>
@@ -858,10 +1054,17 @@
     <hyperlink r:id="rId4" ref="C8" tooltip=""/>
     <hyperlink r:id="rId5" ref="C9" tooltip=""/>
     <hyperlink r:id="rId6" ref="C10" tooltip=""/>
+    <hyperlink r:id="rId7" ref="C11" tooltip=""/>
+    <hyperlink r:id="rId8" ref="C12" tooltip=""/>
+    <hyperlink r:id="rId9" ref="C13" tooltip=""/>
+    <hyperlink r:id="rId10" ref="C14" tooltip=""/>
+    <hyperlink r:id="rId11" ref="C15" tooltip=""/>
+    <hyperlink r:id="rId12" ref="C16" tooltip=""/>
+    <hyperlink r:id="rId13" ref="C17" tooltip=""/>
   </hyperlinks>
   <printOptions headings="0" gridLines="0"/>
   <pageMargins left="0.70078740157480324" right="0.70078740157480324" top="0.75196850393700787" bottom="0.75196850393700787" header="0.29999999999999999" footer="0.29999999999999999"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="landscape" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
   <headerFooter/>
 </worksheet>
 </file>

--- a/Hardware/Matériel.xlsx
+++ b/Hardware/Matériel.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="48">
   <si>
     <t>Nom</t>
   </si>
@@ -59,7 +59,7 @@
     <t>Alimentation</t>
   </si>
   <si>
-    <t>TR10S3V3</t>
+    <t xml:space="preserve">TSR 1-2433E</t>
   </si>
   <si>
     <t xml:space="preserve">Écran OLED</t>
@@ -86,40 +86,79 @@
     <t>SLW-874744-6A-RA-N-D</t>
   </si>
   <si>
+    <t xml:space="preserve">LED (ambre)</t>
+  </si>
+  <si>
+    <t>LTST-C150AKT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Résistance 68R</t>
+  </si>
+  <si>
+    <t>AC1206JR-0768RL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Résistance 120R</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> RC1206JR-07120RL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Résistance 4k7</t>
+  </si>
+  <si>
+    <t>RC1206JR-104K7L</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Condensateur  10 uF ceram</t>
+  </si>
+  <si>
+    <t>CL31A106MBHNNNE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Condensateur  4,7 uF ceram</t>
+  </si>
+  <si>
+    <t>CL10A475MQ8NQWC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Condensateur  22 uF ceram</t>
+  </si>
+  <si>
+    <t>GRM188R61A226ME15D</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Condensateur  470 uF elec</t>
+  </si>
+  <si>
+    <t>REF1020471M050K</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fusible réarmable PTC</t>
+  </si>
+  <si>
+    <t>MF-R050</t>
+  </si>
+  <si>
+    <t xml:space="preserve">diode TVS</t>
+  </si>
+  <si>
     <t xml:space="preserve">Diode Schottky</t>
   </si>
   <si>
-    <t>1N5822-T</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LED (ambre)</t>
-  </si>
-  <si>
-    <t>LTST-C150AKT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Résistance 68R</t>
-  </si>
-  <si>
-    <t>AC1206JR-0768RL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Résistance 120R</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> RC1206JR-07120RL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Résistance 4k7</t>
-  </si>
-  <si>
-    <t>RC1206JR-104K7L</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Condensateur  22 uF</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Condensateur  47 uF</t>
+    <t>BX36_R1_00001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">inductance de mode commun</t>
+  </si>
+  <si>
+    <t>SS11VL-11050</t>
+  </si>
+  <si>
+    <t>Varistance</t>
+  </si>
+  <si>
+    <t>MOV-20D470K</t>
   </si>
   <si>
     <t>total</t>
@@ -179,7 +218,7 @@
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf fontId="0" fillId="2" borderId="0" numFmtId="44" applyNumberFormat="1" applyFont="0" applyFill="0" applyBorder="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="14">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -203,7 +242,13 @@
     </xf>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="164" xfId="0" applyNumberFormat="1"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
-    <xf fontId="1" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
+    <xf fontId="1" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0">
+      <protection hidden="0" locked="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -709,11 +754,12 @@
   </sheetPr>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col bestFit="1" customWidth="1" min="2" max="2" width="24.390625"/>
+    <col customWidth="1" min="2" max="2" width="29.140625"/>
     <col bestFit="1" customWidth="1" min="3" max="3" width="27.7734375"/>
     <col bestFit="1" customWidth="1" min="4" max="4" width="10.86328125"/>
-    <col bestFit="1" min="5" max="6" width="9.58203125"/>
-    <col bestFit="1" min="7" max="7" width="10.6328125"/>
+    <col bestFit="1" min="5" max="5" width="12.953125"/>
+    <col bestFit="1" min="6" max="6" width="9.58203125"/>
+    <col bestFit="1" min="7" max="7" width="12.953125"/>
     <col bestFit="1" min="9" max="9" width="11.69140625"/>
     <col bestFit="1" min="10" max="10" width="10.6328125"/>
   </cols>
@@ -792,14 +838,14 @@
         <v>8</v>
       </c>
       <c r="E6" s="6">
-        <v>3.29</v>
+        <v>2.9199999999999999</v>
       </c>
       <c r="F6" s="2">
         <v>1</v>
       </c>
       <c r="G6" s="7">
         <f t="shared" si="0"/>
-        <v>3.29</v>
+        <v>2.9199999999999999</v>
       </c>
       <c r="I6" s="9"/>
     </row>
@@ -899,14 +945,14 @@
         <v>8</v>
       </c>
       <c r="E11" s="6">
-        <v>0.87</v>
+        <v>0.11</v>
       </c>
       <c r="F11" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G11" s="7">
         <f>F11*E11</f>
-        <v>0.87</v>
+        <v>0.22</v>
       </c>
     </row>
     <row r="12" ht="14.25">
@@ -920,18 +966,18 @@
         <v>8</v>
       </c>
       <c r="E12" s="6">
-        <v>0.11</v>
+        <v>0.080000000000000002</v>
       </c>
       <c r="F12" s="2">
         <v>2</v>
       </c>
       <c r="G12" s="7">
         <f>F12*E12</f>
-        <v>0.22</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="13" ht="14.25">
-      <c r="B13" t="s">
+      <c r="B13" s="10" t="s">
         <v>26</v>
       </c>
       <c r="C13" s="4" t="s">
@@ -941,109 +987,233 @@
         <v>8</v>
       </c>
       <c r="E13" s="6">
-        <v>8.0000000000000002e-002</v>
+        <v>0.080000000000000002</v>
       </c>
       <c r="F13" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G13" s="7">
         <f>F13*E13</f>
-        <v>0.16</v>
+        <v>0.080000000000000002</v>
       </c>
     </row>
     <row r="14" ht="14.25">
       <c r="B14" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="C14" s="11" t="s">
+      <c r="C14" s="4" t="s">
         <v>29</v>
       </c>
       <c r="D14" s="5" t="s">
         <v>8</v>
       </c>
       <c r="E14" s="6">
-        <v>8.0000000000000002e-002</v>
+        <v>0.080000000000000002</v>
       </c>
       <c r="F14" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G14" s="7">
         <f>F14*E14</f>
-        <v>8.0000000000000002e-002</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="15" ht="14.25">
-      <c r="B15" s="10" t="s">
+      <c r="B15" t="s">
         <v>30</v>
       </c>
-      <c r="C15" s="11" t="s">
+      <c r="C15" s="4" t="s">
         <v>31</v>
       </c>
       <c r="D15" s="5" t="s">
         <v>8</v>
       </c>
       <c r="E15" s="6">
-        <v>8.0000000000000002e-002</v>
+        <v>0.20999999999999999</v>
       </c>
       <c r="F15" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G15" s="7">
         <f>F15*E15</f>
-        <v>0.16</v>
+        <v>0.20999999999999999</v>
       </c>
     </row>
     <row r="16" ht="14.25">
-      <c r="B16" t="s">
+      <c r="B16" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="C16" s="11" t="str">
-        <f>"860010272001"</f>
-        <v>860010272001</v>
+      <c r="C16" s="4" t="s">
+        <v>33</v>
       </c>
       <c r="D16" s="5" t="s">
         <v>8</v>
       </c>
       <c r="E16" s="6">
-        <v>8.0000000000000002e-002</v>
+        <v>0.080000000000000002</v>
       </c>
       <c r="F16" s="2">
         <v>1</v>
       </c>
       <c r="G16" s="7">
         <f>F16*E16</f>
-        <v>8.0000000000000002e-002</v>
+        <v>0.080000000000000002</v>
       </c>
     </row>
     <row r="17" ht="14.25">
-      <c r="B17" s="10" t="s">
-        <v>33</v>
-      </c>
-      <c r="C17" s="11" t="str">
-        <f>"860010272003"</f>
-        <v>860010272003</v>
+      <c r="B17" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>35</v>
       </c>
       <c r="D17" s="5" t="s">
         <v>8</v>
       </c>
       <c r="E17" s="6">
-        <v>8.0000000000000002e-002</v>
+        <v>0.089999999999999997</v>
       </c>
       <c r="F17" s="2">
         <v>1</v>
       </c>
       <c r="G17" s="7">
         <f>F17*E17</f>
-        <v>8.0000000000000002e-002</v>
+        <v>0.089999999999999997</v>
+      </c>
+    </row>
+    <row r="18" ht="14.25">
+      <c r="B18" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="D18" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E18" s="6">
+        <v>0.56999999999999995</v>
+      </c>
+      <c r="F18" s="2">
+        <v>1</v>
+      </c>
+      <c r="G18" s="7">
+        <f>F18*E18</f>
+        <v>0.56999999999999995</v>
       </c>
     </row>
     <row r="19" ht="14.25">
-      <c r="F19" t="s">
-        <v>34</v>
-      </c>
-      <c r="G19" s="9">
-        <f>SUM(G4:G17)</f>
-        <v>31.139999999999993</v>
+      <c r="B19" t="s">
+        <v>38</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="D19" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E19" s="6">
+        <v>0.32000000000000001</v>
+      </c>
+      <c r="F19" s="2">
+        <v>1</v>
+      </c>
+      <c r="G19" s="7">
+        <f>F19*E19</f>
+        <v>0.32000000000000001</v>
+      </c>
+    </row>
+    <row r="20" ht="14.25">
+      <c r="B20" t="s">
+        <v>40</v>
+      </c>
+      <c r="C20" s="12">
+        <v>824500281</v>
+      </c>
+      <c r="D20" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E20" s="6">
+        <v>0.26000000000000001</v>
+      </c>
+      <c r="F20" s="2">
+        <v>1</v>
+      </c>
+      <c r="G20" s="7">
+        <f>F20*E20</f>
+        <v>0.26000000000000001</v>
+      </c>
+    </row>
+    <row r="21" ht="14.25">
+      <c r="B21" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="D21" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E21" s="6">
+        <v>0.29999999999999999</v>
+      </c>
+      <c r="F21" s="2">
+        <v>1</v>
+      </c>
+      <c r="G21" s="7">
+        <f>F21*E21</f>
+        <v>0.29999999999999999</v>
+      </c>
+    </row>
+    <row r="22" ht="14.25">
+      <c r="B22" t="s">
+        <v>43</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="D22" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E22" s="6">
+        <v>1.49</v>
+      </c>
+      <c r="F22" s="2">
+        <v>1</v>
+      </c>
+      <c r="G22" s="7">
+        <f>F22*E22</f>
+        <v>1.49</v>
+      </c>
+    </row>
+    <row r="23" ht="14.25">
+      <c r="B23" t="s">
+        <v>45</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="D23" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E23" s="6">
+        <v>0.67000000000000004</v>
+      </c>
+      <c r="F23" s="2">
+        <v>1</v>
+      </c>
+      <c r="G23" s="7">
+        <f>F23*E23</f>
+        <v>0.67000000000000004</v>
+      </c>
+    </row>
+    <row r="25" ht="14.25">
+      <c r="F25" t="s">
+        <v>47</v>
+      </c>
+      <c r="G25" s="9">
+        <f>SUM(G4:G22)</f>
+        <v>33.060000000000002</v>
       </c>
     </row>
   </sheetData>
@@ -1061,6 +1231,12 @@
     <hyperlink r:id="rId11" ref="C15" tooltip=""/>
     <hyperlink r:id="rId12" ref="C16" tooltip=""/>
     <hyperlink r:id="rId13" ref="C17" tooltip=""/>
+    <hyperlink r:id="rId14" ref="C18" tooltip=""/>
+    <hyperlink r:id="rId15" ref="C19" tooltip=""/>
+    <hyperlink r:id="rId16" ref="C20" tooltip=""/>
+    <hyperlink r:id="rId17" ref="C21" tooltip=""/>
+    <hyperlink r:id="rId18" ref="C22" tooltip=""/>
+    <hyperlink r:id="rId19" ref="C23" tooltip=""/>
   </hyperlinks>
   <printOptions headings="0" gridLines="0"/>
   <pageMargins left="0.70078740157480324" right="0.70078740157480324" top="0.75196850393700787" bottom="0.75196850393700787" header="0.29999999999999999" footer="0.29999999999999999"/>

--- a/Hardware/Matériel.xlsx
+++ b/Hardware/Matériel.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="66">
   <si>
     <t>Nom</t>
   </si>
@@ -26,6 +26,9 @@
     <t>Ref</t>
   </si>
   <si>
+    <t>datasheet</t>
+  </si>
+  <si>
     <t>Fournisseur</t>
   </si>
   <si>
@@ -44,6 +47,9 @@
     <t>XIAO-ESP32-S3</t>
   </si>
   <si>
+    <t>./Datasheets/esp32-s3.pdf</t>
+  </si>
+  <si>
     <t>Mouser</t>
   </si>
   <si>
@@ -62,6 +68,9 @@
     <t xml:space="preserve">TSR 1-2433E</t>
   </si>
   <si>
+    <t xml:space="preserve">./Datasheets/TSR 1-2433E - tsr1e_datasheet.pdf</t>
+  </si>
+  <si>
     <t xml:space="preserve">Écran OLED</t>
   </si>
   <si>
@@ -74,36 +83,54 @@
     <t>TB0011-350-04GR</t>
   </si>
   <si>
+    <t>./Datasheets/TB0011-350-04GR.pdf</t>
+  </si>
+  <si>
     <t xml:space="preserve">transceiver UART &lt;-&gt; RS485</t>
   </si>
   <si>
     <t>MAX3485CSA+T</t>
   </si>
   <si>
+    <t>./Datasheets/MAX3483_MAX3491.pdf</t>
+  </si>
+  <si>
     <t xml:space="preserve">Switch horizontal</t>
   </si>
   <si>
     <t>SLW-874744-6A-RA-N-D</t>
   </si>
   <si>
+    <t>./Datasheets/slw_874744_6a_ra_n_d.pdf</t>
+  </si>
+  <si>
     <t xml:space="preserve">LED (ambre)</t>
   </si>
   <si>
     <t>LTST-C150AKT</t>
   </si>
   <si>
+    <t xml:space="preserve">./Datasheets/AmberLed - LTST-C150AKT.pdf</t>
+  </si>
+  <si>
     <t xml:space="preserve">Résistance 68R</t>
   </si>
   <si>
     <t>AC1206JR-0768RL</t>
   </si>
   <si>
+    <t xml:space="preserve">./Datasheets/68R - PYU_AC_51_ROHS_L.pdf</t>
+  </si>
+  <si>
     <t xml:space="preserve">Résistance 120R</t>
   </si>
   <si>
     <t xml:space="preserve"> RC1206JR-07120RL</t>
   </si>
   <si>
+    <t xml:space="preserve">./Datasheets/120R - YAGEO_PYu_RC_Group_51_RoHS_L_12.pdf</t>
+  </si>
+  <si>
     <t xml:space="preserve">Résistance 4k7</t>
   </si>
   <si>
@@ -116,16 +143,25 @@
     <t>CL31A106MBHNNNE</t>
   </si>
   <si>
+    <t xml:space="preserve">./Datasheets/Condensateur  10 uF ceram - DataSheet_CL31A106MBHNNN_20260505.pdf</t>
+  </si>
+  <si>
     <t xml:space="preserve">Condensateur  4,7 uF ceram</t>
   </si>
   <si>
-    <t>CL10A475MQ8NQWC</t>
+    <t>GRM319R61H475KA12D</t>
+  </si>
+  <si>
+    <t xml:space="preserve">./Datasheets/Condensateur  4,7 uF ceram - Samsung_MLCC-1837944.pdf</t>
   </si>
   <si>
     <t xml:space="preserve">Condensateur  22 uF ceram</t>
   </si>
   <si>
-    <t>GRM188R61A226ME15D</t>
+    <t>RDEC71H226MWK1H03B</t>
+  </si>
+  <si>
+    <t xml:space="preserve">./Datasheets/Condensateur  22 uF ceram - GRM188R61A226ME15-02A.pdf</t>
   </si>
   <si>
     <t xml:space="preserve">Condensateur  470 uF elec</t>
@@ -134,31 +170,49 @@
     <t>REF1020471M050K</t>
   </si>
   <si>
+    <t xml:space="preserve">./Datasheets/Condensateur  470 uF elec - ref-series.pdf</t>
+  </si>
+  <si>
     <t xml:space="preserve">Fusible réarmable PTC</t>
   </si>
   <si>
     <t>MF-R050</t>
   </si>
   <si>
+    <t>./Datasheets/PTC.pdf</t>
+  </si>
+  <si>
     <t xml:space="preserve">diode TVS</t>
   </si>
   <si>
+    <t xml:space="preserve">./Datasheets/diode TVS - 824500281.pdf</t>
+  </si>
+  <si>
     <t xml:space="preserve">Diode Schottky</t>
   </si>
   <si>
     <t>BX36_R1_00001</t>
   </si>
   <si>
+    <t xml:space="preserve">./Datasheets/Diode - BX36_R1_00001.pdf</t>
+  </si>
+  <si>
     <t xml:space="preserve">inductance de mode commun</t>
   </si>
   <si>
     <t>SS11VL-11050</t>
   </si>
   <si>
+    <t xml:space="preserve">./Datasheets/induct - SS11VL_11050.pdf</t>
+  </si>
+  <si>
     <t>Varistance</t>
   </si>
   <si>
     <t>MOV-20D470K</t>
+  </si>
+  <si>
+    <t xml:space="preserve">./Datasheets/Varistance - mov20d.pdf</t>
   </si>
   <si>
     <t>total</t>
@@ -218,7 +272,7 @@
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf fontId="0" fillId="2" borderId="0" numFmtId="44" applyNumberFormat="1" applyFont="0" applyFill="0" applyBorder="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="13">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -241,7 +295,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="164" xfId="0" applyNumberFormat="1"/>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
     <xf fontId="1" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -756,12 +809,13 @@
   <cols>
     <col customWidth="1" min="2" max="2" width="29.140625"/>
     <col bestFit="1" customWidth="1" min="3" max="3" width="27.7734375"/>
-    <col bestFit="1" customWidth="1" min="4" max="4" width="10.86328125"/>
-    <col bestFit="1" min="5" max="5" width="12.953125"/>
-    <col bestFit="1" min="6" max="6" width="9.58203125"/>
-    <col bestFit="1" min="7" max="7" width="12.953125"/>
-    <col bestFit="1" min="9" max="9" width="11.69140625"/>
-    <col bestFit="1" min="10" max="10" width="10.6328125"/>
+    <col bestFit="1" customWidth="1" min="4" max="4" width="76.75390625"/>
+    <col bestFit="1" customWidth="1" min="5" max="5" width="10.86328125"/>
+    <col bestFit="1" min="6" max="6" width="12.953125"/>
+    <col bestFit="1" min="7" max="7" width="9.58203125"/>
+    <col bestFit="1" min="8" max="8" width="12.953125"/>
+    <col bestFit="1" min="10" max="10" width="11.69140625"/>
+    <col bestFit="1" min="11" max="11" width="10.6328125"/>
   </cols>
   <sheetData>
     <row r="3" ht="14.25">
@@ -771,7 +825,7 @@
       <c r="C3" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" s="1" t="s">
         <v>2</v>
       </c>
       <c r="E3" s="2" t="s">
@@ -780,463 +834,540 @@
       <c r="F3" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="G3" s="3" t="s">
+      <c r="G3" s="2" t="s">
         <v>5</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="4" ht="14.25">
       <c r="B4" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="D4" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="E4" s="6">
+      <c r="D4" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="F4" s="6">
         <v>5.9400000000000004</v>
       </c>
-      <c r="F4" s="2">
-        <v>1</v>
-      </c>
-      <c r="G4" s="7">
-        <f t="shared" ref="G4:G9" si="0">F4*E4</f>
+      <c r="G4" s="2">
+        <v>1</v>
+      </c>
+      <c r="H4" s="7">
+        <f t="shared" ref="H4:H9" si="0">G4*F4</f>
         <v>5.9400000000000004</v>
       </c>
     </row>
     <row r="5" ht="14.25">
       <c r="B5" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C5" t="s">
-        <v>10</v>
-      </c>
-      <c r="D5" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="E5" s="6">
+        <v>12</v>
+      </c>
+      <c r="D5" s="4"/>
+      <c r="E5" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F5" s="6">
         <v>8</v>
       </c>
-      <c r="F5" s="2">
-        <v>1</v>
-      </c>
-      <c r="G5" s="7">
+      <c r="G5" s="2">
+        <v>1</v>
+      </c>
+      <c r="H5" s="7">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="J5" s="9"/>
+      <c r="K5" s="9"/>
     </row>
     <row r="6" ht="14.25">
       <c r="B6" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="D6" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="E6" s="6">
+        <v>15</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="F6" s="6">
         <v>2.9199999999999999</v>
       </c>
-      <c r="F6" s="2">
-        <v>1</v>
-      </c>
-      <c r="G6" s="7">
+      <c r="G6" s="2">
+        <v>1</v>
+      </c>
+      <c r="H6" s="7">
         <f t="shared" si="0"/>
         <v>2.9199999999999999</v>
       </c>
-      <c r="I6" s="9"/>
+      <c r="J6" s="9"/>
     </row>
     <row r="7" ht="14.25">
       <c r="B7" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="D7" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="E7" s="6">
+        <v>18</v>
+      </c>
+      <c r="D7" s="4"/>
+      <c r="E7" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="F7" s="6">
         <v>5.3600000000000003</v>
       </c>
-      <c r="F7" s="2">
-        <v>1</v>
-      </c>
-      <c r="G7" s="7">
+      <c r="G7" s="2">
+        <v>1</v>
+      </c>
+      <c r="H7" s="7">
         <f t="shared" si="0"/>
         <v>5.3600000000000003</v>
       </c>
-      <c r="I7" s="9"/>
+      <c r="J7" s="9"/>
     </row>
     <row r="8" ht="14.25">
       <c r="B8" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="D8" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="E8" s="6">
+        <v>20</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="F8" s="6">
         <v>0.70999999999999996</v>
       </c>
-      <c r="F8" s="2">
+      <c r="G8" s="2">
         <v>2</v>
       </c>
-      <c r="G8" s="7">
+      <c r="H8" s="7">
         <f t="shared" si="0"/>
         <v>1.4199999999999999</v>
       </c>
     </row>
     <row r="9" ht="14.25">
       <c r="B9" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="D9" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="E9" s="6">
+        <v>23</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="F9" s="6">
         <v>5.0700000000000003</v>
       </c>
-      <c r="F9" s="2">
-        <v>1</v>
-      </c>
-      <c r="G9" s="7">
+      <c r="G9" s="2">
+        <v>1</v>
+      </c>
+      <c r="H9" s="7">
         <f t="shared" si="0"/>
         <v>5.0700000000000003</v>
       </c>
     </row>
     <row r="10" ht="14.25">
       <c r="B10" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="D10" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="E10" s="6">
+        <v>26</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="F10" s="6">
         <v>0.40999999999999998</v>
       </c>
-      <c r="F10" s="2">
-        <v>1</v>
-      </c>
-      <c r="G10" s="7">
-        <f>F10*E10</f>
+      <c r="G10" s="2">
+        <v>1</v>
+      </c>
+      <c r="H10" s="7">
+        <f t="shared" ref="H10:H23" si="1">G10*F10</f>
         <v>0.40999999999999998</v>
       </c>
     </row>
     <row r="11" ht="14.25">
       <c r="B11" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="D11" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="E11" s="6">
+        <v>29</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="F11" s="6">
         <v>0.11</v>
       </c>
-      <c r="F11" s="2">
+      <c r="G11" s="2">
         <v>2</v>
       </c>
-      <c r="G11" s="7">
-        <f>F11*E11</f>
+      <c r="H11" s="7">
+        <f t="shared" si="1"/>
         <v>0.22</v>
       </c>
     </row>
     <row r="12" ht="14.25">
       <c r="B12" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="D12" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="E12" s="6">
-        <v>0.080000000000000002</v>
-      </c>
-      <c r="F12" s="2">
+        <v>32</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="E12" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="F12" s="6">
+        <v>8.0000000000000002e-002</v>
+      </c>
+      <c r="G12" s="2">
         <v>2</v>
       </c>
-      <c r="G12" s="7">
-        <f>F12*E12</f>
+      <c r="H12" s="7">
+        <f t="shared" si="1"/>
         <v>0.16</v>
       </c>
     </row>
     <row r="13" ht="14.25">
       <c r="B13" s="10" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="D13" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="E13" s="6">
-        <v>0.080000000000000002</v>
-      </c>
-      <c r="F13" s="2">
-        <v>1</v>
-      </c>
-      <c r="G13" s="7">
-        <f>F13*E13</f>
-        <v>0.080000000000000002</v>
+        <v>35</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="E13" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="F13" s="6">
+        <v>8.0000000000000002e-002</v>
+      </c>
+      <c r="G13" s="2">
+        <v>1</v>
+      </c>
+      <c r="H13" s="7">
+        <f t="shared" si="1"/>
+        <v>8.0000000000000002e-002</v>
       </c>
     </row>
     <row r="14" ht="14.25">
       <c r="B14" s="10" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="D14" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="E14" s="6">
-        <v>0.080000000000000002</v>
-      </c>
-      <c r="F14" s="2">
+        <v>38</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="E14" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="F14" s="6">
+        <v>8.0000000000000002e-002</v>
+      </c>
+      <c r="G14" s="2">
         <v>2</v>
       </c>
-      <c r="G14" s="7">
-        <f>F14*E14</f>
+      <c r="H14" s="7">
+        <f t="shared" si="1"/>
         <v>0.16</v>
       </c>
     </row>
     <row r="15" ht="14.25">
       <c r="B15" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="D15" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="E15" s="6">
+        <v>40</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="E15" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="F15" s="6">
         <v>0.20999999999999999</v>
       </c>
-      <c r="F15" s="2">
-        <v>1</v>
-      </c>
-      <c r="G15" s="7">
-        <f>F15*E15</f>
+      <c r="G15" s="2">
+        <v>1</v>
+      </c>
+      <c r="H15" s="7">
+        <f t="shared" si="1"/>
         <v>0.20999999999999999</v>
       </c>
     </row>
     <row r="16" ht="14.25">
-      <c r="B16" s="11" t="s">
-        <v>32</v>
+      <c r="B16" s="10" t="s">
+        <v>42</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="D16" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="E16" s="6">
-        <v>0.080000000000000002</v>
-      </c>
-      <c r="F16" s="2">
-        <v>1</v>
-      </c>
-      <c r="G16" s="7">
-        <f>F16*E16</f>
-        <v>0.080000000000000002</v>
+        <v>43</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="E16" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="F16" s="6">
+        <v>0.17999999999999999</v>
+      </c>
+      <c r="G16" s="2">
+        <v>1</v>
+      </c>
+      <c r="H16" s="7">
+        <f t="shared" si="1"/>
+        <v>0.17999999999999999</v>
       </c>
     </row>
     <row r="17" ht="14.25">
-      <c r="B17" s="11" t="s">
-        <v>34</v>
+      <c r="B17" s="10" t="s">
+        <v>45</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="D17" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="E17" s="6">
-        <v>0.089999999999999997</v>
-      </c>
-      <c r="F17" s="2">
-        <v>1</v>
-      </c>
-      <c r="G17" s="7">
-        <f>F17*E17</f>
-        <v>0.089999999999999997</v>
+        <v>46</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="E17" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="F17" s="6">
+        <v>1.3100000000000001</v>
+      </c>
+      <c r="G17" s="2">
+        <v>1</v>
+      </c>
+      <c r="H17" s="7">
+        <f t="shared" si="1"/>
+        <v>1.3100000000000001</v>
       </c>
     </row>
     <row r="18" ht="14.25">
-      <c r="B18" s="11" t="s">
-        <v>36</v>
+      <c r="B18" s="10" t="s">
+        <v>48</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="D18" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="E18" s="6">
+        <v>49</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="E18" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="F18" s="6">
         <v>0.56999999999999995</v>
       </c>
-      <c r="F18" s="2">
-        <v>1</v>
-      </c>
-      <c r="G18" s="7">
-        <f>F18*E18</f>
+      <c r="G18" s="2">
+        <v>1</v>
+      </c>
+      <c r="H18" s="7">
+        <f t="shared" si="1"/>
         <v>0.56999999999999995</v>
       </c>
     </row>
     <row r="19" ht="14.25">
       <c r="B19" t="s">
-        <v>38</v>
+        <v>51</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="D19" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="E19" s="6">
+        <v>52</v>
+      </c>
+      <c r="D19" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="E19" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="F19" s="6">
         <v>0.32000000000000001</v>
       </c>
-      <c r="F19" s="2">
-        <v>1</v>
-      </c>
-      <c r="G19" s="7">
-        <f>F19*E19</f>
+      <c r="G19" s="2">
+        <v>1</v>
+      </c>
+      <c r="H19" s="7">
+        <f t="shared" si="1"/>
         <v>0.32000000000000001</v>
       </c>
     </row>
     <row r="20" ht="14.25">
       <c r="B20" t="s">
-        <v>40</v>
-      </c>
-      <c r="C20" s="12">
+        <v>54</v>
+      </c>
+      <c r="C20" s="11">
         <v>824500281</v>
       </c>
-      <c r="D20" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="E20" s="6">
+      <c r="D20" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="E20" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="F20" s="6">
         <v>0.26000000000000001</v>
       </c>
-      <c r="F20" s="2">
-        <v>1</v>
-      </c>
-      <c r="G20" s="7">
-        <f>F20*E20</f>
+      <c r="G20" s="2">
+        <v>1</v>
+      </c>
+      <c r="H20" s="7">
+        <f t="shared" si="1"/>
         <v>0.26000000000000001</v>
       </c>
     </row>
     <row r="21" ht="14.25">
-      <c r="B21" s="13" t="s">
-        <v>41</v>
+      <c r="B21" s="12" t="s">
+        <v>56</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="D21" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="E21" s="6">
+        <v>57</v>
+      </c>
+      <c r="D21" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="E21" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="F21" s="6">
         <v>0.29999999999999999</v>
       </c>
-      <c r="F21" s="2">
-        <v>1</v>
-      </c>
-      <c r="G21" s="7">
-        <f>F21*E21</f>
+      <c r="G21" s="2">
+        <v>1</v>
+      </c>
+      <c r="H21" s="7">
+        <f t="shared" si="1"/>
         <v>0.29999999999999999</v>
       </c>
     </row>
     <row r="22" ht="14.25">
       <c r="B22" t="s">
-        <v>43</v>
+        <v>59</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="D22" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="E22" s="6">
+        <v>60</v>
+      </c>
+      <c r="D22" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="E22" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="F22" s="6">
         <v>1.49</v>
       </c>
-      <c r="F22" s="2">
-        <v>1</v>
-      </c>
-      <c r="G22" s="7">
-        <f>F22*E22</f>
+      <c r="G22" s="2">
+        <v>1</v>
+      </c>
+      <c r="H22" s="7">
+        <f t="shared" si="1"/>
         <v>1.49</v>
       </c>
     </row>
     <row r="23" ht="14.25">
       <c r="B23" t="s">
-        <v>45</v>
+        <v>62</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="D23" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="E23" s="6">
+        <v>63</v>
+      </c>
+      <c r="D23" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E23" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="F23" s="6">
         <v>0.67000000000000004</v>
       </c>
-      <c r="F23" s="2">
-        <v>1</v>
-      </c>
-      <c r="G23" s="7">
-        <f>F23*E23</f>
+      <c r="G23" s="2">
+        <v>1</v>
+      </c>
+      <c r="H23" s="7">
+        <f t="shared" si="1"/>
         <v>0.67000000000000004</v>
       </c>
     </row>
     <row r="25" ht="14.25">
-      <c r="F25" t="s">
-        <v>47</v>
-      </c>
-      <c r="G25" s="9">
-        <f>SUM(G4:G22)</f>
-        <v>33.060000000000002</v>
+      <c r="G25" t="s">
+        <v>65</v>
+      </c>
+      <c r="H25" s="9">
+        <f>SUM(H4:H22)</f>
+        <v>34.379999999999995</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink r:id="rId1" ref="C4" tooltip=""/>
-    <hyperlink r:id="rId2" ref="C6" tooltip=""/>
-    <hyperlink r:id="rId3" ref="C7" tooltip=""/>
-    <hyperlink r:id="rId4" ref="C8" tooltip=""/>
-    <hyperlink r:id="rId5" ref="C9" tooltip=""/>
-    <hyperlink r:id="rId6" ref="C10" tooltip=""/>
-    <hyperlink r:id="rId7" ref="C11" tooltip=""/>
-    <hyperlink r:id="rId8" ref="C12" tooltip=""/>
-    <hyperlink r:id="rId9" ref="C13" tooltip=""/>
-    <hyperlink r:id="rId10" ref="C14" tooltip=""/>
-    <hyperlink r:id="rId11" ref="C15" tooltip=""/>
-    <hyperlink r:id="rId12" ref="C16" tooltip=""/>
-    <hyperlink r:id="rId13" ref="C17" tooltip=""/>
-    <hyperlink r:id="rId14" ref="C18" tooltip=""/>
-    <hyperlink r:id="rId15" ref="C19" tooltip=""/>
-    <hyperlink r:id="rId16" ref="C20" tooltip=""/>
-    <hyperlink r:id="rId17" ref="C21" tooltip=""/>
-    <hyperlink r:id="rId18" ref="C22" tooltip=""/>
-    <hyperlink r:id="rId19" ref="C23" tooltip=""/>
+    <hyperlink r:id="rId2" ref="D4" tooltip=""/>
+    <hyperlink r:id="rId3" ref="C6" tooltip=""/>
+    <hyperlink r:id="rId4" ref="D6" tooltip=""/>
+    <hyperlink r:id="rId5" ref="C7" tooltip=""/>
+    <hyperlink r:id="rId6" ref="C8" tooltip=""/>
+    <hyperlink r:id="rId7" ref="D8" tooltip=""/>
+    <hyperlink r:id="rId8" ref="C9" tooltip=""/>
+    <hyperlink r:id="rId9" ref="D9" tooltip=""/>
+    <hyperlink r:id="rId10" ref="C10" tooltip=""/>
+    <hyperlink r:id="rId11" ref="D10" tooltip=""/>
+    <hyperlink r:id="rId12" ref="C11" tooltip=""/>
+    <hyperlink r:id="rId13" ref="D11" tooltip=""/>
+    <hyperlink r:id="rId14" ref="C12" tooltip=""/>
+    <hyperlink r:id="rId15" ref="D12" tooltip=""/>
+    <hyperlink r:id="rId16" ref="C13" tooltip=""/>
+    <hyperlink r:id="rId17" ref="D13" tooltip=""/>
+    <hyperlink r:id="rId18" ref="C14" tooltip=""/>
+    <hyperlink r:id="rId17" ref="D14" tooltip=""/>
+    <hyperlink r:id="rId19" ref="C15" tooltip=""/>
+    <hyperlink r:id="rId20" ref="D15" tooltip=""/>
+    <hyperlink r:id="rId21" ref="C16" tooltip=""/>
+    <hyperlink r:id="rId22" ref="D16" tooltip=""/>
+    <hyperlink r:id="rId23" ref="C17" tooltip=""/>
+    <hyperlink r:id="rId24" ref="D17" tooltip=""/>
+    <hyperlink r:id="rId25" ref="C18" tooltip=""/>
+    <hyperlink r:id="rId26" ref="D18" tooltip=""/>
+    <hyperlink r:id="rId27" ref="C19" tooltip=""/>
+    <hyperlink r:id="rId28" ref="D19" tooltip=""/>
+    <hyperlink r:id="rId29" ref="C20" tooltip=""/>
+    <hyperlink r:id="rId30" ref="D20" tooltip=""/>
+    <hyperlink r:id="rId31" ref="C21" tooltip=""/>
+    <hyperlink r:id="rId32" ref="D21" tooltip=""/>
+    <hyperlink r:id="rId33" ref="C22" tooltip=""/>
+    <hyperlink r:id="rId34" ref="D22" tooltip=""/>
+    <hyperlink r:id="rId35" ref="C23" tooltip=""/>
+    <hyperlink r:id="rId36" ref="D23" tooltip=""/>
   </hyperlinks>
   <printOptions headings="0" gridLines="0"/>
   <pageMargins left="0.70078740157480324" right="0.70078740157480324" top="0.75196850393700787" bottom="0.75196850393700787" header="0.29999999999999999" footer="0.29999999999999999"/>

--- a/Hardware/Matériel.xlsx
+++ b/Hardware/Matériel.xlsx
@@ -152,7 +152,7 @@
     <t>GRM319R61H475KA12D</t>
   </si>
   <si>
-    <t xml:space="preserve">./Datasheets/Condensateur  4,7 uF ceram - Samsung_MLCC-1837944.pdf</t>
+    <t xml:space="preserve">./Datasheets/Condensateur  4,7 uF ceram - GRM319R61H475KA12_01A.pdf</t>
   </si>
   <si>
     <t xml:space="preserve">Condensateur  22 uF ceram</t>

--- a/Hardware/Matériel.xlsx
+++ b/Hardware/Matériel.xlsx
@@ -9,6 +9,7 @@
     <sheet name="Liste de matériels (prototype)" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Commandes" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="BOM" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="XIAO ESP32" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <calcPr/>
   <extLst>
@@ -18,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="145">
   <si>
     <t>Nom</t>
   </si>
@@ -74,7 +75,7 @@
     <t xml:space="preserve">Écran OLED</t>
   </si>
   <si>
-    <t xml:space="preserve">DST-015 (OLED based SSD1305)</t>
+    <t xml:space="preserve">DST-015 (OLED SSD1305)</t>
   </si>
   <si>
     <t>Bornier</t>
@@ -143,7 +144,7 @@
     <t>CL31A106MBHNNNE</t>
   </si>
   <si>
-    <t xml:space="preserve">./Datasheets/Condensateur  10 uF ceram - DataSheet_CL31A106MBHNNN_20260505.pdf</t>
+    <t>./Datasheets/DataSheet_CL31A106MBHNNN_20260505.pdf</t>
   </si>
   <si>
     <t xml:space="preserve">Condensateur  4,7 uF ceram</t>
@@ -215,7 +216,244 @@
     <t xml:space="preserve">./Datasheets/Varistance - mov20d.pdf</t>
   </si>
   <si>
+    <t xml:space="preserve">inductance torique</t>
+  </si>
+  <si>
+    <t xml:space="preserve">./Datasheets/induct - 7447060.pdf</t>
+  </si>
+  <si>
     <t>total</t>
+  </si>
+  <si>
+    <t>TOUCH1</t>
+  </si>
+  <si>
+    <t>A0</t>
+  </si>
+  <si>
+    <t>GPIO1</t>
+  </si>
+  <si>
+    <t>D0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">XIAO ESP32-S3</t>
+  </si>
+  <si>
+    <t>5V</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dual-core 240MHz</t>
+  </si>
+  <si>
+    <t>TOUCH2</t>
+  </si>
+  <si>
+    <t>A1</t>
+  </si>
+  <si>
+    <t>GPIO2</t>
+  </si>
+  <si>
+    <t>D1</t>
+  </si>
+  <si>
+    <t>GND</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8MB PSRAM</t>
+  </si>
+  <si>
+    <t>TOUCH3</t>
+  </si>
+  <si>
+    <t>A2</t>
+  </si>
+  <si>
+    <t>GPIO3</t>
+  </si>
+  <si>
+    <t>D2</t>
+  </si>
+  <si>
+    <t>3V3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8MB Flash</t>
+  </si>
+  <si>
+    <t>TOUCH4</t>
+  </si>
+  <si>
+    <t>A3</t>
+  </si>
+  <si>
+    <t>GPIO4</t>
+  </si>
+  <si>
+    <t>D3</t>
+  </si>
+  <si>
+    <t>D10</t>
+  </si>
+  <si>
+    <t>GPIO9</t>
+  </si>
+  <si>
+    <t>A10</t>
+  </si>
+  <si>
+    <t>MOSI</t>
+  </si>
+  <si>
+    <t>TOUCH9</t>
+  </si>
+  <si>
+    <t>https://wiki.seeedstudio.com/xiao_esp32s3_getting_started/</t>
+  </si>
+  <si>
+    <t>TOUCH5</t>
+  </si>
+  <si>
+    <t>SDA</t>
+  </si>
+  <si>
+    <t>A4</t>
+  </si>
+  <si>
+    <t>GPIO5</t>
+  </si>
+  <si>
+    <t>D4</t>
+  </si>
+  <si>
+    <t>D9</t>
+  </si>
+  <si>
+    <t>GPIO8</t>
+  </si>
+  <si>
+    <t>A9</t>
+  </si>
+  <si>
+    <t>MISO</t>
+  </si>
+  <si>
+    <t>TOUCH8</t>
+  </si>
+  <si>
+    <t>TOUCH6</t>
+  </si>
+  <si>
+    <t>SCL</t>
+  </si>
+  <si>
+    <t>A5</t>
+  </si>
+  <si>
+    <t>GPIO6</t>
+  </si>
+  <si>
+    <t>D5</t>
+  </si>
+  <si>
+    <t>D8</t>
+  </si>
+  <si>
+    <t>GPIO7</t>
+  </si>
+  <si>
+    <t>A8</t>
+  </si>
+  <si>
+    <t>SCK</t>
+  </si>
+  <si>
+    <t>TOUCH7</t>
+  </si>
+  <si>
+    <t>TX</t>
+  </si>
+  <si>
+    <t>GPIO43</t>
+  </si>
+  <si>
+    <t>D6</t>
+  </si>
+  <si>
+    <t>D7</t>
+  </si>
+  <si>
+    <t>GPIO44</t>
+  </si>
+  <si>
+    <t>RX</t>
+  </si>
+  <si>
+    <t>LP_GPIO1</t>
+  </si>
+  <si>
+    <t>GPIO0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">XIAO ESP32-C6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dual-core 160MHz</t>
+  </si>
+  <si>
+    <t>LP_GPIO2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">512KB SRAM</t>
+  </si>
+  <si>
+    <t>SDIO_DATA1</t>
+  </si>
+  <si>
+    <t>GPIO21</t>
+  </si>
+  <si>
+    <t>GPIO18</t>
+  </si>
+  <si>
+    <t>SDIO_CMD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4 MB Flash</t>
+  </si>
+  <si>
+    <t>SDIO_DATA2</t>
+  </si>
+  <si>
+    <t>GPIO22</t>
+  </si>
+  <si>
+    <t>GPIO20</t>
+  </si>
+  <si>
+    <t>SDIO_DATA0</t>
+  </si>
+  <si>
+    <t>https://wiki.seeedstudio.com/xiao_esp32C6_getting_started/</t>
+  </si>
+  <si>
+    <t>SDIO_DATA3</t>
+  </si>
+  <si>
+    <t>GPIO23</t>
+  </si>
+  <si>
+    <t>GPIO19</t>
+  </si>
+  <si>
+    <t>SDIO_CLK</t>
+  </si>
+  <si>
+    <t>GPIO16</t>
+  </si>
+  <si>
+    <t>GPIO17</t>
   </si>
 </sst>
 </file>
@@ -225,10 +463,31 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="_-* #,##0.00\ [$CHF-100C]_-;\-* #,##0.00\ [$CHF-100C]_-;_-* &quot;-&quot;??\ [$CHF-100C]_-;_-@_-"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="6">
     <font>
       <sz val="11.000000"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10.000000"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="10.000000"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10.000000"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10.000000"/>
       <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
@@ -237,15 +496,6 @@
       <sz val="11.000000"/>
       <color theme="10"/>
       <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11.000000"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11.000000"/>
-      <name val="Calibri"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -272,35 +522,65 @@
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf fontId="0" fillId="2" borderId="0" numFmtId="44" applyNumberFormat="1" applyFont="0" applyFill="0" applyBorder="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="25">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
+    <xf fontId="1" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf fontId="1" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="1" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf fontId="1" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf fontId="2" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf fontId="3" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="1" fillId="0" borderId="0" numFmtId="164" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf fontId="1" fillId="0" borderId="0" numFmtId="164" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf fontId="4" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="164" xfId="0" applyNumberFormat="1"/>
+    <xf fontId="2" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf fontId="1" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1">
+      <protection hidden="0" locked="1"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
+    <xf fontId="5" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf fontId="5" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf fontId="1" fillId="0" borderId="0" numFmtId="164" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" textRotation="180" vertical="center"/>
+    </xf>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment horizontal="center" textRotation="180" vertical="center"/>
     </xf>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf fontId="1" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf fontId="2" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="164" xfId="1" applyNumberFormat="1"/>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="164" xfId="1" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf fontId="3" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="164" xfId="0" applyNumberFormat="1"/>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
-    <xf fontId="1" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0">
-      <protection hidden="0" locked="1"/>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" textRotation="180" vertical="center"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" textRotation="180" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -318,6 +598,116 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math" xmlns:w="http://schemas.openxmlformats.org/wordprocessingml/2006/main">
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>563942</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>78581</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="3962752" cy="1844035"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="498148791" name=""/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill rotWithShape="1">
+        <a:blip r:embed="rId1"/>
+        <a:srcRect l="0" t="9115" r="0" b="37357"/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm flipH="0" flipV="0">
+          <a:off x="6107492" y="983455"/>
+          <a:ext cx="3962752" cy="1844035"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:twoCellAnchor editAs="twoCell">
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>473659</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>162251</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>8905</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>181575</xdr:rowOff>
+    </xdr:to>
+    <xdr:grpSp>
+      <xdr:nvGrpSpPr>
+        <xdr:cNvPr id="0" name=""/>
+        <xdr:cNvGrpSpPr/>
+      </xdr:nvGrpSpPr>
+      <xdr:grpSpPr bwMode="auto">
+        <a:xfrm flipH="0" flipV="0">
+          <a:off x="6017209" y="2876876"/>
+          <a:ext cx="4412045" cy="1647498"/>
+          <a:chOff x="0" y="0"/>
+          <a:chExt cx="4412045" cy="1654693"/>
+        </a:xfrm>
+      </xdr:grpSpPr>
+      <xdr:pic>
+        <xdr:nvPicPr>
+          <xdr:cNvPr id="630608922" name=""/>
+          <xdr:cNvPicPr>
+            <a:picLocks noChangeAspect="1"/>
+          </xdr:cNvPicPr>
+        </xdr:nvPicPr>
+        <xdr:blipFill rotWithShape="1">
+          <a:blip r:embed="rId2"/>
+          <a:srcRect l="0" t="0" r="0" b="55890"/>
+          <a:stretch/>
+        </xdr:blipFill>
+        <xdr:spPr bwMode="auto">
+          <a:xfrm flipH="0" flipV="0">
+            <a:off x="0" y="0"/>
+            <a:ext cx="4412045" cy="1582228"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+        </xdr:spPr>
+      </xdr:pic>
+      <xdr:pic>
+        <xdr:nvPicPr>
+          <xdr:cNvPr id="632672839" name=""/>
+          <xdr:cNvPicPr>
+            <a:picLocks noChangeAspect="1"/>
+          </xdr:cNvPicPr>
+        </xdr:nvPicPr>
+        <xdr:blipFill rotWithShape="1">
+          <a:blip r:embed="rId3"/>
+          <a:srcRect l="0" t="95959" r="0" b="0"/>
+          <a:stretch/>
+        </xdr:blipFill>
+        <xdr:spPr bwMode="auto">
+          <a:xfrm flipH="0" flipV="0">
+            <a:off x="0" y="1509763"/>
+            <a:ext cx="4412045" cy="144929"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+        </xdr:spPr>
+      </xdr:pic>
+    </xdr:grpSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme.xml><?xml version="1.0" encoding="utf-8"?>
@@ -803,17 +1193,17 @@
   <sheetPr>
     <tabColor theme="4" tint="0"/>
     <outlinePr applyStyles="0" summaryBelow="1" summaryRight="1" showOutlineSymbols="1"/>
-    <pageSetUpPr autoPageBreaks="1" fitToPage="0"/>
+    <pageSetUpPr autoPageBreaks="1" fitToPage="1"/>
   </sheetPr>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col customWidth="1" min="2" max="2" width="29.140625"/>
-    <col bestFit="1" customWidth="1" min="3" max="3" width="27.7734375"/>
-    <col bestFit="1" customWidth="1" min="4" max="4" width="76.75390625"/>
-    <col bestFit="1" customWidth="1" min="5" max="5" width="10.86328125"/>
-    <col bestFit="1" min="6" max="6" width="12.953125"/>
-    <col bestFit="1" min="7" max="7" width="9.58203125"/>
-    <col bestFit="1" min="8" max="8" width="12.953125"/>
+    <col bestFit="1" customWidth="1" min="2" max="2" width="24.29296875"/>
+    <col bestFit="1" customWidth="1" min="3" max="3" width="20.03125"/>
+    <col bestFit="1" customWidth="1" min="4" max="4" width="59.4140625"/>
+    <col bestFit="1" customWidth="1" min="5" max="5" width="9.75390625"/>
+    <col bestFit="1" customWidth="1" min="6" max="6" width="11.62109375"/>
+    <col bestFit="1" min="7" max="7" width="6.94140625"/>
+    <col bestFit="1" customWidth="1" min="8" max="8" width="11.62109375"/>
     <col bestFit="1" min="10" max="10" width="11.69140625"/>
     <col bestFit="1" min="11" max="11" width="10.6328125"/>
   </cols>
@@ -842,408 +1232,408 @@
       </c>
     </row>
     <row r="4" ht="14.25">
-      <c r="B4" t="s">
+      <c r="B4" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C4" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="D4" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="E4" s="5" t="s">
+      <c r="E4" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="F4" s="6">
+      <c r="F4" s="7">
         <v>5.9400000000000004</v>
       </c>
       <c r="G4" s="2">
         <v>1</v>
       </c>
-      <c r="H4" s="7">
+      <c r="H4" s="8">
         <f t="shared" ref="H4:H9" si="0">G4*F4</f>
         <v>5.9400000000000004</v>
       </c>
     </row>
     <row r="5" ht="14.25">
-      <c r="B5" t="s">
+      <c r="B5" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C5" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D5" s="4"/>
-      <c r="E5" s="8" t="s">
+      <c r="D5" s="5"/>
+      <c r="E5" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="F5" s="6">
+      <c r="F5" s="7">
         <v>8</v>
       </c>
       <c r="G5" s="2">
         <v>1</v>
       </c>
-      <c r="H5" s="7">
+      <c r="H5" s="8">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="K5" s="9"/>
+      <c r="K5" s="10"/>
     </row>
     <row r="6" ht="14.25">
-      <c r="B6" t="s">
+      <c r="B6" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="C6" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="D6" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="E6" s="5" t="s">
+      <c r="E6" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="F6" s="6">
+      <c r="F6" s="7">
         <v>2.9199999999999999</v>
       </c>
       <c r="G6" s="2">
         <v>1</v>
       </c>
-      <c r="H6" s="7">
+      <c r="H6" s="8">
         <f t="shared" si="0"/>
         <v>2.9199999999999999</v>
       </c>
-      <c r="J6" s="9"/>
+      <c r="J6" s="10"/>
     </row>
     <row r="7" ht="14.25">
-      <c r="B7" t="s">
+      <c r="B7" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="C7" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="D7" s="4"/>
-      <c r="E7" s="5" t="s">
+      <c r="D7" s="5"/>
+      <c r="E7" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="F7" s="6">
+      <c r="F7" s="7">
         <v>5.3600000000000003</v>
       </c>
       <c r="G7" s="2">
         <v>1</v>
       </c>
-      <c r="H7" s="7">
+      <c r="H7" s="8">
         <f t="shared" si="0"/>
         <v>5.3600000000000003</v>
       </c>
-      <c r="J7" s="9"/>
+      <c r="J7" s="10"/>
     </row>
     <row r="8" ht="14.25">
-      <c r="B8" t="s">
+      <c r="B8" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="C8" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="D8" s="4" t="s">
+      <c r="D8" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="E8" s="5" t="s">
+      <c r="E8" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="F8" s="6">
+      <c r="F8" s="7">
         <v>0.70999999999999996</v>
       </c>
       <c r="G8" s="2">
         <v>2</v>
       </c>
-      <c r="H8" s="7">
+      <c r="H8" s="8">
         <f t="shared" si="0"/>
         <v>1.4199999999999999</v>
       </c>
     </row>
     <row r="9" ht="14.25">
-      <c r="B9" t="s">
+      <c r="B9" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="C9" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="D9" s="4" t="s">
+      <c r="D9" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="E9" s="5" t="s">
+      <c r="E9" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="F9" s="6">
+      <c r="F9" s="7">
         <v>5.0700000000000003</v>
       </c>
       <c r="G9" s="2">
         <v>1</v>
       </c>
-      <c r="H9" s="7">
+      <c r="H9" s="8">
         <f t="shared" si="0"/>
         <v>5.0700000000000003</v>
       </c>
     </row>
     <row r="10" ht="14.25">
-      <c r="B10" t="s">
+      <c r="B10" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="C10" s="4" t="s">
+      <c r="C10" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="D10" s="4" t="s">
+      <c r="D10" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="E10" s="5" t="s">
+      <c r="E10" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="F10" s="6">
+      <c r="F10" s="7">
         <v>0.40999999999999998</v>
       </c>
       <c r="G10" s="2">
         <v>1</v>
       </c>
-      <c r="H10" s="7">
+      <c r="H10" s="8">
         <f t="shared" ref="H10:H23" si="1">G10*F10</f>
         <v>0.40999999999999998</v>
       </c>
     </row>
     <row r="11" ht="14.25">
-      <c r="B11" t="s">
+      <c r="B11" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="C11" s="4" t="s">
+      <c r="C11" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="D11" s="4" t="s">
+      <c r="D11" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="E11" s="5" t="s">
+      <c r="E11" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="F11" s="6">
+      <c r="F11" s="7">
         <v>0.11</v>
       </c>
       <c r="G11" s="2">
         <v>2</v>
       </c>
-      <c r="H11" s="7">
+      <c r="H11" s="8">
         <f t="shared" si="1"/>
         <v>0.22</v>
       </c>
     </row>
     <row r="12" ht="14.25">
-      <c r="B12" t="s">
+      <c r="B12" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="C12" s="4" t="s">
+      <c r="C12" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="D12" s="4" t="s">
+      <c r="D12" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="E12" s="5" t="s">
+      <c r="E12" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="F12" s="6">
+      <c r="F12" s="7">
         <v>8.0000000000000002e-002</v>
       </c>
       <c r="G12" s="2">
         <v>2</v>
       </c>
-      <c r="H12" s="7">
+      <c r="H12" s="8">
         <f t="shared" si="1"/>
         <v>0.16</v>
       </c>
     </row>
     <row r="13" ht="14.25">
-      <c r="B13" s="10" t="s">
+      <c r="B13" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="C13" s="4" t="s">
+      <c r="C13" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="D13" s="4" t="s">
+      <c r="D13" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="E13" s="5" t="s">
+      <c r="E13" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="F13" s="6">
+      <c r="F13" s="7">
         <v>8.0000000000000002e-002</v>
       </c>
       <c r="G13" s="2">
         <v>1</v>
       </c>
-      <c r="H13" s="7">
+      <c r="H13" s="8">
         <f t="shared" si="1"/>
         <v>8.0000000000000002e-002</v>
       </c>
     </row>
     <row r="14" ht="14.25">
-      <c r="B14" s="10" t="s">
+      <c r="B14" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="C14" s="4" t="s">
+      <c r="C14" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="D14" s="4" t="s">
+      <c r="D14" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="E14" s="5" t="s">
+      <c r="E14" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="F14" s="6">
+      <c r="F14" s="7">
         <v>8.0000000000000002e-002</v>
       </c>
       <c r="G14" s="2">
         <v>2</v>
       </c>
-      <c r="H14" s="7">
+      <c r="H14" s="8">
         <f t="shared" si="1"/>
         <v>0.16</v>
       </c>
     </row>
     <row r="15" ht="14.25">
-      <c r="B15" t="s">
+      <c r="B15" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="C15" s="4" t="s">
+      <c r="C15" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="D15" s="4" t="s">
+      <c r="D15" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="E15" s="5" t="s">
+      <c r="E15" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="F15" s="6">
+      <c r="F15" s="7">
         <v>0.20999999999999999</v>
       </c>
       <c r="G15" s="2">
         <v>1</v>
       </c>
-      <c r="H15" s="7">
+      <c r="H15" s="8">
         <f t="shared" si="1"/>
         <v>0.20999999999999999</v>
       </c>
     </row>
     <row r="16" ht="14.25">
-      <c r="B16" s="10" t="s">
+      <c r="B16" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="C16" s="4" t="s">
+      <c r="C16" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="D16" s="4" t="s">
+      <c r="D16" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="E16" s="5" t="s">
+      <c r="E16" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="F16" s="6">
+      <c r="F16" s="7">
         <v>0.17999999999999999</v>
       </c>
       <c r="G16" s="2">
         <v>1</v>
       </c>
-      <c r="H16" s="7">
+      <c r="H16" s="8">
         <f t="shared" si="1"/>
         <v>0.17999999999999999</v>
       </c>
     </row>
     <row r="17" ht="14.25">
-      <c r="B17" s="10" t="s">
+      <c r="B17" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="C17" s="4" t="s">
+      <c r="C17" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="D17" s="4" t="s">
+      <c r="D17" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="E17" s="5" t="s">
+      <c r="E17" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="F17" s="6">
+      <c r="F17" s="7">
         <v>1.3100000000000001</v>
       </c>
       <c r="G17" s="2">
         <v>1</v>
       </c>
-      <c r="H17" s="7">
+      <c r="H17" s="8">
         <f t="shared" si="1"/>
         <v>1.3100000000000001</v>
       </c>
     </row>
     <row r="18" ht="14.25">
-      <c r="B18" s="10" t="s">
+      <c r="B18" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="C18" s="4" t="s">
+      <c r="C18" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="D18" s="4" t="s">
+      <c r="D18" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="E18" s="5" t="s">
+      <c r="E18" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="F18" s="6">
+      <c r="F18" s="7">
         <v>0.56999999999999995</v>
       </c>
       <c r="G18" s="2">
         <v>1</v>
       </c>
-      <c r="H18" s="7">
+      <c r="H18" s="8">
         <f t="shared" si="1"/>
         <v>0.56999999999999995</v>
       </c>
     </row>
     <row r="19" ht="14.25">
-      <c r="B19" t="s">
+      <c r="B19" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="C19" s="4" t="s">
+      <c r="C19" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="D19" s="4" t="s">
+      <c r="D19" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="E19" s="5" t="s">
+      <c r="E19" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="F19" s="6">
+      <c r="F19" s="7">
         <v>0.32000000000000001</v>
       </c>
       <c r="G19" s="2">
         <v>1</v>
       </c>
-      <c r="H19" s="7">
+      <c r="H19" s="8">
         <f t="shared" si="1"/>
         <v>0.32000000000000001</v>
       </c>
     </row>
     <row r="20" ht="14.25">
-      <c r="B20" t="s">
+      <c r="B20" s="4" t="s">
         <v>54</v>
       </c>
       <c r="C20" s="11">
         <v>824500281</v>
       </c>
-      <c r="D20" s="4" t="s">
+      <c r="D20" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="E20" s="5" t="s">
+      <c r="E20" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="F20" s="6">
+      <c r="F20" s="7">
         <v>0.26000000000000001</v>
       </c>
       <c r="G20" s="2">
         <v>1</v>
       </c>
-      <c r="H20" s="7">
+      <c r="H20" s="8">
         <f t="shared" si="1"/>
         <v>0.26000000000000001</v>
       </c>
@@ -1252,81 +1642,112 @@
       <c r="B21" s="12" t="s">
         <v>56</v>
       </c>
-      <c r="C21" s="4" t="s">
+      <c r="C21" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="D21" s="4" t="s">
+      <c r="D21" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="E21" s="5" t="s">
+      <c r="E21" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="F21" s="6">
+      <c r="F21" s="7">
         <v>0.29999999999999999</v>
       </c>
       <c r="G21" s="2">
         <v>1</v>
       </c>
-      <c r="H21" s="7">
+      <c r="H21" s="8">
         <f t="shared" si="1"/>
         <v>0.29999999999999999</v>
       </c>
     </row>
     <row r="22" ht="14.25">
-      <c r="B22" t="s">
+      <c r="B22" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="C22" s="4" t="s">
+      <c r="C22" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="D22" s="4" t="s">
+      <c r="D22" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="E22" s="5" t="s">
+      <c r="E22" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="F22" s="6">
+      <c r="F22" s="7">
         <v>1.49</v>
       </c>
       <c r="G22" s="2">
         <v>1</v>
       </c>
-      <c r="H22" s="7">
+      <c r="H22" s="8">
         <f t="shared" si="1"/>
         <v>1.49</v>
       </c>
     </row>
     <row r="23" ht="14.25">
-      <c r="B23" t="s">
+      <c r="B23" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="C23" s="4" t="s">
+      <c r="C23" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="D23" s="4" t="s">
+      <c r="D23" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="E23" s="5" t="s">
+      <c r="E23" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="F23" s="6">
+      <c r="F23" s="7">
         <v>0.67000000000000004</v>
       </c>
       <c r="G23" s="2">
         <v>1</v>
       </c>
-      <c r="H23" s="7">
+      <c r="H23" s="8">
         <f t="shared" si="1"/>
         <v>0.67000000000000004</v>
       </c>
     </row>
+    <row r="24" ht="14.25">
+      <c r="B24" s="13" t="s">
+        <v>65</v>
+      </c>
+      <c r="C24" s="14">
+        <v>7447060</v>
+      </c>
+      <c r="D24" s="15" t="s">
+        <v>66</v>
+      </c>
+      <c r="E24" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="F24" s="7">
+        <v>2.0600000000000001</v>
+      </c>
+      <c r="G24" s="2">
+        <v>1</v>
+      </c>
+      <c r="H24" s="8">
+        <f>G24*F24</f>
+        <v>2.0600000000000001</v>
+      </c>
+    </row>
     <row r="25" ht="14.25">
-      <c r="G25" t="s">
-        <v>65</v>
-      </c>
-      <c r="H25" s="9">
-        <f>SUM(H4:H22)</f>
-        <v>34.379999999999995</v>
+      <c r="B25" s="4"/>
+      <c r="C25" s="4"/>
+      <c r="D25" s="4"/>
+      <c r="E25" s="4"/>
+      <c r="F25" s="4"/>
+    </row>
+    <row r="27" ht="14.25">
+      <c r="G27" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="H27" s="16">
+        <f>SUM(H4:H24)</f>
+        <v>37.109999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -1368,10 +1789,12 @@
     <hyperlink r:id="rId34" ref="D22" tooltip=""/>
     <hyperlink r:id="rId35" ref="C23" tooltip=""/>
     <hyperlink r:id="rId36" ref="D23" tooltip=""/>
+    <hyperlink r:id="rId37" ref="C24" tooltip=""/>
+    <hyperlink r:id="rId38" ref="D24" tooltip=""/>
   </hyperlinks>
   <printOptions headings="0" gridLines="0"/>
-  <pageMargins left="0.70078740157480324" right="0.70078740157480324" top="0.75196850393700787" bottom="0.75196850393700787" header="0.29999999999999999" footer="0.29999999999999999"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="landscape" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
+  <pageMargins left="0.25196850393700787" right="0.25196850393700787" top="0.75196850393700787" bottom="0.75196850393700787" header="0.29999999999999999" footer="0.29999999999999999"/>
+  <pageSetup paperSize="9" scale="98" firstPageNumber="1" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="landscape" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="1" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
   <headerFooter/>
 </worksheet>
 </file>
@@ -1383,7 +1806,7 @@
     <outlinePr applyStyles="0" summaryBelow="1" summaryRight="1" showOutlineSymbols="1"/>
     <pageSetUpPr autoPageBreaks="1" fitToPage="0"/>
   </sheetPr>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData/>
   <printOptions headings="0" gridLines="0"/>
   <pageMargins left="0.70078740157480324" right="0.70078740157480324" top="0.75196850393700787" bottom="0.75196850393700787" header="0.29999999999999999" footer="0.29999999999999999"/>
@@ -1406,4 +1829,398 @@
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
   <headerFooter/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
+  <sheetPr>
+    <tabColor indexed="2"/>
+    <outlinePr applyStyles="0" summaryBelow="1" summaryRight="1" showOutlineSymbols="1"/>
+    <pageSetUpPr autoPageBreaks="1" fitToPage="0"/>
+  </sheetPr>
+  <sheetFormatPr defaultRowHeight="14.25"/>
+  <cols>
+    <col bestFit="1" min="2" max="2" width="11.7421875"/>
+    <col bestFit="1" min="3" max="3" width="9.18359375"/>
+    <col bestFit="1" min="4" max="4" width="4.140625"/>
+    <col bestFit="1" min="5" max="5" width="7.23046875"/>
+    <col bestFit="1" min="6" max="6" width="3.0625"/>
+    <col bestFit="1" min="8" max="8" width="4.68359375"/>
+    <col bestFit="1" min="9" max="9" width="7.23046875"/>
+    <col bestFit="1" min="10" max="10" width="4.07421875"/>
+    <col bestFit="1" min="11" max="11" width="5.421875"/>
+    <col bestFit="1" min="12" max="12" width="7.97265625"/>
+  </cols>
+  <sheetData>
+    <row r="8" ht="14.25">
+      <c r="C8" s="17" t="s">
+        <v>68</v>
+      </c>
+      <c r="D8" s="18" t="s">
+        <v>69</v>
+      </c>
+      <c r="E8" s="18" t="s">
+        <v>70</v>
+      </c>
+      <c r="F8" s="18" t="s">
+        <v>71</v>
+      </c>
+      <c r="G8" s="19" t="s">
+        <v>72</v>
+      </c>
+      <c r="H8" s="20" t="s">
+        <v>73</v>
+      </c>
+      <c r="U8" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="9" ht="14.25">
+      <c r="C9" s="17" t="s">
+        <v>75</v>
+      </c>
+      <c r="D9" s="17" t="s">
+        <v>76</v>
+      </c>
+      <c r="E9" s="17" t="s">
+        <v>77</v>
+      </c>
+      <c r="F9" s="18" t="s">
+        <v>78</v>
+      </c>
+      <c r="G9" s="21"/>
+      <c r="H9" s="20" t="s">
+        <v>79</v>
+      </c>
+      <c r="U9" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="10" ht="14.25">
+      <c r="C10" s="17" t="s">
+        <v>81</v>
+      </c>
+      <c r="D10" s="17" t="s">
+        <v>82</v>
+      </c>
+      <c r="E10" s="17" t="s">
+        <v>83</v>
+      </c>
+      <c r="F10" s="17" t="s">
+        <v>84</v>
+      </c>
+      <c r="G10" s="21"/>
+      <c r="H10" s="20" t="s">
+        <v>85</v>
+      </c>
+      <c r="U10" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="11" ht="14.25">
+      <c r="C11" s="17" t="s">
+        <v>87</v>
+      </c>
+      <c r="D11" s="17" t="s">
+        <v>88</v>
+      </c>
+      <c r="E11" s="17" t="s">
+        <v>89</v>
+      </c>
+      <c r="F11" s="17" t="s">
+        <v>90</v>
+      </c>
+      <c r="G11" s="21"/>
+      <c r="H11" s="20" t="s">
+        <v>91</v>
+      </c>
+      <c r="I11" t="s">
+        <v>92</v>
+      </c>
+      <c r="J11" s="22" t="s">
+        <v>93</v>
+      </c>
+      <c r="K11" t="s">
+        <v>94</v>
+      </c>
+      <c r="L11" t="s">
+        <v>95</v>
+      </c>
+      <c r="U11" s="15" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="12" ht="14.25">
+      <c r="B12" t="s">
+        <v>97</v>
+      </c>
+      <c r="C12" s="18" t="s">
+        <v>98</v>
+      </c>
+      <c r="D12" s="17" t="s">
+        <v>99</v>
+      </c>
+      <c r="E12" s="17" t="s">
+        <v>100</v>
+      </c>
+      <c r="F12" s="17" t="s">
+        <v>101</v>
+      </c>
+      <c r="G12" s="21"/>
+      <c r="H12" s="20" t="s">
+        <v>102</v>
+      </c>
+      <c r="I12" t="s">
+        <v>103</v>
+      </c>
+      <c r="J12" t="s">
+        <v>104</v>
+      </c>
+      <c r="K12" t="s">
+        <v>105</v>
+      </c>
+      <c r="L12" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="13" ht="14.25">
+      <c r="B13" t="s">
+        <v>107</v>
+      </c>
+      <c r="C13" s="18" t="s">
+        <v>108</v>
+      </c>
+      <c r="D13" s="17" t="s">
+        <v>109</v>
+      </c>
+      <c r="E13" s="17" t="s">
+        <v>110</v>
+      </c>
+      <c r="F13" s="17" t="s">
+        <v>111</v>
+      </c>
+      <c r="G13" s="21"/>
+      <c r="H13" s="20" t="s">
+        <v>112</v>
+      </c>
+      <c r="I13" t="s">
+        <v>113</v>
+      </c>
+      <c r="J13" t="s">
+        <v>114</v>
+      </c>
+      <c r="K13" t="s">
+        <v>115</v>
+      </c>
+      <c r="L13" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="14" ht="14.25">
+      <c r="C14" s="18"/>
+      <c r="D14" s="18" t="s">
+        <v>117</v>
+      </c>
+      <c r="E14" s="18" t="s">
+        <v>118</v>
+      </c>
+      <c r="F14" s="17" t="s">
+        <v>119</v>
+      </c>
+      <c r="G14" s="21"/>
+      <c r="H14" s="20" t="s">
+        <v>120</v>
+      </c>
+      <c r="I14" t="s">
+        <v>121</v>
+      </c>
+      <c r="J14" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="17" ht="14.25">
+      <c r="O17" s="20"/>
+    </row>
+    <row r="18" ht="14.25">
+      <c r="B18" t="s">
+        <v>123</v>
+      </c>
+      <c r="D18" s="18" t="s">
+        <v>69</v>
+      </c>
+      <c r="E18" t="s">
+        <v>124</v>
+      </c>
+      <c r="F18" s="18" t="s">
+        <v>71</v>
+      </c>
+      <c r="G18" s="23" t="s">
+        <v>125</v>
+      </c>
+      <c r="H18" s="20" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="19" ht="14.25">
+      <c r="B19" t="s">
+        <v>123</v>
+      </c>
+      <c r="D19" s="18" t="s">
+        <v>76</v>
+      </c>
+      <c r="E19" s="13" t="s">
+        <v>70</v>
+      </c>
+      <c r="F19" s="18" t="s">
+        <v>78</v>
+      </c>
+      <c r="G19" s="24"/>
+      <c r="H19" s="20" t="s">
+        <v>79</v>
+      </c>
+      <c r="U19" s="13" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="20" ht="14.25">
+      <c r="B20" t="s">
+        <v>127</v>
+      </c>
+      <c r="D20" s="18" t="s">
+        <v>82</v>
+      </c>
+      <c r="E20" s="13" t="s">
+        <v>77</v>
+      </c>
+      <c r="F20" s="18" t="s">
+        <v>84</v>
+      </c>
+      <c r="G20" s="24"/>
+      <c r="H20" s="20" t="s">
+        <v>85</v>
+      </c>
+      <c r="U20" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="21" ht="14.25">
+      <c r="B21" t="s">
+        <v>129</v>
+      </c>
+      <c r="E21" t="s">
+        <v>130</v>
+      </c>
+      <c r="F21" s="18" t="s">
+        <v>90</v>
+      </c>
+      <c r="G21" s="24"/>
+      <c r="H21" s="20" t="s">
+        <v>91</v>
+      </c>
+      <c r="I21" t="s">
+        <v>131</v>
+      </c>
+      <c r="K21" t="s">
+        <v>94</v>
+      </c>
+      <c r="L21" t="s">
+        <v>132</v>
+      </c>
+      <c r="U21" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="22" ht="14.25">
+      <c r="B22" t="s">
+        <v>134</v>
+      </c>
+      <c r="C22" s="18" t="s">
+        <v>98</v>
+      </c>
+      <c r="E22" t="s">
+        <v>135</v>
+      </c>
+      <c r="F22" s="18" t="s">
+        <v>101</v>
+      </c>
+      <c r="G22" s="24"/>
+      <c r="H22" s="20" t="s">
+        <v>102</v>
+      </c>
+      <c r="I22" t="s">
+        <v>136</v>
+      </c>
+      <c r="K22" t="s">
+        <v>105</v>
+      </c>
+      <c r="L22" t="s">
+        <v>137</v>
+      </c>
+      <c r="U22" s="15" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="23" ht="14.25">
+      <c r="B23" t="s">
+        <v>139</v>
+      </c>
+      <c r="C23" s="18" t="s">
+        <v>108</v>
+      </c>
+      <c r="E23" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="F23" s="18" t="s">
+        <v>111</v>
+      </c>
+      <c r="G23" s="24"/>
+      <c r="H23" s="20" t="s">
+        <v>112</v>
+      </c>
+      <c r="I23" t="s">
+        <v>141</v>
+      </c>
+      <c r="K23" t="s">
+        <v>115</v>
+      </c>
+      <c r="L23" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="24" ht="14.25">
+      <c r="D24" t="s">
+        <v>117</v>
+      </c>
+      <c r="E24" t="s">
+        <v>143</v>
+      </c>
+      <c r="F24" s="18" t="s">
+        <v>119</v>
+      </c>
+      <c r="G24" s="24"/>
+      <c r="H24" s="20" t="s">
+        <v>120</v>
+      </c>
+      <c r="I24" t="s">
+        <v>144</v>
+      </c>
+      <c r="J24" t="s">
+        <v>122</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="G8:G14"/>
+    <mergeCell ref="G18:G24"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink r:id="rId1" ref="U11"/>
+    <hyperlink r:id="rId2" ref="U22"/>
+  </hyperlinks>
+  <printOptions headings="0" gridLines="0"/>
+  <pageMargins left="0.70078740157480324" right="0.70078740157480324" top="0.75196850393700787" bottom="0.75196850393700787" header="0.29999999999999999" footer="0.29999999999999999"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
+  <headerFooter/>
+  <drawing r:id="rId3"/>
+</worksheet>
 </file>
--- a/Hardware/Matériel.xlsx
+++ b/Hardware/Matériel.xlsx
@@ -522,7 +522,7 @@
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf fontId="0" fillId="2" borderId="0" numFmtId="44" applyNumberFormat="1" applyFont="0" applyFill="0" applyBorder="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="20">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
     <xf fontId="1" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -562,25 +562,10 @@
       <alignment horizontal="right"/>
     </xf>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" textRotation="180" vertical="center"/>
     </xf>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" textRotation="180" vertical="center"/>
-    </xf>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" textRotation="180" vertical="center"/>
-    </xf>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" textRotation="180" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -607,7 +592,7 @@
       <xdr:col>12</xdr:col>
       <xdr:colOff>563942</xdr:colOff>
       <xdr:row>5</xdr:row>
-      <xdr:rowOff>78581</xdr:rowOff>
+      <xdr:rowOff>78580</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="3962752" cy="1844035"/>
     <xdr:pic>
@@ -645,7 +630,7 @@
       <xdr:col>20</xdr:col>
       <xdr:colOff>8905</xdr:colOff>
       <xdr:row>24</xdr:row>
-      <xdr:rowOff>181575</xdr:rowOff>
+      <xdr:rowOff>181574</xdr:rowOff>
     </xdr:to>
     <xdr:grpSp>
       <xdr:nvGrpSpPr>
@@ -1394,7 +1379,7 @@
         <v>1</v>
       </c>
       <c r="H10" s="8">
-        <f t="shared" ref="H10:H23" si="1">G10*F10</f>
+        <f t="shared" ref="H10:H24" si="1">G10*F10</f>
         <v>0.40999999999999998</v>
       </c>
     </row>
@@ -1730,7 +1715,7 @@
         <v>1</v>
       </c>
       <c r="H24" s="8">
-        <f>G24*F24</f>
+        <f t="shared" si="1"/>
         <v>2.0600000000000001</v>
       </c>
     </row>
@@ -1856,19 +1841,19 @@
       <c r="C8" s="17" t="s">
         <v>68</v>
       </c>
-      <c r="D8" s="18" t="s">
+      <c r="D8" s="17" t="s">
         <v>69</v>
       </c>
-      <c r="E8" s="18" t="s">
+      <c r="E8" s="17" t="s">
         <v>70</v>
       </c>
-      <c r="F8" s="18" t="s">
+      <c r="F8" s="17" t="s">
         <v>71</v>
       </c>
-      <c r="G8" s="19" t="s">
+      <c r="G8" s="18" t="s">
         <v>72</v>
       </c>
-      <c r="H8" s="20" t="s">
+      <c r="H8" s="19" t="s">
         <v>73</v>
       </c>
       <c r="U8" t="s">
@@ -1885,11 +1870,11 @@
       <c r="E9" s="17" t="s">
         <v>77</v>
       </c>
-      <c r="F9" s="18" t="s">
+      <c r="F9" s="17" t="s">
         <v>78</v>
       </c>
-      <c r="G9" s="21"/>
-      <c r="H9" s="20" t="s">
+      <c r="G9" s="18"/>
+      <c r="H9" s="19" t="s">
         <v>79</v>
       </c>
       <c r="U9" t="s">
@@ -1909,8 +1894,8 @@
       <c r="F10" s="17" t="s">
         <v>84</v>
       </c>
-      <c r="G10" s="21"/>
-      <c r="H10" s="20" t="s">
+      <c r="G10" s="18"/>
+      <c r="H10" s="19" t="s">
         <v>85</v>
       </c>
       <c r="U10" t="s">
@@ -1930,14 +1915,14 @@
       <c r="F11" s="17" t="s">
         <v>90</v>
       </c>
-      <c r="G11" s="21"/>
-      <c r="H11" s="20" t="s">
+      <c r="G11" s="18"/>
+      <c r="H11" s="19" t="s">
         <v>91</v>
       </c>
       <c r="I11" t="s">
         <v>92</v>
       </c>
-      <c r="J11" s="22" t="s">
+      <c r="J11" s="19" t="s">
         <v>93</v>
       </c>
       <c r="K11" t="s">
@@ -1954,7 +1939,7 @@
       <c r="B12" t="s">
         <v>97</v>
       </c>
-      <c r="C12" s="18" t="s">
+      <c r="C12" s="17" t="s">
         <v>98</v>
       </c>
       <c r="D12" s="17" t="s">
@@ -1966,8 +1951,8 @@
       <c r="F12" s="17" t="s">
         <v>101</v>
       </c>
-      <c r="G12" s="21"/>
-      <c r="H12" s="20" t="s">
+      <c r="G12" s="18"/>
+      <c r="H12" s="19" t="s">
         <v>102</v>
       </c>
       <c r="I12" t="s">
@@ -1987,7 +1972,7 @@
       <c r="B13" t="s">
         <v>107</v>
       </c>
-      <c r="C13" s="18" t="s">
+      <c r="C13" s="17" t="s">
         <v>108</v>
       </c>
       <c r="D13" s="17" t="s">
@@ -1999,8 +1984,8 @@
       <c r="F13" s="17" t="s">
         <v>111</v>
       </c>
-      <c r="G13" s="21"/>
-      <c r="H13" s="20" t="s">
+      <c r="G13" s="18"/>
+      <c r="H13" s="19" t="s">
         <v>112</v>
       </c>
       <c r="I13" t="s">
@@ -2017,18 +2002,18 @@
       </c>
     </row>
     <row r="14" ht="14.25">
-      <c r="C14" s="18"/>
-      <c r="D14" s="18" t="s">
+      <c r="C14" s="17"/>
+      <c r="D14" s="17" t="s">
         <v>117</v>
       </c>
-      <c r="E14" s="18" t="s">
+      <c r="E14" s="17" t="s">
         <v>118</v>
       </c>
       <c r="F14" s="17" t="s">
         <v>119</v>
       </c>
-      <c r="G14" s="21"/>
-      <c r="H14" s="20" t="s">
+      <c r="G14" s="18"/>
+      <c r="H14" s="19" t="s">
         <v>120</v>
       </c>
       <c r="I14" t="s">
@@ -2039,25 +2024,25 @@
       </c>
     </row>
     <row r="17" ht="14.25">
-      <c r="O17" s="20"/>
+      <c r="O17" s="19"/>
     </row>
     <row r="18" ht="14.25">
       <c r="B18" t="s">
         <v>123</v>
       </c>
-      <c r="D18" s="18" t="s">
+      <c r="D18" s="17" t="s">
         <v>69</v>
       </c>
       <c r="E18" t="s">
         <v>124</v>
       </c>
-      <c r="F18" s="18" t="s">
+      <c r="F18" s="17" t="s">
         <v>71</v>
       </c>
-      <c r="G18" s="23" t="s">
+      <c r="G18" s="18" t="s">
         <v>125</v>
       </c>
-      <c r="H18" s="20" t="s">
+      <c r="H18" s="19" t="s">
         <v>73</v>
       </c>
     </row>
@@ -2065,17 +2050,17 @@
       <c r="B19" t="s">
         <v>123</v>
       </c>
-      <c r="D19" s="18" t="s">
+      <c r="D19" s="17" t="s">
         <v>76</v>
       </c>
       <c r="E19" s="13" t="s">
         <v>70</v>
       </c>
-      <c r="F19" s="18" t="s">
+      <c r="F19" s="17" t="s">
         <v>78</v>
       </c>
-      <c r="G19" s="24"/>
-      <c r="H19" s="20" t="s">
+      <c r="G19" s="18"/>
+      <c r="H19" s="19" t="s">
         <v>79</v>
       </c>
       <c r="U19" s="13" t="s">
@@ -2086,17 +2071,17 @@
       <c r="B20" t="s">
         <v>127</v>
       </c>
-      <c r="D20" s="18" t="s">
+      <c r="D20" s="17" t="s">
         <v>82</v>
       </c>
       <c r="E20" s="13" t="s">
         <v>77</v>
       </c>
-      <c r="F20" s="18" t="s">
+      <c r="F20" s="17" t="s">
         <v>84</v>
       </c>
-      <c r="G20" s="24"/>
-      <c r="H20" s="20" t="s">
+      <c r="G20" s="18"/>
+      <c r="H20" s="19" t="s">
         <v>85</v>
       </c>
       <c r="U20" t="s">
@@ -2110,11 +2095,11 @@
       <c r="E21" t="s">
         <v>130</v>
       </c>
-      <c r="F21" s="18" t="s">
+      <c r="F21" s="17" t="s">
         <v>90</v>
       </c>
-      <c r="G21" s="24"/>
-      <c r="H21" s="20" t="s">
+      <c r="G21" s="18"/>
+      <c r="H21" s="19" t="s">
         <v>91</v>
       </c>
       <c r="I21" t="s">
@@ -2134,17 +2119,17 @@
       <c r="B22" t="s">
         <v>134</v>
       </c>
-      <c r="C22" s="18" t="s">
+      <c r="C22" s="17" t="s">
         <v>98</v>
       </c>
       <c r="E22" t="s">
         <v>135</v>
       </c>
-      <c r="F22" s="18" t="s">
+      <c r="F22" s="17" t="s">
         <v>101</v>
       </c>
-      <c r="G22" s="24"/>
-      <c r="H22" s="20" t="s">
+      <c r="G22" s="18"/>
+      <c r="H22" s="19" t="s">
         <v>102</v>
       </c>
       <c r="I22" t="s">
@@ -2164,17 +2149,17 @@
       <c r="B23" t="s">
         <v>139</v>
       </c>
-      <c r="C23" s="18" t="s">
+      <c r="C23" s="17" t="s">
         <v>108</v>
       </c>
       <c r="E23" s="13" t="s">
         <v>140</v>
       </c>
-      <c r="F23" s="18" t="s">
+      <c r="F23" s="17" t="s">
         <v>111</v>
       </c>
-      <c r="G23" s="24"/>
-      <c r="H23" s="20" t="s">
+      <c r="G23" s="18"/>
+      <c r="H23" s="19" t="s">
         <v>112</v>
       </c>
       <c r="I23" t="s">
@@ -2194,11 +2179,11 @@
       <c r="E24" t="s">
         <v>143</v>
       </c>
-      <c r="F24" s="18" t="s">
+      <c r="F24" s="17" t="s">
         <v>119</v>
       </c>
-      <c r="G24" s="24"/>
-      <c r="H24" s="20" t="s">
+      <c r="G24" s="18"/>
+      <c r="H24" s="19" t="s">
         <v>120</v>
       </c>
       <c r="I24" t="s">

--- a/Hardware/Matériel.xlsx
+++ b/Hardware/Matériel.xlsx
@@ -12,9 +12,6 @@
     <sheet name="XIAO ESP32" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <calcPr/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{D0CA8CA8-9F24-4464-BF8E-62219DCF47F9}"/>
-  </extLst>
 </workbook>
 </file>
 
@@ -1421,7 +1418,7 @@
         <v>10</v>
       </c>
       <c r="F12" s="7">
-        <v>8.0000000000000002e-002</v>
+        <v>0.080000000000000002</v>
       </c>
       <c r="G12" s="2">
         <v>2</v>
@@ -1445,14 +1442,14 @@
         <v>10</v>
       </c>
       <c r="F13" s="7">
-        <v>8.0000000000000002e-002</v>
+        <v>0.080000000000000002</v>
       </c>
       <c r="G13" s="2">
         <v>1</v>
       </c>
       <c r="H13" s="8">
         <f t="shared" si="1"/>
-        <v>8.0000000000000002e-002</v>
+        <v>0.080000000000000002</v>
       </c>
     </row>
     <row r="14" ht="14.25">
@@ -1469,7 +1466,7 @@
         <v>10</v>
       </c>
       <c r="F14" s="7">
-        <v>8.0000000000000002e-002</v>
+        <v>0.080000000000000002</v>
       </c>
       <c r="G14" s="2">
         <v>2</v>

--- a/Hardware/Matériel.xlsx
+++ b/Hardware/Matériel.xlsx
@@ -3,25 +3,33 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="0"/>
+    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Liste de matériels (prototype)" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Commandes" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="BOM" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="XIAO ESP32" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="XIAO ESP32" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <calcPr/>
+  <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{D0CA8CA8-9F24-4464-BF8E-62219DCF47F9}"/>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="145">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="183">
+  <si>
+    <t>Reference</t>
+  </si>
   <si>
     <t>Nom</t>
   </si>
   <si>
-    <t>Ref</t>
+    <t>Valeur</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ref fab.</t>
   </si>
   <si>
     <t>datasheet</t>
@@ -39,52 +47,277 @@
     <t>somme</t>
   </si>
   <si>
+    <t>C1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Condensateur électrolytique</t>
+  </si>
+  <si>
+    <t>470µF</t>
+  </si>
+  <si>
+    <t>REF1020471M050K</t>
+  </si>
+  <si>
+    <t xml:space="preserve">./Datasheets/Condensateur  470 uF elec - ref-series.pdf</t>
+  </si>
+  <si>
+    <t>Mouser</t>
+  </si>
+  <si>
+    <t>C2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Condensateur ceram</t>
+  </si>
+  <si>
+    <t>4.7μF</t>
+  </si>
+  <si>
+    <t>GRM319R61H475KA12D</t>
+  </si>
+  <si>
+    <t xml:space="preserve">./Datasheets/Condensateur  4,7 uF ceram - GRM319R61H475KA12_01A.pdf</t>
+  </si>
+  <si>
+    <t>C3</t>
+  </si>
+  <si>
+    <t>10µF</t>
+  </si>
+  <si>
+    <t>CL31A106MBHNNNE</t>
+  </si>
+  <si>
+    <t>./Datasheets/DataSheet_CL31A106MBHNNN_20260505.pdf</t>
+  </si>
+  <si>
+    <t>C4</t>
+  </si>
+  <si>
+    <t>22µF</t>
+  </si>
+  <si>
+    <t>RDEC71H226MWK1H03B</t>
+  </si>
+  <si>
+    <t xml:space="preserve">./Datasheets/Condensateur  22 uF ceram - GRM188R61A226ME15-02A.pdf</t>
+  </si>
+  <si>
+    <t>D1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Diode Schottky</t>
+  </si>
+  <si>
+    <t>BX36_R1</t>
+  </si>
+  <si>
+    <t>BX36_R1_00001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">./Datasheets/Diode - BX36_R1_00001.pdf</t>
+  </si>
+  <si>
+    <t>D2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">diode TVS</t>
+  </si>
+  <si>
+    <t>SMAJ28A</t>
+  </si>
+  <si>
+    <t>SMAJ28A/TR13</t>
+  </si>
+  <si>
+    <t>./Datasheets/SMAJ_1.pdf</t>
+  </si>
+  <si>
+    <t>E1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Écran OLED</t>
+  </si>
+  <si>
+    <t>DM-OLED096-636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DST-015 (OLED SSD1305)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E2, E3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LED (ambre)</t>
+  </si>
+  <si>
+    <t>LED</t>
+  </si>
+  <si>
+    <t>LTST-C150AKT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">./Datasheets/AmberLed - LTST-C150AKT.pdf</t>
+  </si>
+  <si>
+    <t>F1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fusible réarmable</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PTC 1A</t>
+  </si>
+  <si>
+    <t>MF-R050</t>
+  </si>
+  <si>
+    <t>./Datasheets/PTC.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">J1, J2</t>
+  </si>
+  <si>
+    <t>Bornier</t>
+  </si>
+  <si>
+    <t>TB0011-350-04GR</t>
+  </si>
+  <si>
+    <t>./Datasheets/TB0011-350-04GR.pdf</t>
+  </si>
+  <si>
+    <t>L1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">inductance torique</t>
+  </si>
+  <si>
+    <t xml:space="preserve">300 µH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">./Datasheets/induct - 7447060.pdf</t>
+  </si>
+  <si>
+    <t>L2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">inductance de mode commun</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5 mH</t>
+  </si>
+  <si>
+    <t>SS11VL-11050</t>
+  </si>
+  <si>
+    <t xml:space="preserve">./Datasheets/induct - SS11VL_11050.pdf</t>
+  </si>
+  <si>
+    <t>PS1</t>
+  </si>
+  <si>
+    <t>Alimentation</t>
+  </si>
+  <si>
+    <t>TSR_1-2433E</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TSR 1-2433E</t>
+  </si>
+  <si>
+    <t xml:space="preserve">./Datasheets/TSR 1-2433E - tsr1e_datasheet.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R1, R5</t>
+  </si>
+  <si>
+    <t>Résistance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">68 R</t>
+  </si>
+  <si>
+    <t>AC1206JR-0768RL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">./Datasheets/68R - PYU_AC_51_ROHS_L.pdf</t>
+  </si>
+  <si>
+    <t>R2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">120 R</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> RC1206JR-07120RL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">./Datasheets/120R - YAGEO_PYu_RC_Group_51_RoHS_L_12.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R3, R4</t>
+  </si>
+  <si>
+    <t>4k7</t>
+  </si>
+  <si>
+    <t>RC1206JR-104K7L</t>
+  </si>
+  <si>
+    <t>S1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Switch horizontal</t>
+  </si>
+  <si>
+    <t>SLW-874744</t>
+  </si>
+  <si>
+    <t>SLW-874744-6A-RA-N-D</t>
+  </si>
+  <si>
+    <t>./Datasheets/slw_874744_6a_ra_n_d.pdf</t>
+  </si>
+  <si>
+    <t>U1</t>
+  </si>
+  <si>
     <t>ESP32</t>
   </si>
   <si>
+    <t>XIAO-ESP32-C6-DIP</t>
+  </si>
+  <si>
     <t>XIAO-ESP32-S3</t>
   </si>
   <si>
     <t>./Datasheets/esp32-s3.pdf</t>
   </si>
   <si>
-    <t>Mouser</t>
+    <t>U2</t>
   </si>
   <si>
     <t xml:space="preserve">Module RFID</t>
   </si>
   <si>
+    <t>RFID-RC522</t>
+  </si>
+  <si>
     <t xml:space="preserve">Module SBC-RFID-RC522</t>
   </si>
   <si>
     <t>Inconnu</t>
   </si>
   <si>
-    <t>Alimentation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TSR 1-2433E</t>
-  </si>
-  <si>
-    <t xml:space="preserve">./Datasheets/TSR 1-2433E - tsr1e_datasheet.pdf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Écran OLED</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DST-015 (OLED SSD1305)</t>
-  </si>
-  <si>
-    <t>Bornier</t>
-  </si>
-  <si>
-    <t>TB0011-350-04GR</t>
-  </si>
-  <si>
-    <t>./Datasheets/TB0011-350-04GR.pdf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">transceiver UART &lt;-&gt; RS485</t>
+    <t>U3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">transceiver UART</t>
+  </si>
+  <si>
+    <t>MAX3485CSA_T</t>
   </si>
   <si>
     <t>MAX3485CSA+T</t>
@@ -93,132 +326,21 @@
     <t>./Datasheets/MAX3483_MAX3491.pdf</t>
   </si>
   <si>
-    <t xml:space="preserve">Switch horizontal</t>
-  </si>
-  <si>
-    <t>SLW-874744-6A-RA-N-D</t>
-  </si>
-  <si>
-    <t>./Datasheets/slw_874744_6a_ra_n_d.pdf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LED (ambre)</t>
-  </si>
-  <si>
-    <t>LTST-C150AKT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">./Datasheets/AmberLed - LTST-C150AKT.pdf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Résistance 68R</t>
-  </si>
-  <si>
-    <t>AC1206JR-0768RL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">./Datasheets/68R - PYU_AC_51_ROHS_L.pdf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Résistance 120R</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> RC1206JR-07120RL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">./Datasheets/120R - YAGEO_PYu_RC_Group_51_RoHS_L_12.pdf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Résistance 4k7</t>
-  </si>
-  <si>
-    <t>RC1206JR-104K7L</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Condensateur  10 uF ceram</t>
-  </si>
-  <si>
-    <t>CL31A106MBHNNNE</t>
-  </si>
-  <si>
-    <t>./Datasheets/DataSheet_CL31A106MBHNNN_20260505.pdf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Condensateur  4,7 uF ceram</t>
-  </si>
-  <si>
-    <t>GRM319R61H475KA12D</t>
-  </si>
-  <si>
-    <t xml:space="preserve">./Datasheets/Condensateur  4,7 uF ceram - GRM319R61H475KA12_01A.pdf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Condensateur  22 uF ceram</t>
-  </si>
-  <si>
-    <t>RDEC71H226MWK1H03B</t>
-  </si>
-  <si>
-    <t xml:space="preserve">./Datasheets/Condensateur  22 uF ceram - GRM188R61A226ME15-02A.pdf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Condensateur  470 uF elec</t>
-  </si>
-  <si>
-    <t>REF1020471M050K</t>
-  </si>
-  <si>
-    <t xml:space="preserve">./Datasheets/Condensateur  470 uF elec - ref-series.pdf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fusible réarmable PTC</t>
-  </si>
-  <si>
-    <t>MF-R050</t>
-  </si>
-  <si>
-    <t>./Datasheets/PTC.pdf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">diode TVS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">./Datasheets/diode TVS - 824500281.pdf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Diode Schottky</t>
-  </si>
-  <si>
-    <t>BX36_R1_00001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">./Datasheets/Diode - BX36_R1_00001.pdf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">inductance de mode commun</t>
-  </si>
-  <si>
-    <t>SS11VL-11050</t>
-  </si>
-  <si>
-    <t xml:space="preserve">./Datasheets/induct - SS11VL_11050.pdf</t>
+    <t>RV1</t>
   </si>
   <si>
     <t>Varistance</t>
   </si>
   <si>
+    <t>20D470K</t>
+  </si>
+  <si>
     <t>MOV-20D470K</t>
   </si>
   <si>
     <t xml:space="preserve">./Datasheets/Varistance - mov20d.pdf</t>
   </si>
   <si>
-    <t xml:space="preserve">inductance torique</t>
-  </si>
-  <si>
-    <t xml:space="preserve">./Datasheets/induct - 7447060.pdf</t>
-  </si>
-  <si>
     <t>total</t>
   </si>
   <si>
@@ -252,9 +374,6 @@
     <t>GPIO2</t>
   </si>
   <si>
-    <t>D1</t>
-  </si>
-  <si>
     <t>GND</t>
   </si>
   <si>
@@ -268,9 +387,6 @@
   </si>
   <si>
     <t>GPIO3</t>
-  </si>
-  <si>
-    <t>D2</t>
   </si>
   <si>
     <t>3V3</t>
@@ -484,15 +600,15 @@
       <name val="Calibri"/>
     </font>
     <font>
-      <sz val="10.000000"/>
-      <name val="Calibri"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <u/>
       <sz val="11.000000"/>
       <color theme="10"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10.000000"/>
+      <name val="Calibri"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -519,8 +635,11 @@
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf fontId="0" fillId="2" borderId="0" numFmtId="44" applyNumberFormat="1" applyFont="0" applyFill="0" applyBorder="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="21">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0">
+      <protection hidden="0" locked="1"/>
+    </xf>
     <xf fontId="1" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -539,21 +658,21 @@
     <xf fontId="1" fillId="0" borderId="0" numFmtId="164" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf fontId="4" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="164" xfId="0" applyNumberFormat="1"/>
-    <xf fontId="2" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf fontId="1" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1">
       <protection hidden="0" locked="1"/>
     </xf>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0">
+      <protection hidden="0" locked="1"/>
+    </xf>
+    <xf fontId="4" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf fontId="4" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
     <xf fontId="5" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+      <alignment horizontal="center"/>
     </xf>
-    <xf fontId="5" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1"/>
     <xf fontId="1" fillId="0" borderId="0" numFmtId="164" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -1179,25 +1298,27 @@
   </sheetPr>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col bestFit="1" customWidth="1" min="2" max="2" width="24.29296875"/>
-    <col bestFit="1" customWidth="1" min="3" max="3" width="20.03125"/>
-    <col bestFit="1" customWidth="1" min="4" max="4" width="59.4140625"/>
-    <col bestFit="1" customWidth="1" min="5" max="5" width="9.75390625"/>
-    <col bestFit="1" customWidth="1" min="6" max="6" width="11.62109375"/>
-    <col bestFit="1" min="7" max="7" width="6.94140625"/>
-    <col bestFit="1" customWidth="1" min="8" max="8" width="11.62109375"/>
-    <col bestFit="1" min="10" max="10" width="11.69140625"/>
-    <col bestFit="1" min="11" max="11" width="10.6328125"/>
+    <col bestFit="1" customWidth="1" min="2" max="2" width="9.44140625"/>
+    <col bestFit="1" customWidth="1" min="3" max="3" width="24.29296875"/>
+    <col customWidth="1" min="4" max="4" width="24.29296875"/>
+    <col bestFit="1" customWidth="1" min="5" max="5" width="20.03125"/>
+    <col bestFit="1" customWidth="1" min="6" max="6" width="59.4140625"/>
+    <col bestFit="1" customWidth="1" min="7" max="7" width="9.75390625"/>
+    <col customWidth="1" min="8" max="8" width="9.28125"/>
+    <col bestFit="1" min="9" max="9" width="6.94140625"/>
+    <col customWidth="1" min="10" max="10" width="10.57421875"/>
+    <col bestFit="1" min="12" max="12" width="11.69140625"/>
+    <col bestFit="1" min="13" max="13" width="10.6328125"/>
   </cols>
   <sheetData>
     <row r="3" ht="14.25">
       <c r="B3" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C3" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="D3" s="2" t="s">
         <v>2</v>
       </c>
       <c r="E3" s="2" t="s">
@@ -1206,573 +1327,746 @@
       <c r="F3" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="G3" s="3" t="s">
         <v>5</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>6</v>
       </c>
+      <c r="I3" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="J3" s="4" t="s">
+        <v>8</v>
+      </c>
     </row>
     <row r="4" ht="14.25">
-      <c r="B4" s="4" t="s">
-        <v>7</v>
+      <c r="B4" s="1" t="s">
+        <v>9</v>
       </c>
       <c r="C4" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="F4" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G4" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="H4" s="8">
+        <v>0.56999999999999995</v>
+      </c>
+      <c r="I4" s="3">
+        <v>1</v>
+      </c>
+      <c r="J4" s="9">
+        <f>I4*H4</f>
+        <v>0.56999999999999995</v>
+      </c>
+    </row>
+    <row r="5" ht="14.25">
+      <c r="B5" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E5" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F5" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="G5" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="H5" s="8">
+        <v>0.17999999999999999</v>
+      </c>
+      <c r="I5" s="3">
+        <v>1</v>
+      </c>
+      <c r="J5" s="9">
+        <f>I5*H5</f>
+        <v>0.17999999999999999</v>
+      </c>
+      <c r="M5" s="10"/>
+      <c r="N5"/>
+      <c r="O5"/>
+      <c r="P5"/>
+      <c r="Q5"/>
+    </row>
+    <row r="6" ht="14.25">
+      <c r="B6" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E6" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="F6" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="G6" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="H6" s="8">
+        <v>0.20999999999999999</v>
+      </c>
+      <c r="I6" s="3">
+        <v>1</v>
+      </c>
+      <c r="J6" s="9">
+        <f>I6*H6</f>
+        <v>0.20999999999999999</v>
+      </c>
+      <c r="L6" s="10"/>
+      <c r="P6" s="1"/>
+      <c r="Q6" s="1"/>
+    </row>
+    <row r="7" ht="14.25">
+      <c r="B7" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E7" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="F7" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="G7" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="H7" s="8">
+        <v>1.3100000000000001</v>
+      </c>
+      <c r="I7" s="3">
+        <v>1</v>
+      </c>
+      <c r="J7" s="9">
+        <f>I7*H7</f>
+        <v>1.3100000000000001</v>
+      </c>
+      <c r="L7" s="10"/>
+      <c r="P7" s="1"/>
+      <c r="Q7" s="1"/>
+    </row>
+    <row r="8" ht="14.25">
+      <c r="B8" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C8" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E8" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="F8" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="G8" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="H8" s="8">
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="I8" s="3">
+        <v>1</v>
+      </c>
+      <c r="J8" s="9">
+        <f>I8*H8</f>
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="P8" s="1"/>
+      <c r="Q8" s="1"/>
+    </row>
+    <row r="9" ht="14.25">
+      <c r="B9" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="D9" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="E9" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="F9" s="14" t="s">
+        <v>37</v>
+      </c>
+      <c r="G9" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="H9" s="8">
+        <v>0.11</v>
+      </c>
+      <c r="I9" s="3">
+        <v>1</v>
+      </c>
+      <c r="J9" s="9">
+        <f>I9*H9</f>
+        <v>0.11</v>
+      </c>
+      <c r="P9" s="1"/>
+      <c r="Q9" s="1"/>
+    </row>
+    <row r="10" ht="14.25">
+      <c r="B10" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="E10" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="F10" s="6"/>
+      <c r="G10" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="H10" s="8">
+        <v>5.3600000000000003</v>
+      </c>
+      <c r="I10" s="3">
+        <v>1</v>
+      </c>
+      <c r="J10" s="9">
+        <f>I10*H10</f>
+        <v>5.3600000000000003</v>
+      </c>
+      <c r="P10" s="1"/>
+      <c r="Q10" s="1"/>
+    </row>
+    <row r="11" ht="14.25">
+      <c r="B11" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E11" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="F11" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="G11" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="H11" s="8">
+        <v>0.11</v>
+      </c>
+      <c r="I11" s="3">
+        <v>2</v>
+      </c>
+      <c r="J11" s="9">
+        <f>I11*H11</f>
+        <v>0.22</v>
+      </c>
+      <c r="P11" s="1"/>
+      <c r="Q11" s="1"/>
+    </row>
+    <row r="12" ht="14.25">
+      <c r="B12" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="E12" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="F12" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="G12" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="H12" s="8">
+        <v>0.32000000000000001</v>
+      </c>
+      <c r="I12" s="3">
+        <v>1</v>
+      </c>
+      <c r="J12" s="9">
+        <f>I12*H12</f>
+        <v>0.32000000000000001</v>
+      </c>
+      <c r="P12" s="1"/>
+      <c r="Q12" s="1"/>
+    </row>
+    <row r="13" ht="14.25">
+      <c r="B13" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="E13" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="F13" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="G13" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="H13" s="8">
+        <v>0.70999999999999996</v>
+      </c>
+      <c r="I13" s="3">
+        <v>2</v>
+      </c>
+      <c r="J13" s="9">
+        <f>I13*H13</f>
+        <v>1.4199999999999999</v>
+      </c>
+      <c r="P13" s="1"/>
+      <c r="Q13" s="1"/>
+    </row>
+    <row r="14" ht="14.25">
+      <c r="B14" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C14" s="15" t="s">
+        <v>57</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E14" s="13">
+        <v>7447060</v>
+      </c>
+      <c r="F14" s="14" t="s">
+        <v>59</v>
+      </c>
+      <c r="G14" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="H14" s="8">
+        <v>2.0600000000000001</v>
+      </c>
+      <c r="I14" s="3">
+        <v>1</v>
+      </c>
+      <c r="J14" s="9">
+        <f>I14*H14</f>
+        <v>2.0600000000000001</v>
+      </c>
+      <c r="P14" s="1"/>
+      <c r="Q14" s="1"/>
+    </row>
+    <row r="15" ht="14.25">
+      <c r="B15" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="E15" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="F15" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="G15" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="H15" s="8">
+        <v>1.49</v>
+      </c>
+      <c r="I15" s="3">
+        <v>1</v>
+      </c>
+      <c r="J15" s="9">
+        <f>I15*H15</f>
+        <v>1.49</v>
+      </c>
+      <c r="P15" s="1"/>
+      <c r="Q15" s="1"/>
+    </row>
+    <row r="16" ht="14.25">
+      <c r="B16" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="E16" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="F16" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="G16" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="H16" s="8">
+        <v>2.9199999999999999</v>
+      </c>
+      <c r="I16" s="3">
+        <v>1</v>
+      </c>
+      <c r="J16" s="9">
+        <f>I16*H16</f>
+        <v>2.9199999999999999</v>
+      </c>
+      <c r="P16" s="1"/>
+      <c r="Q16" s="1"/>
+    </row>
+    <row r="17" ht="14.25">
+      <c r="B17" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="C17" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="E17" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="F17" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="G17" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="H17" s="8">
+        <v>8.0000000000000002e-002</v>
+      </c>
+      <c r="I17" s="3">
+        <v>2</v>
+      </c>
+      <c r="J17" s="9">
+        <f>I17*H17</f>
+        <v>0.16</v>
+      </c>
+      <c r="P17" s="1"/>
+      <c r="Q17" s="1"/>
+    </row>
+    <row r="18" ht="14.25">
+      <c r="B18" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="C18" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="E18" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="F18" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="G18" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="H18" s="8">
+        <v>8.0000000000000002e-002</v>
+      </c>
+      <c r="I18" s="3">
+        <v>1</v>
+      </c>
+      <c r="J18" s="9">
+        <f>I18*H18</f>
+        <v>8.0000000000000002e-002</v>
+      </c>
+      <c r="P18" s="1"/>
+      <c r="Q18" s="1"/>
+    </row>
+    <row r="19" ht="14.25">
+      <c r="B19" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="C19" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="E19" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="F19" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="G19" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="H19" s="8">
+        <v>8.0000000000000002e-002</v>
+      </c>
+      <c r="I19" s="3">
+        <v>2</v>
+      </c>
+      <c r="J19" s="9">
+        <f>I19*H19</f>
+        <v>0.16</v>
+      </c>
+      <c r="P19" s="1"/>
+      <c r="Q19" s="1"/>
+    </row>
+    <row r="20" ht="14.25">
+      <c r="B20" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="C20" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="E20" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="F20" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="G20" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="H20" s="8">
+        <v>0.40999999999999998</v>
+      </c>
+      <c r="I20" s="3">
+        <v>1</v>
+      </c>
+      <c r="J20" s="9">
+        <f>I20*H20</f>
+        <v>0.40999999999999998</v>
+      </c>
+      <c r="P20" s="1"/>
+      <c r="Q20" s="1"/>
+    </row>
+    <row r="21" ht="14.25">
+      <c r="B21" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="C21" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="E21" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="F21" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="G21" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="H21" s="8">
+        <v>5.9400000000000004</v>
+      </c>
+      <c r="I21" s="3">
+        <v>1</v>
+      </c>
+      <c r="J21" s="9">
+        <f>I21*H21</f>
+        <v>5.9400000000000004</v>
+      </c>
+      <c r="P21" s="1"/>
+      <c r="Q21" s="1"/>
+    </row>
+    <row r="22" ht="14.25">
+      <c r="B22" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="C22" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="E22" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="F22" s="6"/>
+      <c r="G22" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="H22" s="8">
         <v>8</v>
       </c>
-      <c r="D4" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E4" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="F4" s="7">
-        <v>5.9400000000000004</v>
-      </c>
-      <c r="G4" s="2">
+      <c r="I22" s="3">
         <v>1</v>
       </c>
-      <c r="H4" s="8">
-        <f t="shared" ref="H4:H9" si="0">G4*F4</f>
-        <v>5.9400000000000004</v>
-      </c>
-    </row>
-    <row r="5" ht="14.25">
-      <c r="B5" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="D5" s="5"/>
-      <c r="E5" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="F5" s="7">
+      <c r="J22" s="9">
+        <f>I22*H22</f>
         <v>8</v>
       </c>
-      <c r="G5" s="2">
+      <c r="P22" s="1"/>
+      <c r="Q22" s="1"/>
+    </row>
+    <row r="23" ht="14.25">
+      <c r="B23" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="C23" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="E23" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="F23" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="G23" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="H23" s="8">
+        <v>5.0700000000000003</v>
+      </c>
+      <c r="I23" s="3">
         <v>1</v>
       </c>
-      <c r="H5" s="8">
-        <f t="shared" si="0"/>
-        <v>8</v>
-      </c>
-      <c r="K5" s="10"/>
-    </row>
-    <row r="6" ht="14.25">
-      <c r="B6" s="4" t="s">
+      <c r="J23" s="9">
+        <f>I23*H23</f>
+        <v>5.0700000000000003</v>
+      </c>
+      <c r="P23" s="1"/>
+      <c r="Q23" s="1"/>
+    </row>
+    <row r="24" ht="14.25">
+      <c r="B24" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="C24" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="E24" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="F24" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="G24" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="C6" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="D6" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="E6" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="F6" s="7">
-        <v>2.9199999999999999</v>
-      </c>
-      <c r="G6" s="2">
+      <c r="H24" s="8">
+        <v>0.67000000000000004</v>
+      </c>
+      <c r="I24" s="3">
         <v>1</v>
       </c>
-      <c r="H6" s="8">
-        <f t="shared" si="0"/>
-        <v>2.9199999999999999</v>
-      </c>
-      <c r="J6" s="10"/>
-    </row>
-    <row r="7" ht="14.25">
-      <c r="B7" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="D7" s="5"/>
-      <c r="E7" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="F7" s="7">
-        <v>5.3600000000000003</v>
-      </c>
-      <c r="G7" s="2">
-        <v>1</v>
-      </c>
-      <c r="H7" s="8">
-        <f t="shared" si="0"/>
-        <v>5.3600000000000003</v>
-      </c>
-      <c r="J7" s="10"/>
-    </row>
-    <row r="8" ht="14.25">
-      <c r="B8" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="D8" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="E8" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="F8" s="7">
-        <v>0.70999999999999996</v>
-      </c>
-      <c r="G8" s="2">
-        <v>2</v>
-      </c>
-      <c r="H8" s="8">
-        <f t="shared" si="0"/>
-        <v>1.4199999999999999</v>
-      </c>
-    </row>
-    <row r="9" ht="14.25">
-      <c r="B9" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="C9" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="D9" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E9" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="F9" s="7">
-        <v>5.0700000000000003</v>
-      </c>
-      <c r="G9" s="2">
-        <v>1</v>
-      </c>
-      <c r="H9" s="8">
-        <f t="shared" si="0"/>
-        <v>5.0700000000000003</v>
-      </c>
-    </row>
-    <row r="10" ht="14.25">
-      <c r="B10" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="C10" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="D10" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="E10" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="F10" s="7">
-        <v>0.40999999999999998</v>
-      </c>
-      <c r="G10" s="2">
-        <v>1</v>
-      </c>
-      <c r="H10" s="8">
-        <f t="shared" ref="H10:H24" si="1">G10*F10</f>
-        <v>0.40999999999999998</v>
-      </c>
-    </row>
-    <row r="11" ht="14.25">
-      <c r="B11" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="C11" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="D11" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="E11" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="F11" s="7">
-        <v>0.11</v>
-      </c>
-      <c r="G11" s="2">
-        <v>2</v>
-      </c>
-      <c r="H11" s="8">
-        <f t="shared" si="1"/>
-        <v>0.22</v>
-      </c>
-    </row>
-    <row r="12" ht="14.25">
-      <c r="B12" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="C12" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="D12" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="E12" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="F12" s="7">
-        <v>0.080000000000000002</v>
-      </c>
-      <c r="G12" s="2">
-        <v>2</v>
-      </c>
-      <c r="H12" s="8">
-        <f t="shared" si="1"/>
-        <v>0.16</v>
-      </c>
-    </row>
-    <row r="13" ht="14.25">
-      <c r="B13" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="C13" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="D13" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="E13" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="F13" s="7">
-        <v>0.080000000000000002</v>
-      </c>
-      <c r="G13" s="2">
-        <v>1</v>
-      </c>
-      <c r="H13" s="8">
-        <f t="shared" si="1"/>
-        <v>0.080000000000000002</v>
-      </c>
-    </row>
-    <row r="14" ht="14.25">
-      <c r="B14" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="C14" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="D14" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="E14" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="F14" s="7">
-        <v>0.080000000000000002</v>
-      </c>
-      <c r="G14" s="2">
-        <v>2</v>
-      </c>
-      <c r="H14" s="8">
-        <f t="shared" si="1"/>
-        <v>0.16</v>
-      </c>
-    </row>
-    <row r="15" ht="14.25">
-      <c r="B15" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="C15" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="D15" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="E15" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="F15" s="7">
-        <v>0.20999999999999999</v>
-      </c>
-      <c r="G15" s="2">
-        <v>1</v>
-      </c>
-      <c r="H15" s="8">
-        <f t="shared" si="1"/>
-        <v>0.20999999999999999</v>
-      </c>
-    </row>
-    <row r="16" ht="14.25">
-      <c r="B16" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="C16" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="D16" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="E16" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="F16" s="7">
-        <v>0.17999999999999999</v>
-      </c>
-      <c r="G16" s="2">
-        <v>1</v>
-      </c>
-      <c r="H16" s="8">
-        <f t="shared" si="1"/>
-        <v>0.17999999999999999</v>
-      </c>
-    </row>
-    <row r="17" ht="14.25">
-      <c r="B17" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="C17" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="D17" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="E17" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="F17" s="7">
-        <v>1.3100000000000001</v>
-      </c>
-      <c r="G17" s="2">
-        <v>1</v>
-      </c>
-      <c r="H17" s="8">
-        <f t="shared" si="1"/>
-        <v>1.3100000000000001</v>
-      </c>
-    </row>
-    <row r="18" ht="14.25">
-      <c r="B18" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="C18" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="D18" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="E18" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="F18" s="7">
-        <v>0.56999999999999995</v>
-      </c>
-      <c r="G18" s="2">
-        <v>1</v>
-      </c>
-      <c r="H18" s="8">
-        <f t="shared" si="1"/>
-        <v>0.56999999999999995</v>
-      </c>
-    </row>
-    <row r="19" ht="14.25">
-      <c r="B19" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="C19" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="D19" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="E19" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="F19" s="7">
-        <v>0.32000000000000001</v>
-      </c>
-      <c r="G19" s="2">
-        <v>1</v>
-      </c>
-      <c r="H19" s="8">
-        <f t="shared" si="1"/>
-        <v>0.32000000000000001</v>
-      </c>
-    </row>
-    <row r="20" ht="14.25">
-      <c r="B20" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="C20" s="11">
-        <v>824500281</v>
-      </c>
-      <c r="D20" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="E20" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="F20" s="7">
-        <v>0.26000000000000001</v>
-      </c>
-      <c r="G20" s="2">
-        <v>1</v>
-      </c>
-      <c r="H20" s="8">
-        <f t="shared" si="1"/>
-        <v>0.26000000000000001</v>
-      </c>
-    </row>
-    <row r="21" ht="14.25">
-      <c r="B21" s="12" t="s">
-        <v>56</v>
-      </c>
-      <c r="C21" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="D21" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="E21" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="F21" s="7">
-        <v>0.29999999999999999</v>
-      </c>
-      <c r="G21" s="2">
-        <v>1</v>
-      </c>
-      <c r="H21" s="8">
-        <f t="shared" si="1"/>
-        <v>0.29999999999999999</v>
-      </c>
-    </row>
-    <row r="22" ht="14.25">
-      <c r="B22" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="C22" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="D22" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="E22" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="F22" s="7">
-        <v>1.49</v>
-      </c>
-      <c r="G22" s="2">
-        <v>1</v>
-      </c>
-      <c r="H22" s="8">
-        <f t="shared" si="1"/>
-        <v>1.49</v>
-      </c>
-    </row>
-    <row r="23" ht="14.25">
-      <c r="B23" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="C23" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="D23" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="E23" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="F23" s="7">
+      <c r="J24" s="9">
+        <f>I24*H24</f>
         <v>0.67000000000000004</v>
       </c>
-      <c r="G23" s="2">
-        <v>1</v>
-      </c>
-      <c r="H23" s="8">
-        <f t="shared" si="1"/>
-        <v>0.67000000000000004</v>
-      </c>
-    </row>
-    <row r="24" ht="14.25">
-      <c r="B24" s="13" t="s">
-        <v>65</v>
-      </c>
-      <c r="C24" s="14">
-        <v>7447060</v>
-      </c>
-      <c r="D24" s="15" t="s">
-        <v>66</v>
-      </c>
-      <c r="E24" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="F24" s="7">
-        <v>2.0600000000000001</v>
-      </c>
-      <c r="G24" s="2">
-        <v>1</v>
-      </c>
-      <c r="H24" s="8">
-        <f t="shared" si="1"/>
-        <v>2.0600000000000001</v>
-      </c>
+      <c r="P24" s="1"/>
+      <c r="Q24" s="1"/>
     </row>
     <row r="25" ht="14.25">
-      <c r="B25" s="4"/>
-      <c r="C25" s="4"/>
-      <c r="D25" s="4"/>
-      <c r="E25" s="4"/>
-      <c r="F25" s="4"/>
-    </row>
-    <row r="27" ht="14.25">
-      <c r="G27" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="H27" s="16">
-        <f>SUM(H4:H24)</f>
-        <v>37.109999999999999</v>
-      </c>
+      <c r="P25" s="1"/>
+      <c r="Q25" s="1"/>
+    </row>
+    <row r="26" ht="14.25">
+      <c r="I26" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="J26" s="17">
+        <f>SUM(J4:J24)</f>
+        <v>36.950000000000003</v>
+      </c>
+      <c r="P26" s="1"/>
+      <c r="Q26" s="1"/>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink r:id="rId1" ref="C4" tooltip=""/>
-    <hyperlink r:id="rId2" ref="D4" tooltip=""/>
-    <hyperlink r:id="rId3" ref="C6" tooltip=""/>
-    <hyperlink r:id="rId4" ref="D6" tooltip=""/>
-    <hyperlink r:id="rId5" ref="C7" tooltip=""/>
-    <hyperlink r:id="rId6" ref="C8" tooltip=""/>
-    <hyperlink r:id="rId7" ref="D8" tooltip=""/>
-    <hyperlink r:id="rId8" ref="C9" tooltip=""/>
-    <hyperlink r:id="rId9" ref="D9" tooltip=""/>
-    <hyperlink r:id="rId10" ref="C10" tooltip=""/>
-    <hyperlink r:id="rId11" ref="D10" tooltip=""/>
-    <hyperlink r:id="rId12" ref="C11" tooltip=""/>
-    <hyperlink r:id="rId13" ref="D11" tooltip=""/>
-    <hyperlink r:id="rId14" ref="C12" tooltip=""/>
-    <hyperlink r:id="rId15" ref="D12" tooltip=""/>
-    <hyperlink r:id="rId16" ref="C13" tooltip=""/>
-    <hyperlink r:id="rId17" ref="D13" tooltip=""/>
-    <hyperlink r:id="rId18" ref="C14" tooltip=""/>
-    <hyperlink r:id="rId17" ref="D14" tooltip=""/>
-    <hyperlink r:id="rId19" ref="C15" tooltip=""/>
-    <hyperlink r:id="rId20" ref="D15" tooltip=""/>
-    <hyperlink r:id="rId21" ref="C16" tooltip=""/>
-    <hyperlink r:id="rId22" ref="D16" tooltip=""/>
-    <hyperlink r:id="rId23" ref="C17" tooltip=""/>
-    <hyperlink r:id="rId24" ref="D17" tooltip=""/>
-    <hyperlink r:id="rId25" ref="C18" tooltip=""/>
-    <hyperlink r:id="rId26" ref="D18" tooltip=""/>
-    <hyperlink r:id="rId27" ref="C19" tooltip=""/>
-    <hyperlink r:id="rId28" ref="D19" tooltip=""/>
-    <hyperlink r:id="rId29" ref="C20" tooltip=""/>
-    <hyperlink r:id="rId30" ref="D20" tooltip=""/>
-    <hyperlink r:id="rId31" ref="C21" tooltip=""/>
-    <hyperlink r:id="rId32" ref="D21" tooltip=""/>
-    <hyperlink r:id="rId33" ref="C22" tooltip=""/>
-    <hyperlink r:id="rId34" ref="D22" tooltip=""/>
-    <hyperlink r:id="rId35" ref="C23" tooltip=""/>
-    <hyperlink r:id="rId36" ref="D23" tooltip=""/>
-    <hyperlink r:id="rId37" ref="C24" tooltip=""/>
-    <hyperlink r:id="rId38" ref="D24" tooltip=""/>
+    <hyperlink r:id="rId1" ref="E4" tooltip=""/>
+    <hyperlink r:id="rId2" ref="F4" tooltip=""/>
+    <hyperlink r:id="rId3" ref="E5" tooltip=""/>
+    <hyperlink r:id="rId4" ref="F5" tooltip=""/>
+    <hyperlink r:id="rId5" ref="E6" tooltip=""/>
+    <hyperlink r:id="rId6" ref="F6" tooltip=""/>
+    <hyperlink r:id="rId7" ref="E7" tooltip=""/>
+    <hyperlink r:id="rId8" ref="F7" tooltip=""/>
+    <hyperlink r:id="rId9" ref="E8" tooltip=""/>
+    <hyperlink r:id="rId10" ref="F8" tooltip=""/>
+    <hyperlink r:id="rId11" ref="E9" tooltip=""/>
+    <hyperlink r:id="rId12" ref="F9" tooltip=""/>
+    <hyperlink r:id="rId13" ref="E10" tooltip=""/>
+    <hyperlink r:id="rId14" ref="E11" tooltip=""/>
+    <hyperlink r:id="rId15" ref="F11" tooltip=""/>
+    <hyperlink r:id="rId16" ref="E12" tooltip=""/>
+    <hyperlink r:id="rId17" ref="F12" tooltip=""/>
+    <hyperlink r:id="rId18" ref="E13" tooltip=""/>
+    <hyperlink r:id="rId19" ref="F13" tooltip=""/>
+    <hyperlink r:id="rId20" ref="E14" tooltip=""/>
+    <hyperlink r:id="rId21" ref="F14" tooltip=""/>
+    <hyperlink r:id="rId22" ref="E15" tooltip=""/>
+    <hyperlink r:id="rId23" ref="F15" tooltip=""/>
+    <hyperlink r:id="rId24" ref="E16" tooltip=""/>
+    <hyperlink r:id="rId25" ref="F16" tooltip=""/>
+    <hyperlink r:id="rId26" ref="E17" tooltip=""/>
+    <hyperlink r:id="rId27" ref="F17" tooltip=""/>
+    <hyperlink r:id="rId28" ref="E18" tooltip=""/>
+    <hyperlink r:id="rId29" ref="F18" tooltip=""/>
+    <hyperlink r:id="rId30" ref="E19" tooltip=""/>
+    <hyperlink r:id="rId29" ref="F19" tooltip=""/>
+    <hyperlink r:id="rId31" ref="E20" tooltip=""/>
+    <hyperlink r:id="rId32" ref="F20" tooltip=""/>
+    <hyperlink r:id="rId33" ref="E21" tooltip=""/>
+    <hyperlink r:id="rId34" ref="F21" tooltip=""/>
+    <hyperlink r:id="rId35" ref="E23" tooltip=""/>
+    <hyperlink r:id="rId36" ref="F23" tooltip=""/>
+    <hyperlink r:id="rId37" ref="E24" tooltip=""/>
+    <hyperlink r:id="rId38" ref="F24" tooltip=""/>
   </hyperlinks>
   <printOptions headings="0" gridLines="0"/>
   <pageMargins left="0.25196850393700787" right="0.25196850393700787" top="0.75196850393700787" bottom="0.75196850393700787" header="0.29999999999999999" footer="0.29999999999999999"/>
@@ -1800,22 +2094,6 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
   <sheetPr>
-    <tabColor rgb="FF002060"/>
-    <outlinePr applyStyles="0" summaryBelow="1" summaryRight="1" showOutlineSymbols="1"/>
-    <pageSetUpPr autoPageBreaks="1" fitToPage="0"/>
-  </sheetPr>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData/>
-  <printOptions headings="0" gridLines="0"/>
-  <pageMargins left="0.70078740157480324" right="0.70078740157480324" top="0.75196850393700787" bottom="0.75196850393700787" header="0.29999999999999999" footer="0.29999999999999999"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
-  <headerFooter/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
-  <sheetPr>
     <tabColor indexed="2"/>
     <outlinePr applyStyles="0" summaryBelow="1" summaryRight="1" showOutlineSymbols="1"/>
     <pageSetUpPr autoPageBreaks="1" fitToPage="0"/>
@@ -1835,359 +2113,359 @@
   </cols>
   <sheetData>
     <row r="8" ht="14.25">
-      <c r="C8" s="17" t="s">
-        <v>68</v>
-      </c>
-      <c r="D8" s="17" t="s">
-        <v>69</v>
-      </c>
-      <c r="E8" s="17" t="s">
-        <v>70</v>
-      </c>
-      <c r="F8" s="17" t="s">
-        <v>71</v>
-      </c>
-      <c r="G8" s="18" t="s">
-        <v>72</v>
-      </c>
-      <c r="H8" s="19" t="s">
-        <v>73</v>
+      <c r="C8" s="18" t="s">
+        <v>108</v>
+      </c>
+      <c r="D8" s="18" t="s">
+        <v>109</v>
+      </c>
+      <c r="E8" s="18" t="s">
+        <v>110</v>
+      </c>
+      <c r="F8" s="18" t="s">
+        <v>111</v>
+      </c>
+      <c r="G8" s="19" t="s">
+        <v>112</v>
+      </c>
+      <c r="H8" s="20" t="s">
+        <v>113</v>
       </c>
       <c r="U8" t="s">
-        <v>74</v>
+        <v>114</v>
       </c>
     </row>
     <row r="9" ht="14.25">
-      <c r="C9" s="17" t="s">
-        <v>75</v>
-      </c>
-      <c r="D9" s="17" t="s">
-        <v>76</v>
-      </c>
-      <c r="E9" s="17" t="s">
-        <v>77</v>
-      </c>
-      <c r="F9" s="17" t="s">
-        <v>78</v>
-      </c>
-      <c r="G9" s="18"/>
-      <c r="H9" s="19" t="s">
-        <v>79</v>
+      <c r="C9" s="18" t="s">
+        <v>115</v>
+      </c>
+      <c r="D9" s="18" t="s">
+        <v>116</v>
+      </c>
+      <c r="E9" s="18" t="s">
+        <v>117</v>
+      </c>
+      <c r="F9" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="G9" s="19"/>
+      <c r="H9" s="20" t="s">
+        <v>118</v>
       </c>
       <c r="U9" t="s">
-        <v>80</v>
+        <v>119</v>
       </c>
     </row>
     <row r="10" ht="14.25">
-      <c r="C10" s="17" t="s">
-        <v>81</v>
-      </c>
-      <c r="D10" s="17" t="s">
-        <v>82</v>
-      </c>
-      <c r="E10" s="17" t="s">
-        <v>83</v>
-      </c>
-      <c r="F10" s="17" t="s">
-        <v>84</v>
-      </c>
-      <c r="G10" s="18"/>
-      <c r="H10" s="19" t="s">
-        <v>85</v>
+      <c r="C10" s="18" t="s">
+        <v>120</v>
+      </c>
+      <c r="D10" s="18" t="s">
+        <v>121</v>
+      </c>
+      <c r="E10" s="18" t="s">
+        <v>122</v>
+      </c>
+      <c r="F10" s="18" t="s">
+        <v>33</v>
+      </c>
+      <c r="G10" s="19"/>
+      <c r="H10" s="20" t="s">
+        <v>123</v>
       </c>
       <c r="U10" t="s">
-        <v>86</v>
+        <v>124</v>
       </c>
     </row>
     <row r="11" ht="14.25">
-      <c r="C11" s="17" t="s">
-        <v>87</v>
-      </c>
-      <c r="D11" s="17" t="s">
-        <v>88</v>
-      </c>
-      <c r="E11" s="17" t="s">
-        <v>89</v>
-      </c>
-      <c r="F11" s="17" t="s">
-        <v>90</v>
-      </c>
-      <c r="G11" s="18"/>
-      <c r="H11" s="19" t="s">
-        <v>91</v>
+      <c r="C11" s="18" t="s">
+        <v>125</v>
+      </c>
+      <c r="D11" s="18" t="s">
+        <v>126</v>
+      </c>
+      <c r="E11" s="18" t="s">
+        <v>127</v>
+      </c>
+      <c r="F11" s="18" t="s">
+        <v>128</v>
+      </c>
+      <c r="G11" s="19"/>
+      <c r="H11" s="20" t="s">
+        <v>129</v>
       </c>
       <c r="I11" t="s">
-        <v>92</v>
-      </c>
-      <c r="J11" s="19" t="s">
-        <v>93</v>
+        <v>130</v>
+      </c>
+      <c r="J11" s="20" t="s">
+        <v>131</v>
       </c>
       <c r="K11" t="s">
-        <v>94</v>
+        <v>132</v>
       </c>
       <c r="L11" t="s">
-        <v>95</v>
-      </c>
-      <c r="U11" s="15" t="s">
-        <v>96</v>
+        <v>133</v>
+      </c>
+      <c r="U11" s="14" t="s">
+        <v>134</v>
       </c>
     </row>
     <row r="12" ht="14.25">
       <c r="B12" t="s">
-        <v>97</v>
-      </c>
-      <c r="C12" s="17" t="s">
-        <v>98</v>
-      </c>
-      <c r="D12" s="17" t="s">
-        <v>99</v>
-      </c>
-      <c r="E12" s="17" t="s">
-        <v>100</v>
-      </c>
-      <c r="F12" s="17" t="s">
-        <v>101</v>
-      </c>
-      <c r="G12" s="18"/>
-      <c r="H12" s="19" t="s">
-        <v>102</v>
+        <v>135</v>
+      </c>
+      <c r="C12" s="18" t="s">
+        <v>136</v>
+      </c>
+      <c r="D12" s="18" t="s">
+        <v>137</v>
+      </c>
+      <c r="E12" s="18" t="s">
+        <v>138</v>
+      </c>
+      <c r="F12" s="18" t="s">
+        <v>139</v>
+      </c>
+      <c r="G12" s="19"/>
+      <c r="H12" s="20" t="s">
+        <v>140</v>
       </c>
       <c r="I12" t="s">
-        <v>103</v>
+        <v>141</v>
       </c>
       <c r="J12" t="s">
-        <v>104</v>
+        <v>142</v>
       </c>
       <c r="K12" t="s">
-        <v>105</v>
+        <v>143</v>
       </c>
       <c r="L12" t="s">
-        <v>106</v>
+        <v>144</v>
       </c>
     </row>
     <row r="13" ht="14.25">
       <c r="B13" t="s">
-        <v>107</v>
-      </c>
-      <c r="C13" s="17" t="s">
-        <v>108</v>
-      </c>
-      <c r="D13" s="17" t="s">
-        <v>109</v>
-      </c>
-      <c r="E13" s="17" t="s">
-        <v>110</v>
-      </c>
-      <c r="F13" s="17" t="s">
-        <v>111</v>
-      </c>
-      <c r="G13" s="18"/>
-      <c r="H13" s="19" t="s">
-        <v>112</v>
+        <v>145</v>
+      </c>
+      <c r="C13" s="18" t="s">
+        <v>146</v>
+      </c>
+      <c r="D13" s="18" t="s">
+        <v>147</v>
+      </c>
+      <c r="E13" s="18" t="s">
+        <v>148</v>
+      </c>
+      <c r="F13" s="18" t="s">
+        <v>149</v>
+      </c>
+      <c r="G13" s="19"/>
+      <c r="H13" s="20" t="s">
+        <v>150</v>
       </c>
       <c r="I13" t="s">
-        <v>113</v>
+        <v>151</v>
       </c>
       <c r="J13" t="s">
-        <v>114</v>
+        <v>152</v>
       </c>
       <c r="K13" t="s">
-        <v>115</v>
+        <v>153</v>
       </c>
       <c r="L13" t="s">
-        <v>116</v>
+        <v>154</v>
       </c>
     </row>
     <row r="14" ht="14.25">
-      <c r="C14" s="17"/>
-      <c r="D14" s="17" t="s">
-        <v>117</v>
-      </c>
-      <c r="E14" s="17" t="s">
-        <v>118</v>
-      </c>
-      <c r="F14" s="17" t="s">
-        <v>119</v>
-      </c>
-      <c r="G14" s="18"/>
-      <c r="H14" s="19" t="s">
-        <v>120</v>
+      <c r="C14" s="18"/>
+      <c r="D14" s="18" t="s">
+        <v>155</v>
+      </c>
+      <c r="E14" s="18" t="s">
+        <v>156</v>
+      </c>
+      <c r="F14" s="18" t="s">
+        <v>157</v>
+      </c>
+      <c r="G14" s="19"/>
+      <c r="H14" s="20" t="s">
+        <v>158</v>
       </c>
       <c r="I14" t="s">
-        <v>121</v>
+        <v>159</v>
       </c>
       <c r="J14" t="s">
-        <v>122</v>
+        <v>160</v>
       </c>
     </row>
     <row r="17" ht="14.25">
-      <c r="O17" s="19"/>
+      <c r="O17" s="20"/>
     </row>
     <row r="18" ht="14.25">
       <c r="B18" t="s">
-        <v>123</v>
-      </c>
-      <c r="D18" s="17" t="s">
-        <v>69</v>
+        <v>161</v>
+      </c>
+      <c r="D18" s="18" t="s">
+        <v>109</v>
       </c>
       <c r="E18" t="s">
-        <v>124</v>
-      </c>
-      <c r="F18" s="17" t="s">
-        <v>71</v>
-      </c>
-      <c r="G18" s="18" t="s">
-        <v>125</v>
-      </c>
-      <c r="H18" s="19" t="s">
-        <v>73</v>
+        <v>162</v>
+      </c>
+      <c r="F18" s="18" t="s">
+        <v>111</v>
+      </c>
+      <c r="G18" s="19" t="s">
+        <v>163</v>
+      </c>
+      <c r="H18" s="20" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="19" ht="14.25">
       <c r="B19" t="s">
-        <v>123</v>
-      </c>
-      <c r="D19" s="17" t="s">
-        <v>76</v>
-      </c>
-      <c r="E19" s="13" t="s">
-        <v>70</v>
-      </c>
-      <c r="F19" s="17" t="s">
-        <v>78</v>
-      </c>
-      <c r="G19" s="18"/>
-      <c r="H19" s="19" t="s">
-        <v>79</v>
-      </c>
-      <c r="U19" s="13" t="s">
-        <v>126</v>
+        <v>161</v>
+      </c>
+      <c r="D19" s="18" t="s">
+        <v>116</v>
+      </c>
+      <c r="E19" s="15" t="s">
+        <v>110</v>
+      </c>
+      <c r="F19" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="G19" s="19"/>
+      <c r="H19" s="20" t="s">
+        <v>118</v>
+      </c>
+      <c r="U19" s="15" t="s">
+        <v>164</v>
       </c>
     </row>
     <row r="20" ht="14.25">
       <c r="B20" t="s">
-        <v>127</v>
-      </c>
-      <c r="D20" s="17" t="s">
-        <v>82</v>
-      </c>
-      <c r="E20" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="F20" s="17" t="s">
-        <v>84</v>
-      </c>
-      <c r="G20" s="18"/>
-      <c r="H20" s="19" t="s">
-        <v>85</v>
+        <v>165</v>
+      </c>
+      <c r="D20" s="18" t="s">
+        <v>121</v>
+      </c>
+      <c r="E20" s="15" t="s">
+        <v>117</v>
+      </c>
+      <c r="F20" s="18" t="s">
+        <v>33</v>
+      </c>
+      <c r="G20" s="19"/>
+      <c r="H20" s="20" t="s">
+        <v>123</v>
       </c>
       <c r="U20" t="s">
-        <v>128</v>
+        <v>166</v>
       </c>
     </row>
     <row r="21" ht="14.25">
       <c r="B21" t="s">
+        <v>167</v>
+      </c>
+      <c r="E21" t="s">
+        <v>168</v>
+      </c>
+      <c r="F21" s="18" t="s">
+        <v>128</v>
+      </c>
+      <c r="G21" s="19"/>
+      <c r="H21" s="20" t="s">
         <v>129</v>
       </c>
-      <c r="E21" t="s">
-        <v>130</v>
-      </c>
-      <c r="F21" s="17" t="s">
-        <v>90</v>
-      </c>
-      <c r="G21" s="18"/>
-      <c r="H21" s="19" t="s">
-        <v>91</v>
-      </c>
       <c r="I21" t="s">
-        <v>131</v>
+        <v>169</v>
       </c>
       <c r="K21" t="s">
-        <v>94</v>
+        <v>132</v>
       </c>
       <c r="L21" t="s">
-        <v>132</v>
+        <v>170</v>
       </c>
       <c r="U21" t="s">
-        <v>133</v>
+        <v>171</v>
       </c>
     </row>
     <row r="22" ht="14.25">
       <c r="B22" t="s">
-        <v>134</v>
-      </c>
-      <c r="C22" s="17" t="s">
-        <v>98</v>
+        <v>172</v>
+      </c>
+      <c r="C22" s="18" t="s">
+        <v>136</v>
       </c>
       <c r="E22" t="s">
-        <v>135</v>
-      </c>
-      <c r="F22" s="17" t="s">
-        <v>101</v>
-      </c>
-      <c r="G22" s="18"/>
-      <c r="H22" s="19" t="s">
-        <v>102</v>
+        <v>173</v>
+      </c>
+      <c r="F22" s="18" t="s">
+        <v>139</v>
+      </c>
+      <c r="G22" s="19"/>
+      <c r="H22" s="20" t="s">
+        <v>140</v>
       </c>
       <c r="I22" t="s">
-        <v>136</v>
+        <v>174</v>
       </c>
       <c r="K22" t="s">
-        <v>105</v>
+        <v>143</v>
       </c>
       <c r="L22" t="s">
-        <v>137</v>
-      </c>
-      <c r="U22" s="15" t="s">
-        <v>138</v>
+        <v>175</v>
+      </c>
+      <c r="U22" s="14" t="s">
+        <v>176</v>
       </c>
     </row>
     <row r="23" ht="14.25">
       <c r="B23" t="s">
-        <v>139</v>
-      </c>
-      <c r="C23" s="17" t="s">
-        <v>108</v>
-      </c>
-      <c r="E23" s="13" t="s">
-        <v>140</v>
-      </c>
-      <c r="F23" s="17" t="s">
-        <v>111</v>
-      </c>
-      <c r="G23" s="18"/>
-      <c r="H23" s="19" t="s">
-        <v>112</v>
+        <v>177</v>
+      </c>
+      <c r="C23" s="18" t="s">
+        <v>146</v>
+      </c>
+      <c r="E23" s="15" t="s">
+        <v>178</v>
+      </c>
+      <c r="F23" s="18" t="s">
+        <v>149</v>
+      </c>
+      <c r="G23" s="19"/>
+      <c r="H23" s="20" t="s">
+        <v>150</v>
       </c>
       <c r="I23" t="s">
-        <v>141</v>
+        <v>179</v>
       </c>
       <c r="K23" t="s">
-        <v>115</v>
+        <v>153</v>
       </c>
       <c r="L23" t="s">
-        <v>142</v>
+        <v>180</v>
       </c>
     </row>
     <row r="24" ht="14.25">
       <c r="D24" t="s">
-        <v>117</v>
+        <v>155</v>
       </c>
       <c r="E24" t="s">
-        <v>143</v>
-      </c>
-      <c r="F24" s="17" t="s">
-        <v>119</v>
-      </c>
-      <c r="G24" s="18"/>
-      <c r="H24" s="19" t="s">
-        <v>120</v>
+        <v>181</v>
+      </c>
+      <c r="F24" s="18" t="s">
+        <v>157</v>
+      </c>
+      <c r="G24" s="19"/>
+      <c r="H24" s="20" t="s">
+        <v>158</v>
       </c>
       <c r="I24" t="s">
-        <v>144</v>
+        <v>182</v>
       </c>
       <c r="J24" t="s">
-        <v>122</v>
+        <v>160</v>
       </c>
     </row>
   </sheetData>

--- a/Hardware/Matériel.xlsx
+++ b/Hardware/Matériel.xlsx
@@ -1,24 +1,42 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lukas\Desktop\m7-Lecteur-RFID\Hardware\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38ED39A1-4278-4EB4-B6AF-0F08948ACA16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="2"/>
+    <workbookView xWindow="20808" yWindow="0" windowWidth="10008" windowHeight="16656" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Liste de matériels (prototype)" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Commandes" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="XIAO ESP32" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Liste de matériels (prototy (2)" sheetId="4" r:id="rId1"/>
+    <sheet name="Liste de matériels (prototype)" sheetId="1" r:id="rId2"/>
+    <sheet name="Commandes" sheetId="2" r:id="rId3"/>
+    <sheet name="XIAO ESP32" sheetId="3" r:id="rId4"/>
   </sheets>
-  <calcPr/>
+  <calcPr calcId="191029" calcOnSave="0"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{D0CA8CA8-9F24-4464-BF8E-62219DCF47F9}"/>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="183">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="377" uniqueCount="207">
   <si>
     <t>Reference</t>
   </si>
@@ -29,7 +47,7 @@
     <t>Valeur</t>
   </si>
   <si>
-    <t xml:space="preserve">Ref fab.</t>
+    <t>Ref fab.</t>
   </si>
   <si>
     <t>datasheet</t>
@@ -50,7 +68,7 @@
     <t>C1</t>
   </si>
   <si>
-    <t xml:space="preserve">Condensateur électrolytique</t>
+    <t>Condensateur électrolytique</t>
   </si>
   <si>
     <t>470µF</t>
@@ -59,7 +77,7 @@
     <t>REF1020471M050K</t>
   </si>
   <si>
-    <t xml:space="preserve">./Datasheets/Condensateur  470 uF elec - ref-series.pdf</t>
+    <t>./Datasheets/Condensateur  470 uF elec - ref-series.pdf</t>
   </si>
   <si>
     <t>Mouser</t>
@@ -68,7 +86,7 @@
     <t>C2</t>
   </si>
   <si>
-    <t xml:space="preserve">Condensateur ceram</t>
+    <t>Condensateur ceram</t>
   </si>
   <si>
     <t>4.7μF</t>
@@ -77,7 +95,7 @@
     <t>GRM319R61H475KA12D</t>
   </si>
   <si>
-    <t xml:space="preserve">./Datasheets/Condensateur  4,7 uF ceram - GRM319R61H475KA12_01A.pdf</t>
+    <t>./Datasheets/Condensateur  4,7 uF ceram - GRM319R61H475KA12_01A.pdf</t>
   </si>
   <si>
     <t>C3</t>
@@ -101,13 +119,13 @@
     <t>RDEC71H226MWK1H03B</t>
   </si>
   <si>
-    <t xml:space="preserve">./Datasheets/Condensateur  22 uF ceram - GRM188R61A226ME15-02A.pdf</t>
+    <t>./Datasheets/Condensateur  22 uF ceram - GRM188R61A226ME15-02A.pdf</t>
   </si>
   <si>
     <t>D1</t>
   </si>
   <si>
-    <t xml:space="preserve">Diode Schottky</t>
+    <t>Diode Schottky</t>
   </si>
   <si>
     <t>BX36_R1</t>
@@ -116,13 +134,13 @@
     <t>BX36_R1_00001</t>
   </si>
   <si>
-    <t xml:space="preserve">./Datasheets/Diode - BX36_R1_00001.pdf</t>
+    <t>./Datasheets/Diode - BX36_R1_00001.pdf</t>
   </si>
   <si>
     <t>D2</t>
   </si>
   <si>
-    <t xml:space="preserve">diode TVS</t>
+    <t>diode TVS</t>
   </si>
   <si>
     <t>SMAJ28A</t>
@@ -137,19 +155,19 @@
     <t>E1</t>
   </si>
   <si>
-    <t xml:space="preserve">Écran OLED</t>
+    <t>Écran OLED</t>
   </si>
   <si>
     <t>DM-OLED096-636</t>
   </si>
   <si>
-    <t xml:space="preserve">DST-015 (OLED SSD1305)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">E2, E3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LED (ambre)</t>
+    <t>DST-015 (OLED SSD1305)</t>
+  </si>
+  <si>
+    <t>E2, E3</t>
+  </si>
+  <si>
+    <t>LED (ambre)</t>
   </si>
   <si>
     <t>LED</t>
@@ -158,16 +176,16 @@
     <t>LTST-C150AKT</t>
   </si>
   <si>
-    <t xml:space="preserve">./Datasheets/AmberLed - LTST-C150AKT.pdf</t>
+    <t>./Datasheets/AmberLed - LTST-C150AKT.pdf</t>
   </si>
   <si>
     <t>F1</t>
   </si>
   <si>
-    <t xml:space="preserve">Fusible réarmable</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PTC 1A</t>
+    <t>Fusible réarmable</t>
+  </si>
+  <si>
+    <t>PTC 1A</t>
   </si>
   <si>
     <t>MF-R050</t>
@@ -176,7 +194,7 @@
     <t>./Datasheets/PTC.pdf</t>
   </si>
   <si>
-    <t xml:space="preserve">J1, J2</t>
+    <t>J1, J2</t>
   </si>
   <si>
     <t>Bornier</t>
@@ -191,28 +209,28 @@
     <t>L1</t>
   </si>
   <si>
-    <t xml:space="preserve">inductance torique</t>
-  </si>
-  <si>
-    <t xml:space="preserve">300 µH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">./Datasheets/induct - 7447060.pdf</t>
+    <t>inductance torique</t>
+  </si>
+  <si>
+    <t>300 µH</t>
+  </si>
+  <si>
+    <t>./Datasheets/induct - 7447060.pdf</t>
   </si>
   <si>
     <t>L2</t>
   </si>
   <si>
-    <t xml:space="preserve">inductance de mode commun</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5 mH</t>
+    <t>inductance de mode commun</t>
+  </si>
+  <si>
+    <t>5 mH</t>
   </si>
   <si>
     <t>SS11VL-11050</t>
   </si>
   <si>
-    <t xml:space="preserve">./Datasheets/induct - SS11VL_11050.pdf</t>
+    <t>./Datasheets/induct - SS11VL_11050.pdf</t>
   </si>
   <si>
     <t>PS1</t>
@@ -224,40 +242,40 @@
     <t>TSR_1-2433E</t>
   </si>
   <si>
-    <t xml:space="preserve">TSR 1-2433E</t>
-  </si>
-  <si>
-    <t xml:space="preserve">./Datasheets/TSR 1-2433E - tsr1e_datasheet.pdf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">R1, R5</t>
+    <t>TSR 1-2433E</t>
+  </si>
+  <si>
+    <t>./Datasheets/TSR 1-2433E - tsr1e_datasheet.pdf</t>
+  </si>
+  <si>
+    <t>R1, R5</t>
   </si>
   <si>
     <t>Résistance</t>
   </si>
   <si>
-    <t xml:space="preserve">68 R</t>
+    <t>68 R</t>
   </si>
   <si>
     <t>AC1206JR-0768RL</t>
   </si>
   <si>
-    <t xml:space="preserve">./Datasheets/68R - PYU_AC_51_ROHS_L.pdf</t>
+    <t>./Datasheets/68R - PYU_AC_51_ROHS_L.pdf</t>
   </si>
   <si>
     <t>R2</t>
   </si>
   <si>
-    <t xml:space="preserve">120 R</t>
+    <t>120 R</t>
   </si>
   <si>
     <t xml:space="preserve"> RC1206JR-07120RL</t>
   </si>
   <si>
-    <t xml:space="preserve">./Datasheets/120R - YAGEO_PYu_RC_Group_51_RoHS_L_12.pdf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">R3, R4</t>
+    <t>./Datasheets/120R - YAGEO_PYu_RC_Group_51_RoHS_L_12.pdf</t>
+  </si>
+  <si>
+    <t>R3, R4</t>
   </si>
   <si>
     <t>4k7</t>
@@ -269,7 +287,7 @@
     <t>S1</t>
   </si>
   <si>
-    <t xml:space="preserve">Switch horizontal</t>
+    <t>Switch horizontal</t>
   </si>
   <si>
     <t>SLW-874744</t>
@@ -299,13 +317,13 @@
     <t>U2</t>
   </si>
   <si>
-    <t xml:space="preserve">Module RFID</t>
+    <t>Module RFID</t>
   </si>
   <si>
     <t>RFID-RC522</t>
   </si>
   <si>
-    <t xml:space="preserve">Module SBC-RFID-RC522</t>
+    <t>Module SBC-RFID-RC522</t>
   </si>
   <si>
     <t>Inconnu</t>
@@ -314,7 +332,7 @@
     <t>U3</t>
   </si>
   <si>
-    <t xml:space="preserve">transceiver UART</t>
+    <t>transceiver UART</t>
   </si>
   <si>
     <t>MAX3485CSA_T</t>
@@ -338,7 +356,7 @@
     <t>MOV-20D470K</t>
   </si>
   <si>
-    <t xml:space="preserve">./Datasheets/Varistance - mov20d.pdf</t>
+    <t>./Datasheets/Varistance - mov20d.pdf</t>
   </si>
   <si>
     <t>total</t>
@@ -356,13 +374,13 @@
     <t>D0</t>
   </si>
   <si>
-    <t xml:space="preserve">XIAO ESP32-S3</t>
+    <t>XIAO ESP32-S3</t>
   </si>
   <si>
     <t>5V</t>
   </si>
   <si>
-    <t xml:space="preserve">dual-core 240MHz</t>
+    <t>dual-core 240MHz</t>
   </si>
   <si>
     <t>TOUCH2</t>
@@ -377,7 +395,7 @@
     <t>GND</t>
   </si>
   <si>
-    <t xml:space="preserve">8MB PSRAM</t>
+    <t>8MB PSRAM</t>
   </si>
   <si>
     <t>TOUCH3</t>
@@ -392,7 +410,7 @@
     <t>3V3</t>
   </si>
   <si>
-    <t xml:space="preserve">8MB Flash</t>
+    <t>8MB Flash</t>
   </si>
   <si>
     <t>TOUCH4</t>
@@ -509,16 +527,16 @@
     <t>GPIO0</t>
   </si>
   <si>
-    <t xml:space="preserve">XIAO ESP32-C6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dual-core 160MHz</t>
+    <t>XIAO ESP32-C6</t>
+  </si>
+  <si>
+    <t>dual-core 160MHz</t>
   </si>
   <si>
     <t>LP_GPIO2</t>
   </si>
   <si>
-    <t xml:space="preserve">512KB SRAM</t>
+    <t>512KB SRAM</t>
   </si>
   <si>
     <t>SDIO_DATA1</t>
@@ -533,7 +551,7 @@
     <t>SDIO_CMD</t>
   </si>
   <si>
-    <t xml:space="preserve">4 MB Flash</t>
+    <t>4 MB Flash</t>
   </si>
   <si>
     <t>SDIO_DATA2</t>
@@ -567,48 +585,146 @@
   </si>
   <si>
     <t>GPIO17</t>
+  </si>
+  <si>
+    <t>Atelier ELT</t>
+  </si>
+  <si>
+    <t>Ref Mouser</t>
+  </si>
+  <si>
+    <t>581-REF1020471M050K</t>
+  </si>
+  <si>
+    <t>81-GRM319R61H475KA2D</t>
+  </si>
+  <si>
+    <t>187-CL31A106MBHNNNE</t>
+  </si>
+  <si>
+    <t>81-RDEC71H226MWK1H3B</t>
+  </si>
+  <si>
+    <t>241-BX36_R1_00001</t>
+  </si>
+  <si>
+    <t>603-SMAJ28A/TR13</t>
+  </si>
+  <si>
+    <t>392-CSANAVIDISPLAY1</t>
+  </si>
+  <si>
+    <t>859-LTST-C150AKT</t>
+  </si>
+  <si>
+    <t>652-MFR050</t>
+  </si>
+  <si>
+    <t>179-TB0011-350-04GR</t>
+  </si>
+  <si>
+    <t>710-7447060</t>
+  </si>
+  <si>
+    <t>80-SS11VL-11050</t>
+  </si>
+  <si>
+    <t>495-TSR1-2433E</t>
+  </si>
+  <si>
+    <t>179-SLW8747446ARAND</t>
+  </si>
+  <si>
+    <t>713-113991114</t>
+  </si>
+  <si>
+    <t>700-MAX3485CSAT</t>
+  </si>
+  <si>
+    <t>652-MOV-20D470K</t>
+  </si>
+  <si>
+    <t>538-146153-0100</t>
+  </si>
+  <si>
+    <t>146153-0100</t>
+  </si>
+  <si>
+    <t>Antenne</t>
+  </si>
+  <si>
+    <t>J3</t>
+  </si>
+  <si>
+    <t>50ohms</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <numFmts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="2">
+    <numFmt numFmtId="44" formatCode="_-* #,##0.00\ &quot;CHF&quot;_-;\-* #,##0.00\ &quot;CHF&quot;_-;_-* &quot;-&quot;??\ &quot;CHF&quot;_-;_-@_-"/>
     <numFmt numFmtId="164" formatCode="_-* #,##0.00\ [$CHF-100C]_-;\-* #,##0.00\ [$CHF-100C]_-;_-* &quot;-&quot;??\ [$CHF-100C]_-;_-@_-"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
-      <sz val="11.000000"/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="10.000000"/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <u/>
-      <sz val="10.000000"/>
+      <sz val="10"/>
       <color theme="10"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
-      <sz val="10.000000"/>
+      <sz val="10"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <u/>
-      <sz val="11.000000"/>
+      <sz val="11"/>
       <color theme="10"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
-      <sz val="10.000000"/>
+      <sz val="10"/>
       <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF333333"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
@@ -624,69 +740,67 @@
   </fills>
   <borders count="1">
     <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="2">
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="2" borderId="0" numFmtId="44" applyNumberFormat="1" applyFont="0" applyFill="0" applyBorder="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="44" fontId="7" fillId="2" borderId="0" applyFont="0" applyFill="0" applyBorder="0"/>
   </cellStyleXfs>
   <cellXfs count="21">
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0">
-      <protection hidden="0" locked="1"/>
-    </xf>
-    <xf fontId="1" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf fontId="1" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf fontId="1" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf fontId="1" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf fontId="2" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf fontId="3" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf fontId="1" fillId="0" borderId="0" numFmtId="164" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf fontId="1" fillId="0" borderId="0" numFmtId="164" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="164" xfId="0" applyNumberFormat="1"/>
-    <xf fontId="1" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1">
-      <protection hidden="0" locked="1"/>
-    </xf>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0">
-      <protection hidden="0" locked="1"/>
-    </xf>
-    <xf fontId="4" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf fontId="4" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
-    <xf fontId="5" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf fontId="1" fillId="0" borderId="0" numFmtId="164" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" textRotation="180" vertical="center"/>
-    </xf>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="180"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
+    <cellStyle name="Monétaire" xfId="1" builtinId="4"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Currency" xfId="1" builtinId="4"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -702,7 +816,7 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math" xmlns:w="http://schemas.openxmlformats.org/wordprocessingml/2006/main">
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>12</xdr:col>
@@ -713,18 +827,24 @@
     <xdr:ext cx="3962752" cy="1844035"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="498148791" name=""/>
+        <xdr:cNvPr id="498148791" name="Image 498148790">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-0000B725B11D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill rotWithShape="1">
-        <a:blip r:embed="rId1"/>
-        <a:srcRect l="0" t="9115" r="0" b="37357"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:srcRect t="9115" b="37357"/>
         <a:stretch/>
       </xdr:blipFill>
       <xdr:spPr bwMode="auto">
-        <a:xfrm flipH="0" flipV="0">
+        <a:xfrm>
           <a:off x="6107492" y="983455"/>
           <a:ext cx="3962752" cy="1844035"/>
         </a:xfrm>
@@ -735,7 +855,7 @@
     </xdr:pic>
     <xdr:clientData/>
   </xdr:oneCellAnchor>
-  <xdr:twoCellAnchor editAs="twoCell">
+  <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>12</xdr:col>
       <xdr:colOff>473659</xdr:colOff>
@@ -750,31 +870,43 @@
     </xdr:to>
     <xdr:grpSp>
       <xdr:nvGrpSpPr>
-        <xdr:cNvPr id="0" name=""/>
+        <xdr:cNvPr id="2" name="Groupe 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvGrpSpPr/>
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr bwMode="auto">
-        <a:xfrm flipH="0" flipV="0">
-          <a:off x="6017209" y="2876876"/>
-          <a:ext cx="4412045" cy="1647498"/>
+        <a:xfrm>
+          <a:off x="6142939" y="2905451"/>
+          <a:ext cx="4412046" cy="1665243"/>
           <a:chOff x="0" y="0"/>
           <a:chExt cx="4412045" cy="1654693"/>
         </a:xfrm>
       </xdr:grpSpPr>
       <xdr:pic>
         <xdr:nvPicPr>
-          <xdr:cNvPr id="630608922" name=""/>
+          <xdr:cNvPr id="630608922" name="Image 630608921">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-00001A549625}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
           <xdr:cNvPicPr>
             <a:picLocks noChangeAspect="1"/>
           </xdr:cNvPicPr>
         </xdr:nvPicPr>
         <xdr:blipFill rotWithShape="1">
-          <a:blip r:embed="rId2"/>
-          <a:srcRect l="0" t="0" r="0" b="55890"/>
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+          <a:srcRect b="55890"/>
           <a:stretch/>
         </xdr:blipFill>
         <xdr:spPr bwMode="auto">
-          <a:xfrm flipH="0" flipV="0">
+          <a:xfrm>
             <a:off x="0" y="0"/>
             <a:ext cx="4412045" cy="1582228"/>
           </a:xfrm>
@@ -785,18 +917,24 @@
       </xdr:pic>
       <xdr:pic>
         <xdr:nvPicPr>
-          <xdr:cNvPr id="632672839" name=""/>
+          <xdr:cNvPr id="632672839" name="Image 632672838">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000047D2B525}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
           <xdr:cNvPicPr>
             <a:picLocks noChangeAspect="1"/>
           </xdr:cNvPicPr>
         </xdr:nvPicPr>
         <xdr:blipFill rotWithShape="1">
-          <a:blip r:embed="rId3"/>
-          <a:srcRect l="0" t="95959" r="0" b="0"/>
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+          <a:srcRect t="95959"/>
           <a:stretch/>
         </xdr:blipFill>
         <xdr:spPr bwMode="auto">
-          <a:xfrm flipH="0" flipV="0">
+          <a:xfrm>
             <a:off x="0" y="1509763"/>
             <a:ext cx="4412045" cy="144929"/>
           </a:xfrm>
@@ -811,291 +949,8 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/theme/theme.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
-  <a:themeElements>
-    <a:clrScheme name="Office">
-      <a:dk1>
-        <a:sysClr val="windowText" lastClr="000000"/>
-      </a:dk1>
-      <a:lt1>
-        <a:sysClr val="window" lastClr="FFFFFF"/>
-      </a:lt1>
-      <a:dk2>
-        <a:srgbClr val="1F497D"/>
-      </a:dk2>
-      <a:lt2>
-        <a:srgbClr val="EEECE1"/>
-      </a:lt2>
-      <a:accent1>
-        <a:srgbClr val="4F81BD"/>
-      </a:accent1>
-      <a:accent2>
-        <a:srgbClr val="C0504D"/>
-      </a:accent2>
-      <a:accent3>
-        <a:srgbClr val="9BBB59"/>
-      </a:accent3>
-      <a:accent4>
-        <a:srgbClr val="8064A2"/>
-      </a:accent4>
-      <a:accent5>
-        <a:srgbClr val="4BACC6"/>
-      </a:accent5>
-      <a:accent6>
-        <a:srgbClr val="F79646"/>
-      </a:accent6>
-      <a:hlink>
-        <a:srgbClr val="0000FF"/>
-      </a:hlink>
-      <a:folHlink>
-        <a:srgbClr val="800080"/>
-      </a:folHlink>
-    </a:clrScheme>
-    <a:fontScheme name="Office">
-      <a:majorFont>
-        <a:latin typeface="Cambria"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ ゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Times New Roman"/>
-        <a:font script="Hebr" typeface="Times New Roman"/>
-        <a:font script="Thai" typeface="Angsana New"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="MoolBoran"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Times New Roman"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-      </a:majorFont>
-      <a:minorFont>
-        <a:latin typeface="Calibri"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ 明朝"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Arial"/>
-        <a:font script="Hebr" typeface="Arial"/>
-        <a:font script="Thai" typeface="Cordia New"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="DaunPenh"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Arial"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-      </a:minorFont>
-    </a:fontScheme>
-    <a:fmtScheme name="Office">
-      <a:fillStyleLst>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="50000"/>
-                <a:satMod val="300000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="35000">
-              <a:schemeClr val="phClr">
-                <a:tint val="37000"/>
-                <a:satMod val="300000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:tint val="15000"/>
-                <a:satMod val="350000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="16200000" scaled="1"/>
-        </a:gradFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:shade val="51000"/>
-                <a:satMod val="130000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="80000">
-              <a:schemeClr val="phClr">
-                <a:shade val="93000"/>
-                <a:satMod val="130000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="94000"/>
-                <a:satMod val="135000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="16200000" scaled="0"/>
-        </a:gradFill>
-      </a:fillStyleLst>
-      <a:lnStyleLst>
-        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr">
-              <a:shade val="95000"/>
-              <a:satMod val="105000"/>
-            </a:schemeClr>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-        </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-        </a:ln>
-        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </a:lnStyleLst>
-      <a:effectStyleLst>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="38000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-          <a:scene3d>
-            <a:camera prst="orthographicFront">
-              <a:rot lat="0" lon="0" rev="0"/>
-            </a:camera>
-            <a:lightRig rig="threePt" dir="t">
-              <a:rot lat="0" lon="0" rev="1200000"/>
-            </a:lightRig>
-          </a:scene3d>
-          <a:sp3d>
-            <a:bevelT w="63500" h="25400"/>
-          </a:sp3d>
-        </a:effectStyle>
-      </a:effectStyleLst>
-      <a:bgFillStyleLst>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="40000"/>
-                <a:satMod val="350000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="40000">
-              <a:schemeClr val="phClr">
-                <a:tint val="45000"/>
-                <a:shade val="99000"/>
-                <a:satMod val="350000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="20000"/>
-                <a:satMod val="255000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
-          </a:path>
-        </a:gradFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="80000"/>
-                <a:satMod val="300000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="30000"/>
-                <a:satMod val="200000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
-          </a:path>
-        </a:gradFill>
-      </a:bgFillStyleLst>
-    </a:fmtScheme>
-  </a:themeElements>
-  <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
-</a:theme>
-</file>
-
-<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:p="http://schemas.openxmlformats.org/presentationml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="New Office">
       <a:dk1>
@@ -1286,918 +1141,1598 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3505CEEE-F01C-46F1-946A-EB9EC6A19C4E}">
   <sheetPr>
-    <tabColor theme="4" tint="0"/>
-    <outlinePr applyStyles="0" summaryBelow="1" summaryRight="1" showOutlineSymbols="1"/>
-    <pageSetUpPr autoPageBreaks="1" fitToPage="1"/>
+    <tabColor theme="4"/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <dimension ref="B3:M24"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col bestFit="1" customWidth="1" min="2" max="2" width="9.44140625"/>
-    <col bestFit="1" customWidth="1" min="3" max="3" width="24.29296875"/>
-    <col customWidth="1" min="4" max="4" width="24.29296875"/>
-    <col bestFit="1" customWidth="1" min="5" max="5" width="20.03125"/>
-    <col bestFit="1" customWidth="1" min="6" max="6" width="59.4140625"/>
-    <col bestFit="1" customWidth="1" min="7" max="7" width="9.75390625"/>
-    <col customWidth="1" min="8" max="8" width="9.28125"/>
-    <col bestFit="1" min="9" max="9" width="6.94140625"/>
-    <col customWidth="1" min="10" max="10" width="10.57421875"/>
-    <col bestFit="1" min="12" max="12" width="11.69140625"/>
-    <col bestFit="1" min="13" max="13" width="10.6328125"/>
+    <col min="1" max="1" width="10" customWidth="1"/>
+    <col min="2" max="2" width="9.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="24.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="24.33203125" customWidth="1"/>
+    <col min="5" max="5" width="20" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="24" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="65.109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.44140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.44140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="7.77734375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" ht="14.25">
-      <c r="B3" s="1" t="s">
+    <row r="3" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B3" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="D3" s="2" t="s">
+      <c r="C3" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="E3" s="19" t="s">
+        <v>184</v>
+      </c>
+      <c r="F3" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="G3" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="G3" s="3" t="s">
+      <c r="H3" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="H3" s="3" t="s">
+      <c r="I3" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="I3" s="3" t="s">
+      <c r="J3" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="J3" s="4" t="s">
+      <c r="K3" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="4" ht="14.25">
-      <c r="B4" s="1" t="s">
+    <row r="4" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B4" t="s">
         <v>9</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="C4" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="D4" t="s">
         <v>11</v>
       </c>
-      <c r="E4" s="6" t="s">
+      <c r="E4" s="20" t="s">
+        <v>185</v>
+      </c>
+      <c r="F4" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="F4" s="6" t="s">
+      <c r="G4" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="G4" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="H4" s="8">
+      <c r="H4" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="I4" s="7">
         <v>0.56999999999999995</v>
       </c>
-      <c r="I4" s="3">
-        <v>1</v>
-      </c>
-      <c r="J4" s="9">
-        <f>I4*H4</f>
+      <c r="J4" s="2">
+        <v>1</v>
+      </c>
+      <c r="K4" s="8">
+        <f t="shared" ref="K4:K21" si="0">J4*I4</f>
         <v>0.56999999999999995</v>
       </c>
     </row>
-    <row r="5" ht="14.25">
-      <c r="B5" s="1" t="s">
+    <row r="5" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B5" t="s">
         <v>15</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="C5" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="D5" s="1" t="s">
+      <c r="D5" t="s">
         <v>17</v>
       </c>
-      <c r="E5" s="6" t="s">
+      <c r="E5" s="20" t="s">
+        <v>186</v>
+      </c>
+      <c r="F5" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="F5" s="6" t="s">
+      <c r="G5" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="G5" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="H5" s="8">
-        <v>0.17999999999999999</v>
-      </c>
-      <c r="I5" s="3">
-        <v>1</v>
-      </c>
-      <c r="J5" s="9">
-        <f>I5*H5</f>
-        <v>0.17999999999999999</v>
-      </c>
-      <c r="M5" s="10"/>
-      <c r="N5"/>
-      <c r="O5"/>
-      <c r="P5"/>
-      <c r="Q5"/>
-    </row>
-    <row r="6" ht="14.25">
-      <c r="B6" s="1" t="s">
+      <c r="H5" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="I5" s="7">
+        <v>0.18</v>
+      </c>
+      <c r="J5" s="2">
+        <v>1</v>
+      </c>
+      <c r="K5" s="8">
+        <f t="shared" si="0"/>
+        <v>0.18</v>
+      </c>
+      <c r="M5" s="9"/>
+    </row>
+    <row r="6" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B6" t="s">
         <v>20</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="C6" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="D6" s="1" t="s">
+      <c r="D6" t="s">
         <v>21</v>
       </c>
-      <c r="E6" s="6" t="s">
+      <c r="E6" s="20" t="s">
+        <v>187</v>
+      </c>
+      <c r="F6" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="F6" s="6" t="s">
+      <c r="G6" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="G6" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="H6" s="8">
-        <v>0.20999999999999999</v>
-      </c>
-      <c r="I6" s="3">
-        <v>1</v>
-      </c>
-      <c r="J6" s="9">
-        <f>I6*H6</f>
-        <v>0.20999999999999999</v>
-      </c>
-      <c r="L6" s="10"/>
-      <c r="P6" s="1"/>
-      <c r="Q6" s="1"/>
-    </row>
-    <row r="7" ht="14.25">
-      <c r="B7" s="1" t="s">
+      <c r="H6" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="I6" s="7">
+        <v>0.21</v>
+      </c>
+      <c r="J6" s="2">
+        <v>1</v>
+      </c>
+      <c r="K6" s="8">
+        <f t="shared" si="0"/>
+        <v>0.21</v>
+      </c>
+      <c r="L6" s="9"/>
+    </row>
+    <row r="7" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B7" t="s">
         <v>24</v>
       </c>
-      <c r="C7" s="5" t="s">
+      <c r="C7" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="D7" s="1" t="s">
+      <c r="D7" t="s">
         <v>25</v>
       </c>
-      <c r="E7" s="6" t="s">
+      <c r="E7" s="20" t="s">
+        <v>188</v>
+      </c>
+      <c r="F7" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="F7" s="6" t="s">
+      <c r="G7" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="G7" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="H7" s="8">
-        <v>1.3100000000000001</v>
-      </c>
-      <c r="I7" s="3">
-        <v>1</v>
-      </c>
-      <c r="J7" s="9">
-        <f>I7*H7</f>
-        <v>1.3100000000000001</v>
-      </c>
-      <c r="L7" s="10"/>
-      <c r="P7" s="1"/>
-      <c r="Q7" s="1"/>
-    </row>
-    <row r="8" ht="14.25">
-      <c r="B8" s="1" t="s">
+      <c r="H7" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="I7" s="7">
+        <v>1.31</v>
+      </c>
+      <c r="J7" s="2">
+        <v>1</v>
+      </c>
+      <c r="K7" s="8">
+        <f t="shared" si="0"/>
+        <v>1.31</v>
+      </c>
+      <c r="L7" s="9"/>
+    </row>
+    <row r="8" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B8" t="s">
         <v>28</v>
       </c>
-      <c r="C8" s="11" t="s">
+      <c r="C8" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="D8" s="1" t="s">
+      <c r="D8" t="s">
         <v>30</v>
       </c>
-      <c r="E8" s="6" t="s">
+      <c r="E8" s="20" t="s">
+        <v>189</v>
+      </c>
+      <c r="F8" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="F8" s="6" t="s">
+      <c r="G8" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="G8" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="H8" s="8">
+      <c r="H8" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="I8" s="7">
         <v>0.28999999999999998</v>
       </c>
-      <c r="I8" s="3">
-        <v>1</v>
-      </c>
-      <c r="J8" s="9">
-        <f>I8*H8</f>
+      <c r="J8" s="2">
+        <v>1</v>
+      </c>
+      <c r="K8" s="8">
+        <f t="shared" si="0"/>
         <v>0.28999999999999998</v>
       </c>
-      <c r="P8" s="1"/>
-      <c r="Q8" s="1"/>
-    </row>
-    <row r="9" ht="14.25">
-      <c r="B9" s="1" t="s">
+    </row>
+    <row r="9" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B9" t="s">
         <v>33</v>
       </c>
-      <c r="C9" s="5" t="s">
+      <c r="C9" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="D9" s="12" t="s">
+      <c r="D9" t="s">
         <v>35</v>
       </c>
-      <c r="E9" s="13" t="s">
+      <c r="E9" s="20" t="s">
+        <v>190</v>
+      </c>
+      <c r="F9" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="F9" s="14" t="s">
+      <c r="G9" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="G9" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="H9" s="8">
+      <c r="H9" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="I9" s="7">
         <v>0.11</v>
       </c>
-      <c r="I9" s="3">
-        <v>1</v>
-      </c>
-      <c r="J9" s="9">
-        <f>I9*H9</f>
+      <c r="J9" s="2">
+        <v>1</v>
+      </c>
+      <c r="K9" s="8">
+        <f t="shared" si="0"/>
         <v>0.11</v>
       </c>
-      <c r="P9" s="1"/>
-      <c r="Q9" s="1"/>
-    </row>
-    <row r="10" ht="14.25">
-      <c r="B10" s="1" t="s">
+    </row>
+    <row r="10" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B10" t="s">
         <v>38</v>
       </c>
-      <c r="C10" s="5" t="s">
+      <c r="C10" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="D10" s="1" t="s">
+      <c r="D10" t="s">
         <v>40</v>
       </c>
-      <c r="E10" s="6" t="s">
+      <c r="E10" s="20" t="s">
+        <v>191</v>
+      </c>
+      <c r="F10" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="F10" s="6"/>
-      <c r="G10" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="H10" s="8">
-        <v>5.3600000000000003</v>
-      </c>
-      <c r="I10" s="3">
-        <v>1</v>
-      </c>
-      <c r="J10" s="9">
-        <f>I10*H10</f>
-        <v>5.3600000000000003</v>
-      </c>
-      <c r="P10" s="1"/>
-      <c r="Q10" s="1"/>
-    </row>
-    <row r="11" ht="14.25">
-      <c r="B11" s="1" t="s">
+      <c r="G10" s="5"/>
+      <c r="H10" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="I10" s="7">
+        <v>5.36</v>
+      </c>
+      <c r="J10" s="2">
+        <v>1</v>
+      </c>
+      <c r="K10" s="8">
+        <f t="shared" si="0"/>
+        <v>5.36</v>
+      </c>
+    </row>
+    <row r="11" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B11" t="s">
         <v>42</v>
       </c>
-      <c r="C11" s="5" t="s">
+      <c r="C11" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="D11" s="1" t="s">
+      <c r="D11" t="s">
         <v>44</v>
       </c>
-      <c r="E11" s="6" t="s">
+      <c r="E11" t="s">
+        <v>192</v>
+      </c>
+      <c r="F11" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="F11" s="6" t="s">
+      <c r="G11" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="G11" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="H11" s="8">
+      <c r="H11" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="I11" s="7">
         <v>0.11</v>
       </c>
-      <c r="I11" s="3">
+      <c r="J11" s="2">
         <v>2</v>
       </c>
-      <c r="J11" s="9">
-        <f>I11*H11</f>
+      <c r="K11" s="8">
+        <f t="shared" si="0"/>
         <v>0.22</v>
       </c>
-      <c r="P11" s="1"/>
-      <c r="Q11" s="1"/>
-    </row>
-    <row r="12" ht="14.25">
-      <c r="B12" s="1" t="s">
+    </row>
+    <row r="12" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B12" t="s">
         <v>47</v>
       </c>
-      <c r="C12" s="5" t="s">
+      <c r="C12" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="D12" s="1" t="s">
+      <c r="D12" t="s">
         <v>49</v>
       </c>
-      <c r="E12" s="6" t="s">
+      <c r="E12" s="20" t="s">
+        <v>193</v>
+      </c>
+      <c r="F12" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="F12" s="6" t="s">
+      <c r="G12" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="G12" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="H12" s="8">
-        <v>0.32000000000000001</v>
-      </c>
-      <c r="I12" s="3">
-        <v>1</v>
-      </c>
-      <c r="J12" s="9">
-        <f>I12*H12</f>
-        <v>0.32000000000000001</v>
-      </c>
-      <c r="P12" s="1"/>
-      <c r="Q12" s="1"/>
-    </row>
-    <row r="13" ht="14.25">
-      <c r="B13" s="1" t="s">
+      <c r="H12" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="I12" s="7">
+        <v>0.32</v>
+      </c>
+      <c r="J12" s="2">
+        <v>1</v>
+      </c>
+      <c r="K12" s="8">
+        <f t="shared" si="0"/>
+        <v>0.32</v>
+      </c>
+    </row>
+    <row r="13" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B13" t="s">
         <v>52</v>
       </c>
-      <c r="C13" s="5" t="s">
+      <c r="C13" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="D13" s="1" t="s">
+      <c r="D13" t="s">
         <v>54</v>
       </c>
-      <c r="E13" s="6" t="s">
+      <c r="E13" s="20" t="s">
+        <v>194</v>
+      </c>
+      <c r="F13" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="F13" s="6" t="s">
+      <c r="G13" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="G13" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="H13" s="8">
-        <v>0.70999999999999996</v>
-      </c>
-      <c r="I13" s="3">
+      <c r="H13" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="I13" s="7">
+        <v>0.71</v>
+      </c>
+      <c r="J13" s="2">
         <v>2</v>
       </c>
-      <c r="J13" s="9">
-        <f>I13*H13</f>
-        <v>1.4199999999999999</v>
-      </c>
-      <c r="P13" s="1"/>
-      <c r="Q13" s="1"/>
-    </row>
-    <row r="14" ht="14.25">
-      <c r="B14" s="1" t="s">
+      <c r="K13" s="8">
+        <f t="shared" si="0"/>
+        <v>1.42</v>
+      </c>
+    </row>
+    <row r="14" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B14" t="s">
         <v>56</v>
       </c>
-      <c r="C14" s="15" t="s">
+      <c r="C14" t="s">
         <v>57</v>
       </c>
-      <c r="D14" s="1" t="s">
+      <c r="D14" t="s">
         <v>58</v>
       </c>
-      <c r="E14" s="13">
+      <c r="E14" s="20" t="s">
+        <v>195</v>
+      </c>
+      <c r="F14" s="10">
         <v>7447060</v>
       </c>
-      <c r="F14" s="14" t="s">
+      <c r="G14" s="11" t="s">
         <v>59</v>
       </c>
-      <c r="G14" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="H14" s="8">
-        <v>2.0600000000000001</v>
-      </c>
-      <c r="I14" s="3">
-        <v>1</v>
-      </c>
-      <c r="J14" s="9">
-        <f>I14*H14</f>
-        <v>2.0600000000000001</v>
-      </c>
-      <c r="P14" s="1"/>
-      <c r="Q14" s="1"/>
-    </row>
-    <row r="15" ht="14.25">
-      <c r="B15" s="1" t="s">
+      <c r="H14" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="I14" s="7">
+        <v>2.06</v>
+      </c>
+      <c r="J14" s="2">
+        <v>1</v>
+      </c>
+      <c r="K14" s="8">
+        <f t="shared" si="0"/>
+        <v>2.06</v>
+      </c>
+    </row>
+    <row r="15" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B15" t="s">
         <v>60</v>
       </c>
-      <c r="C15" s="5" t="s">
+      <c r="C15" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="D15" s="1" t="s">
+      <c r="D15" t="s">
         <v>62</v>
       </c>
-      <c r="E15" s="6" t="s">
+      <c r="E15" s="20" t="s">
+        <v>196</v>
+      </c>
+      <c r="F15" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="F15" s="6" t="s">
+      <c r="G15" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="G15" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="H15" s="8">
+      <c r="H15" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="I15" s="7">
         <v>1.49</v>
       </c>
-      <c r="I15" s="3">
-        <v>1</v>
-      </c>
-      <c r="J15" s="9">
-        <f>I15*H15</f>
+      <c r="J15" s="2">
+        <v>1</v>
+      </c>
+      <c r="K15" s="8">
+        <f t="shared" si="0"/>
         <v>1.49</v>
       </c>
-      <c r="P15" s="1"/>
-      <c r="Q15" s="1"/>
-    </row>
-    <row r="16" ht="14.25">
-      <c r="B16" s="1" t="s">
+    </row>
+    <row r="16" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B16" t="s">
         <v>65</v>
       </c>
-      <c r="C16" s="5" t="s">
+      <c r="C16" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="D16" s="1" t="s">
+      <c r="D16" t="s">
         <v>67</v>
       </c>
-      <c r="E16" s="6" t="s">
+      <c r="E16" s="20" t="s">
+        <v>197</v>
+      </c>
+      <c r="F16" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="F16" s="6" t="s">
+      <c r="G16" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="G16" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="H16" s="8">
-        <v>2.9199999999999999</v>
-      </c>
-      <c r="I16" s="3">
-        <v>1</v>
-      </c>
-      <c r="J16" s="9">
-        <f>I16*H16</f>
-        <v>2.9199999999999999</v>
-      </c>
-      <c r="P16" s="1"/>
-      <c r="Q16" s="1"/>
-    </row>
-    <row r="17" ht="14.25">
-      <c r="B17" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="C17" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="D17" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="E17" s="6" t="s">
-        <v>73</v>
-      </c>
-      <c r="F17" s="6" t="s">
-        <v>74</v>
-      </c>
-      <c r="G17" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="H17" s="8">
-        <v>8.0000000000000002e-002</v>
-      </c>
-      <c r="I17" s="3">
-        <v>2</v>
-      </c>
-      <c r="J17" s="9">
-        <f>I17*H17</f>
-        <v>0.16</v>
-      </c>
-      <c r="P17" s="1"/>
-      <c r="Q17" s="1"/>
-    </row>
-    <row r="18" ht="14.25">
-      <c r="B18" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="C18" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="D18" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="E18" s="6" t="s">
-        <v>77</v>
-      </c>
-      <c r="F18" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="G18" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="H18" s="8">
-        <v>8.0000000000000002e-002</v>
-      </c>
-      <c r="I18" s="3">
-        <v>1</v>
-      </c>
-      <c r="J18" s="9">
-        <f>I18*H18</f>
-        <v>8.0000000000000002e-002</v>
-      </c>
-      <c r="P18" s="1"/>
-      <c r="Q18" s="1"/>
-    </row>
-    <row r="19" ht="14.25">
-      <c r="B19" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="C19" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="D19" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="E19" s="6" t="s">
-        <v>81</v>
-      </c>
-      <c r="F19" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="G19" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="H19" s="8">
-        <v>8.0000000000000002e-002</v>
-      </c>
-      <c r="I19" s="3">
-        <v>2</v>
-      </c>
-      <c r="J19" s="9">
-        <f>I19*H19</f>
-        <v>0.16</v>
-      </c>
-      <c r="P19" s="1"/>
-      <c r="Q19" s="1"/>
-    </row>
-    <row r="20" ht="14.25">
-      <c r="B20" s="1" t="s">
+      <c r="H16" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="I16" s="7">
+        <v>2.92</v>
+      </c>
+      <c r="J16" s="2">
+        <v>1</v>
+      </c>
+      <c r="K16" s="8">
+        <f t="shared" si="0"/>
+        <v>2.92</v>
+      </c>
+    </row>
+    <row r="17" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B17" t="s">
         <v>82</v>
       </c>
-      <c r="C20" s="5" t="s">
+      <c r="C17" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="D20" s="1" t="s">
+      <c r="D17" t="s">
         <v>84</v>
       </c>
-      <c r="E20" s="6" t="s">
+      <c r="E17" s="20" t="s">
+        <v>198</v>
+      </c>
+      <c r="F17" s="5" t="s">
         <v>85</v>
       </c>
-      <c r="F20" s="6" t="s">
+      <c r="G17" s="5" t="s">
         <v>86</v>
       </c>
-      <c r="G20" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="H20" s="8">
-        <v>0.40999999999999998</v>
-      </c>
-      <c r="I20" s="3">
-        <v>1</v>
-      </c>
-      <c r="J20" s="9">
-        <f>I20*H20</f>
-        <v>0.40999999999999998</v>
-      </c>
-      <c r="P20" s="1"/>
-      <c r="Q20" s="1"/>
-    </row>
-    <row r="21" ht="14.25">
-      <c r="B21" s="1" t="s">
+      <c r="H17" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="I17" s="7">
+        <v>0.41</v>
+      </c>
+      <c r="J17" s="2">
+        <v>1</v>
+      </c>
+      <c r="K17" s="8">
+        <f t="shared" si="0"/>
+        <v>0.41</v>
+      </c>
+    </row>
+    <row r="18" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B18" t="s">
         <v>87</v>
       </c>
-      <c r="C21" s="5" t="s">
+      <c r="C18" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="D21" s="1" t="s">
+      <c r="D18" t="s">
         <v>89</v>
       </c>
-      <c r="E21" s="6" t="s">
+      <c r="E18" s="20" t="s">
+        <v>199</v>
+      </c>
+      <c r="F18" s="5" t="s">
         <v>90</v>
       </c>
-      <c r="F21" s="6" t="s">
+      <c r="G18" s="5" t="s">
         <v>91</v>
       </c>
-      <c r="G21" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="H21" s="8">
-        <v>5.9400000000000004</v>
-      </c>
-      <c r="I21" s="3">
-        <v>1</v>
-      </c>
-      <c r="J21" s="9">
-        <f>I21*H21</f>
-        <v>5.9400000000000004</v>
-      </c>
-      <c r="P21" s="1"/>
-      <c r="Q21" s="1"/>
-    </row>
-    <row r="22" ht="14.25">
-      <c r="B22" s="1" t="s">
+      <c r="H18" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="I18" s="7">
+        <v>5.94</v>
+      </c>
+      <c r="J18" s="2">
+        <v>1</v>
+      </c>
+      <c r="K18" s="8">
+        <f t="shared" si="0"/>
+        <v>5.94</v>
+      </c>
+    </row>
+    <row r="19" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B19" t="s">
         <v>92</v>
       </c>
-      <c r="C22" s="5" t="s">
+      <c r="C19" s="4" t="s">
         <v>93</v>
       </c>
-      <c r="D22" s="1" t="s">
+      <c r="D19" t="s">
         <v>94</v>
       </c>
-      <c r="E22" s="5" t="s">
+      <c r="F19" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="F22" s="6"/>
-      <c r="G22" s="16" t="s">
+      <c r="G19" s="5"/>
+      <c r="H19" s="12" t="s">
         <v>96</v>
       </c>
-      <c r="H22" s="8">
+      <c r="I19" s="7">
         <v>8</v>
       </c>
-      <c r="I22" s="3">
-        <v>1</v>
-      </c>
-      <c r="J22" s="9">
-        <f>I22*H22</f>
+      <c r="J19" s="2">
+        <v>1</v>
+      </c>
+      <c r="K19" s="8">
+        <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="P22" s="1"/>
-      <c r="Q22" s="1"/>
-    </row>
-    <row r="23" ht="14.25">
-      <c r="B23" s="1" t="s">
+    </row>
+    <row r="20" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B20" t="s">
         <v>97</v>
       </c>
-      <c r="C23" s="5" t="s">
+      <c r="C20" s="4" t="s">
         <v>98</v>
       </c>
-      <c r="D23" s="1" t="s">
+      <c r="D20" t="s">
         <v>99</v>
       </c>
-      <c r="E23" s="6" t="s">
+      <c r="E20" s="20" t="s">
+        <v>200</v>
+      </c>
+      <c r="F20" s="5" t="s">
         <v>100</v>
       </c>
-      <c r="F23" s="6" t="s">
+      <c r="G20" s="5" t="s">
         <v>101</v>
       </c>
-      <c r="G23" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="H23" s="8">
-        <v>5.0700000000000003</v>
-      </c>
-      <c r="I23" s="3">
-        <v>1</v>
-      </c>
-      <c r="J23" s="9">
-        <f>I23*H23</f>
-        <v>5.0700000000000003</v>
-      </c>
-      <c r="P23" s="1"/>
-      <c r="Q23" s="1"/>
-    </row>
-    <row r="24" ht="14.25">
-      <c r="B24" s="1" t="s">
+      <c r="H20" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="I20" s="7">
+        <v>5.07</v>
+      </c>
+      <c r="J20" s="2">
+        <v>1</v>
+      </c>
+      <c r="K20" s="8">
+        <f t="shared" si="0"/>
+        <v>5.07</v>
+      </c>
+    </row>
+    <row r="21" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B21" t="s">
         <v>102</v>
       </c>
-      <c r="C24" s="5" t="s">
+      <c r="C21" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="D24" s="1" t="s">
+      <c r="D21" t="s">
         <v>104</v>
       </c>
-      <c r="E24" s="6" t="s">
+      <c r="E21" s="20" t="s">
+        <v>201</v>
+      </c>
+      <c r="F21" s="5" t="s">
         <v>105</v>
       </c>
-      <c r="F24" s="6" t="s">
+      <c r="G21" s="5" t="s">
         <v>106</v>
       </c>
-      <c r="G24" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="H24" s="8">
-        <v>0.67000000000000004</v>
-      </c>
-      <c r="I24" s="3">
-        <v>1</v>
-      </c>
-      <c r="J24" s="9">
-        <f>I24*H24</f>
-        <v>0.67000000000000004</v>
-      </c>
-      <c r="P24" s="1"/>
-      <c r="Q24" s="1"/>
-    </row>
-    <row r="25" ht="14.25">
-      <c r="P25" s="1"/>
-      <c r="Q25" s="1"/>
-    </row>
-    <row r="26" ht="14.25">
-      <c r="I26" s="5" t="s">
+      <c r="H21" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="I21" s="7">
+        <v>0.67</v>
+      </c>
+      <c r="J21" s="2">
+        <v>1</v>
+      </c>
+      <c r="K21" s="8">
+        <f t="shared" si="0"/>
+        <v>0.67</v>
+      </c>
+    </row>
+    <row r="22" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B22" s="19" t="s">
+        <v>205</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="D22" s="19" t="s">
+        <v>206</v>
+      </c>
+      <c r="E22" s="20" t="s">
+        <v>202</v>
+      </c>
+      <c r="F22" s="20" t="s">
+        <v>203</v>
+      </c>
+      <c r="H22" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="I22" s="7">
+        <v>1.96</v>
+      </c>
+      <c r="J22" s="2">
+        <v>1</v>
+      </c>
+      <c r="K22" s="8">
+        <f t="shared" ref="K22" si="1">J22*I22</f>
+        <v>1.96</v>
+      </c>
+    </row>
+    <row r="24" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="J24" s="4" t="s">
         <v>107</v>
       </c>
-      <c r="J26" s="17">
-        <f>SUM(J4:J24)</f>
-        <v>36.950000000000003</v>
-      </c>
-      <c r="P26" s="1"/>
-      <c r="Q26" s="1"/>
+      <c r="K24" s="13">
+        <f>SUM(K4:K21)</f>
+        <v>36.550000000000004</v>
+      </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink r:id="rId1" ref="E4" tooltip=""/>
-    <hyperlink r:id="rId2" ref="F4" tooltip=""/>
-    <hyperlink r:id="rId3" ref="E5" tooltip=""/>
-    <hyperlink r:id="rId4" ref="F5" tooltip=""/>
-    <hyperlink r:id="rId5" ref="E6" tooltip=""/>
-    <hyperlink r:id="rId6" ref="F6" tooltip=""/>
-    <hyperlink r:id="rId7" ref="E7" tooltip=""/>
-    <hyperlink r:id="rId8" ref="F7" tooltip=""/>
-    <hyperlink r:id="rId9" ref="E8" tooltip=""/>
-    <hyperlink r:id="rId10" ref="F8" tooltip=""/>
-    <hyperlink r:id="rId11" ref="E9" tooltip=""/>
-    <hyperlink r:id="rId12" ref="F9" tooltip=""/>
-    <hyperlink r:id="rId13" ref="E10" tooltip=""/>
-    <hyperlink r:id="rId14" ref="E11" tooltip=""/>
-    <hyperlink r:id="rId15" ref="F11" tooltip=""/>
-    <hyperlink r:id="rId16" ref="E12" tooltip=""/>
-    <hyperlink r:id="rId17" ref="F12" tooltip=""/>
-    <hyperlink r:id="rId18" ref="E13" tooltip=""/>
-    <hyperlink r:id="rId19" ref="F13" tooltip=""/>
-    <hyperlink r:id="rId20" ref="E14" tooltip=""/>
-    <hyperlink r:id="rId21" ref="F14" tooltip=""/>
-    <hyperlink r:id="rId22" ref="E15" tooltip=""/>
-    <hyperlink r:id="rId23" ref="F15" tooltip=""/>
-    <hyperlink r:id="rId24" ref="E16" tooltip=""/>
-    <hyperlink r:id="rId25" ref="F16" tooltip=""/>
-    <hyperlink r:id="rId26" ref="E17" tooltip=""/>
-    <hyperlink r:id="rId27" ref="F17" tooltip=""/>
-    <hyperlink r:id="rId28" ref="E18" tooltip=""/>
-    <hyperlink r:id="rId29" ref="F18" tooltip=""/>
-    <hyperlink r:id="rId30" ref="E19" tooltip=""/>
-    <hyperlink r:id="rId29" ref="F19" tooltip=""/>
-    <hyperlink r:id="rId31" ref="E20" tooltip=""/>
-    <hyperlink r:id="rId32" ref="F20" tooltip=""/>
-    <hyperlink r:id="rId33" ref="E21" tooltip=""/>
-    <hyperlink r:id="rId34" ref="F21" tooltip=""/>
-    <hyperlink r:id="rId35" ref="E23" tooltip=""/>
-    <hyperlink r:id="rId36" ref="F23" tooltip=""/>
-    <hyperlink r:id="rId37" ref="E24" tooltip=""/>
-    <hyperlink r:id="rId38" ref="F24" tooltip=""/>
+    <hyperlink ref="F4" r:id="rId1" xr:uid="{53132534-13D2-49DD-8A33-C78591ECA109}"/>
+    <hyperlink ref="G4" r:id="rId2" xr:uid="{2B843AE8-CCE3-4FA7-B03B-4903228CD231}"/>
+    <hyperlink ref="F5" r:id="rId3" xr:uid="{ADE0ACE8-EB75-422E-B717-4DB7FC89050E}"/>
+    <hyperlink ref="G5" r:id="rId4" xr:uid="{A3954C26-9ADA-4B58-80A7-C243E3DA2E26}"/>
+    <hyperlink ref="F6" r:id="rId5" xr:uid="{77B43A1B-BB58-410E-B10A-6A80348C61E2}"/>
+    <hyperlink ref="G6" r:id="rId6" xr:uid="{31F77AB8-319D-4664-9311-B58D8540ABF5}"/>
+    <hyperlink ref="F7" r:id="rId7" xr:uid="{0A81A5A9-F299-4044-BC0A-5D0D01D7B700}"/>
+    <hyperlink ref="G7" r:id="rId8" xr:uid="{432F5097-3D5A-4701-AFBB-723618CACA33}"/>
+    <hyperlink ref="F8" r:id="rId9" xr:uid="{C33275E7-907A-4DDD-92E4-3E482B57CD34}"/>
+    <hyperlink ref="G8" r:id="rId10" xr:uid="{733EB9B5-7811-4A14-8120-C0DBE5666E71}"/>
+    <hyperlink ref="F9" r:id="rId11" xr:uid="{EB2627D6-B2B5-47F1-99A9-627EE80664C4}"/>
+    <hyperlink ref="G9" r:id="rId12" xr:uid="{91CA2943-2CE4-43F4-8735-E3E8F7B9743F}"/>
+    <hyperlink ref="F10" r:id="rId13" xr:uid="{644B3800-B1BA-4BB3-B0AE-4C8B08F379FE}"/>
+    <hyperlink ref="F11" r:id="rId14" xr:uid="{F49BBBAA-FF2F-4FFB-A379-CA09C1FA8EA0}"/>
+    <hyperlink ref="G11" r:id="rId15" xr:uid="{02B016CE-31FA-4445-9827-01AC1DA04C28}"/>
+    <hyperlink ref="F12" r:id="rId16" xr:uid="{E8B4B08D-2EDB-46F3-A3EB-2EBD2E496F5D}"/>
+    <hyperlink ref="G12" r:id="rId17" xr:uid="{E83DB9BF-9498-44CA-B701-31C78933FF26}"/>
+    <hyperlink ref="F13" r:id="rId18" xr:uid="{AA95AA80-CCC8-465D-A6EF-9A224E15A70A}"/>
+    <hyperlink ref="G13" r:id="rId19" xr:uid="{3E0AEF2F-A77B-4F26-9A55-D4860224D883}"/>
+    <hyperlink ref="F14" r:id="rId20" display="https://www.mouser.fr/ProductDetail/Wurth-Elektronik/7447060?qs=sGAEpiMZZMv126LJFLh8y7bZMRioh4ww7S2La6H8kL0%3D" xr:uid="{3FC050B6-674B-4FD8-8F65-ACA2BA3DD500}"/>
+    <hyperlink ref="G14" r:id="rId21" xr:uid="{4E33E382-85A9-487A-A14B-8734DBD73244}"/>
+    <hyperlink ref="F15" r:id="rId22" xr:uid="{53F82882-A0E8-40D1-BBFF-4EA6DBE20EC3}"/>
+    <hyperlink ref="G15" r:id="rId23" xr:uid="{B1052B83-EAD9-4B5D-AEFA-8D44789227CF}"/>
+    <hyperlink ref="F16" r:id="rId24" xr:uid="{A2CAB422-594C-4C33-99D1-99953319FBDC}"/>
+    <hyperlink ref="G16" r:id="rId25" xr:uid="{EEE1D3E2-622D-488E-B985-2D20410C6C5A}"/>
+    <hyperlink ref="F17" r:id="rId26" xr:uid="{3A5793DE-0BB2-47E9-BA4A-1A4FA1482482}"/>
+    <hyperlink ref="G17" r:id="rId27" xr:uid="{A00DD2AD-6785-47CF-8C7F-AE2EFCE2864F}"/>
+    <hyperlink ref="F18" r:id="rId28" xr:uid="{B2476BE3-13A9-40F6-80A9-BF0216C64B4F}"/>
+    <hyperlink ref="G18" r:id="rId29" xr:uid="{9D923610-A638-4904-A162-F2667BF66E04}"/>
+    <hyperlink ref="F20" r:id="rId30" xr:uid="{17BCDB08-3BEF-45F3-838C-73CFF2F70580}"/>
+    <hyperlink ref="G20" r:id="rId31" xr:uid="{82E43466-A59D-4397-BE95-3268504BF5FC}"/>
+    <hyperlink ref="F21" r:id="rId32" xr:uid="{4D7911BF-3938-44F6-A9A0-F4CC7874BB8A}"/>
+    <hyperlink ref="G21" r:id="rId33" xr:uid="{30FF03F3-020C-4BCB-A0BA-880475F3ADF4}"/>
   </hyperlinks>
-  <printOptions headings="0" gridLines="0"/>
-  <pageMargins left="0.25196850393700787" right="0.25196850393700787" top="0.75196850393700787" bottom="0.75196850393700787" header="0.29999999999999999" footer="0.29999999999999999"/>
-  <pageSetup paperSize="9" scale="98" firstPageNumber="1" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="landscape" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="1" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
-  <headerFooter/>
+  <pageMargins left="0.25196850393700787" right="0.25196850393700787" top="0.75196850393700787" bottom="0.75196850393700787" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" scale="98" orientation="landscape" useFirstPageNumber="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
-    <tabColor theme="9" tint="0"/>
-    <outlinePr applyStyles="0" summaryBelow="1" summaryRight="1" showOutlineSymbols="1"/>
-    <pageSetUpPr autoPageBreaks="1" fitToPage="0"/>
+    <tabColor theme="4"/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <sheetFormatPr defaultRowHeight="14.25"/>
-  <sheetData/>
-  <printOptions headings="0" gridLines="0"/>
-  <pageMargins left="0.70078740157480324" right="0.70078740157480324" top="0.75196850393700787" bottom="0.75196850393700787" header="0.29999999999999999" footer="0.29999999999999999"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
-  <headerFooter/>
+  <dimension ref="A3:M26"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="10" customWidth="1"/>
+    <col min="2" max="2" width="9.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="24.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="24.33203125" customWidth="1"/>
+    <col min="5" max="5" width="20" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="59.44140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.77734375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.33203125" customWidth="1"/>
+    <col min="9" max="9" width="6.88671875" bestFit="1"/>
+    <col min="10" max="10" width="10.5546875" customWidth="1"/>
+    <col min="12" max="12" width="11.6640625" bestFit="1"/>
+    <col min="13" max="13" width="10.6640625" bestFit="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="G4" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="H4" s="7">
+        <v>0.56999999999999995</v>
+      </c>
+      <c r="I4" s="2">
+        <v>1</v>
+      </c>
+      <c r="J4" s="8">
+        <f t="shared" ref="J4:J24" si="0">I4*H4</f>
+        <v>0.56999999999999995</v>
+      </c>
+    </row>
+    <row r="5" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D5" t="s">
+        <v>17</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="G5" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="H5" s="7">
+        <v>0.18</v>
+      </c>
+      <c r="I5" s="2">
+        <v>1</v>
+      </c>
+      <c r="J5" s="8">
+        <f t="shared" si="0"/>
+        <v>0.18</v>
+      </c>
+      <c r="M5" s="9"/>
+    </row>
+    <row r="6" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="G6" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="H6" s="7">
+        <v>0.21</v>
+      </c>
+      <c r="I6" s="2">
+        <v>1</v>
+      </c>
+      <c r="J6" s="8">
+        <f t="shared" si="0"/>
+        <v>0.21</v>
+      </c>
+      <c r="L6" s="9"/>
+    </row>
+    <row r="7" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D7" t="s">
+        <v>25</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="G7" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="H7" s="7">
+        <v>1.31</v>
+      </c>
+      <c r="I7" s="2">
+        <v>1</v>
+      </c>
+      <c r="J7" s="8">
+        <f t="shared" si="0"/>
+        <v>1.31</v>
+      </c>
+      <c r="L7" s="9"/>
+    </row>
+    <row r="8" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B8" t="s">
+        <v>28</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="D8" t="s">
+        <v>30</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="F8" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="G8" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="H8" s="7">
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="I8" s="2">
+        <v>1</v>
+      </c>
+      <c r="J8" s="8">
+        <f t="shared" si="0"/>
+        <v>0.28999999999999998</v>
+      </c>
+    </row>
+    <row r="9" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B9" t="s">
+        <v>33</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="D9" t="s">
+        <v>35</v>
+      </c>
+      <c r="E9" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="F9" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="G9" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="H9" s="7">
+        <v>0.11</v>
+      </c>
+      <c r="I9" s="2">
+        <v>1</v>
+      </c>
+      <c r="J9" s="8">
+        <f t="shared" si="0"/>
+        <v>0.11</v>
+      </c>
+    </row>
+    <row r="10" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B10" t="s">
+        <v>38</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="D10" t="s">
+        <v>40</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="F10" s="5"/>
+      <c r="G10" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="H10" s="7">
+        <v>5.36</v>
+      </c>
+      <c r="I10" s="2">
+        <v>1</v>
+      </c>
+      <c r="J10" s="8">
+        <f t="shared" si="0"/>
+        <v>5.36</v>
+      </c>
+    </row>
+    <row r="11" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B11" t="s">
+        <v>42</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="D11" t="s">
+        <v>44</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="G11" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="H11" s="7">
+        <v>0.11</v>
+      </c>
+      <c r="I11" s="2">
+        <v>2</v>
+      </c>
+      <c r="J11" s="8">
+        <f t="shared" si="0"/>
+        <v>0.22</v>
+      </c>
+    </row>
+    <row r="12" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B12" t="s">
+        <v>47</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="D12" t="s">
+        <v>49</v>
+      </c>
+      <c r="E12" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="F12" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="G12" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="H12" s="7">
+        <v>0.32</v>
+      </c>
+      <c r="I12" s="2">
+        <v>1</v>
+      </c>
+      <c r="J12" s="8">
+        <f t="shared" si="0"/>
+        <v>0.32</v>
+      </c>
+    </row>
+    <row r="13" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B13" t="s">
+        <v>52</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="D13" t="s">
+        <v>54</v>
+      </c>
+      <c r="E13" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="F13" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="G13" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="H13" s="7">
+        <v>0.71</v>
+      </c>
+      <c r="I13" s="2">
+        <v>2</v>
+      </c>
+      <c r="J13" s="8">
+        <f t="shared" si="0"/>
+        <v>1.42</v>
+      </c>
+    </row>
+    <row r="14" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B14" t="s">
+        <v>56</v>
+      </c>
+      <c r="C14" t="s">
+        <v>57</v>
+      </c>
+      <c r="D14" t="s">
+        <v>58</v>
+      </c>
+      <c r="E14" s="10">
+        <v>7447060</v>
+      </c>
+      <c r="F14" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="G14" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="H14" s="7">
+        <v>2.06</v>
+      </c>
+      <c r="I14" s="2">
+        <v>1</v>
+      </c>
+      <c r="J14" s="8">
+        <f t="shared" si="0"/>
+        <v>2.06</v>
+      </c>
+    </row>
+    <row r="15" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B15" t="s">
+        <v>60</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="D15" t="s">
+        <v>62</v>
+      </c>
+      <c r="E15" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="F15" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="G15" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="H15" s="7">
+        <v>1.49</v>
+      </c>
+      <c r="I15" s="2">
+        <v>1</v>
+      </c>
+      <c r="J15" s="8">
+        <f t="shared" si="0"/>
+        <v>1.49</v>
+      </c>
+    </row>
+    <row r="16" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B16" t="s">
+        <v>65</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="D16" t="s">
+        <v>67</v>
+      </c>
+      <c r="E16" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="F16" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="G16" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="H16" s="7">
+        <v>2.92</v>
+      </c>
+      <c r="I16" s="2">
+        <v>1</v>
+      </c>
+      <c r="J16" s="8">
+        <f t="shared" si="0"/>
+        <v>2.92</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A17" s="17" t="s">
+        <v>183</v>
+      </c>
+      <c r="B17" t="s">
+        <v>70</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="D17" t="s">
+        <v>72</v>
+      </c>
+      <c r="E17" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="F17" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="G17" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="H17" s="7">
+        <v>0.08</v>
+      </c>
+      <c r="I17" s="2">
+        <v>2</v>
+      </c>
+      <c r="J17" s="8">
+        <f t="shared" si="0"/>
+        <v>0.16</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A18" s="18"/>
+      <c r="B18" t="s">
+        <v>75</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="D18" t="s">
+        <v>76</v>
+      </c>
+      <c r="E18" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="F18" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="G18" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="H18" s="7">
+        <v>0.08</v>
+      </c>
+      <c r="I18" s="2">
+        <v>1</v>
+      </c>
+      <c r="J18" s="8">
+        <f t="shared" si="0"/>
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A19" s="18"/>
+      <c r="B19" t="s">
+        <v>79</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="D19" t="s">
+        <v>80</v>
+      </c>
+      <c r="E19" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="F19" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="G19" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="H19" s="7">
+        <v>0.08</v>
+      </c>
+      <c r="I19" s="2">
+        <v>2</v>
+      </c>
+      <c r="J19" s="8">
+        <f t="shared" si="0"/>
+        <v>0.16</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="B20" t="s">
+        <v>82</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="D20" t="s">
+        <v>84</v>
+      </c>
+      <c r="E20" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="F20" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="G20" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="H20" s="7">
+        <v>0.41</v>
+      </c>
+      <c r="I20" s="2">
+        <v>1</v>
+      </c>
+      <c r="J20" s="8">
+        <f t="shared" si="0"/>
+        <v>0.41</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="B21" t="s">
+        <v>87</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="D21" t="s">
+        <v>89</v>
+      </c>
+      <c r="E21" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="F21" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="G21" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="H21" s="7">
+        <v>5.94</v>
+      </c>
+      <c r="I21" s="2">
+        <v>1</v>
+      </c>
+      <c r="J21" s="8">
+        <f t="shared" si="0"/>
+        <v>5.94</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="B22" t="s">
+        <v>92</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="D22" t="s">
+        <v>94</v>
+      </c>
+      <c r="E22" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="F22" s="5"/>
+      <c r="G22" s="12" t="s">
+        <v>96</v>
+      </c>
+      <c r="H22" s="7">
+        <v>8</v>
+      </c>
+      <c r="I22" s="2">
+        <v>1</v>
+      </c>
+      <c r="J22" s="8">
+        <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="B23" t="s">
+        <v>97</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="D23" t="s">
+        <v>99</v>
+      </c>
+      <c r="E23" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="F23" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="G23" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="H23" s="7">
+        <v>5.07</v>
+      </c>
+      <c r="I23" s="2">
+        <v>1</v>
+      </c>
+      <c r="J23" s="8">
+        <f t="shared" si="0"/>
+        <v>5.07</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="B24" t="s">
+        <v>102</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="D24" t="s">
+        <v>104</v>
+      </c>
+      <c r="E24" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="F24" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="G24" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="H24" s="7">
+        <v>0.67</v>
+      </c>
+      <c r="I24" s="2">
+        <v>1</v>
+      </c>
+      <c r="J24" s="8">
+        <f t="shared" si="0"/>
+        <v>0.67</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="I26" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="J26" s="13">
+        <f>SUM(J4:J24)</f>
+        <v>36.950000000000003</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A17:A19"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="E4" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="F4" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
+    <hyperlink ref="E5" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
+    <hyperlink ref="F5" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
+    <hyperlink ref="E6" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
+    <hyperlink ref="F6" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
+    <hyperlink ref="E7" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
+    <hyperlink ref="F7" r:id="rId8" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
+    <hyperlink ref="E8" r:id="rId9" xr:uid="{00000000-0004-0000-0000-000008000000}"/>
+    <hyperlink ref="F8" r:id="rId10" xr:uid="{00000000-0004-0000-0000-000009000000}"/>
+    <hyperlink ref="E9" r:id="rId11" xr:uid="{00000000-0004-0000-0000-00000A000000}"/>
+    <hyperlink ref="F9" r:id="rId12" xr:uid="{00000000-0004-0000-0000-00000B000000}"/>
+    <hyperlink ref="E10" r:id="rId13" xr:uid="{00000000-0004-0000-0000-00000C000000}"/>
+    <hyperlink ref="E11" r:id="rId14" xr:uid="{00000000-0004-0000-0000-00000D000000}"/>
+    <hyperlink ref="F11" r:id="rId15" xr:uid="{00000000-0004-0000-0000-00000E000000}"/>
+    <hyperlink ref="E12" r:id="rId16" xr:uid="{00000000-0004-0000-0000-00000F000000}"/>
+    <hyperlink ref="F12" r:id="rId17" xr:uid="{00000000-0004-0000-0000-000010000000}"/>
+    <hyperlink ref="E13" r:id="rId18" xr:uid="{00000000-0004-0000-0000-000011000000}"/>
+    <hyperlink ref="F13" r:id="rId19" xr:uid="{00000000-0004-0000-0000-000012000000}"/>
+    <hyperlink ref="E14" r:id="rId20" display="https://www.mouser.fr/ProductDetail/Wurth-Elektronik/7447060?qs=sGAEpiMZZMv126LJFLh8y7bZMRioh4ww7S2La6H8kL0%3D" xr:uid="{00000000-0004-0000-0000-000013000000}"/>
+    <hyperlink ref="F14" r:id="rId21" xr:uid="{00000000-0004-0000-0000-000014000000}"/>
+    <hyperlink ref="E15" r:id="rId22" xr:uid="{00000000-0004-0000-0000-000015000000}"/>
+    <hyperlink ref="F15" r:id="rId23" xr:uid="{00000000-0004-0000-0000-000016000000}"/>
+    <hyperlink ref="E16" r:id="rId24" xr:uid="{00000000-0004-0000-0000-000017000000}"/>
+    <hyperlink ref="F16" r:id="rId25" xr:uid="{00000000-0004-0000-0000-000018000000}"/>
+    <hyperlink ref="E17" r:id="rId26" xr:uid="{00000000-0004-0000-0000-000019000000}"/>
+    <hyperlink ref="F17" r:id="rId27" xr:uid="{00000000-0004-0000-0000-00001A000000}"/>
+    <hyperlink ref="E18" r:id="rId28" xr:uid="{00000000-0004-0000-0000-00001B000000}"/>
+    <hyperlink ref="F18" r:id="rId29" xr:uid="{00000000-0004-0000-0000-00001C000000}"/>
+    <hyperlink ref="E19" r:id="rId30" xr:uid="{00000000-0004-0000-0000-00001D000000}"/>
+    <hyperlink ref="F19" r:id="rId31" xr:uid="{00000000-0004-0000-0000-00001E000000}"/>
+    <hyperlink ref="E20" r:id="rId32" xr:uid="{00000000-0004-0000-0000-00001F000000}"/>
+    <hyperlink ref="F20" r:id="rId33" xr:uid="{00000000-0004-0000-0000-000020000000}"/>
+    <hyperlink ref="E21" r:id="rId34" xr:uid="{00000000-0004-0000-0000-000021000000}"/>
+    <hyperlink ref="F21" r:id="rId35" xr:uid="{00000000-0004-0000-0000-000022000000}"/>
+    <hyperlink ref="E23" r:id="rId36" xr:uid="{00000000-0004-0000-0000-000023000000}"/>
+    <hyperlink ref="F23" r:id="rId37" xr:uid="{00000000-0004-0000-0000-000024000000}"/>
+    <hyperlink ref="E24" r:id="rId38" xr:uid="{00000000-0004-0000-0000-000025000000}"/>
+    <hyperlink ref="F24" r:id="rId39" xr:uid="{00000000-0004-0000-0000-000026000000}"/>
+  </hyperlinks>
+  <pageMargins left="0.25196850393700787" right="0.25196850393700787" top="0.75196850393700787" bottom="0.75196850393700787" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" scale="98" orientation="landscape" useFirstPageNumber="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <sheetPr>
+    <tabColor theme="9"/>
+  </sheetPr>
+  <dimension ref="A1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData/>
+  <pageMargins left="0.70078740157480324" right="0.70078740157480324" top="0.75196850393700787" bottom="0.75196850393700787" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr>
     <tabColor indexed="2"/>
-    <outlinePr applyStyles="0" summaryBelow="1" summaryRight="1" showOutlineSymbols="1"/>
-    <pageSetUpPr autoPageBreaks="1" fitToPage="0"/>
   </sheetPr>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <dimension ref="B8:U24"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col bestFit="1" min="2" max="2" width="11.7421875"/>
-    <col bestFit="1" min="3" max="3" width="9.18359375"/>
-    <col bestFit="1" min="4" max="4" width="4.140625"/>
-    <col bestFit="1" min="5" max="5" width="7.23046875"/>
-    <col bestFit="1" min="6" max="6" width="3.0625"/>
-    <col bestFit="1" min="8" max="8" width="4.68359375"/>
-    <col bestFit="1" min="9" max="9" width="7.23046875"/>
-    <col bestFit="1" min="10" max="10" width="4.07421875"/>
-    <col bestFit="1" min="11" max="11" width="5.421875"/>
-    <col bestFit="1" min="12" max="12" width="7.97265625"/>
+    <col min="2" max="2" width="11.77734375" bestFit="1"/>
+    <col min="3" max="3" width="9.21875" bestFit="1"/>
+    <col min="4" max="4" width="4.109375" bestFit="1"/>
+    <col min="5" max="5" width="7.21875" bestFit="1"/>
+    <col min="6" max="6" width="3.109375" bestFit="1"/>
+    <col min="8" max="8" width="4.6640625" bestFit="1"/>
+    <col min="9" max="9" width="7.21875" bestFit="1"/>
+    <col min="10" max="10" width="4.109375" bestFit="1"/>
+    <col min="11" max="11" width="5.44140625" bestFit="1"/>
+    <col min="12" max="12" width="8" bestFit="1"/>
   </cols>
   <sheetData>
-    <row r="8" ht="14.25">
-      <c r="C8" s="18" t="s">
+    <row r="8" spans="2:21" x14ac:dyDescent="0.3">
+      <c r="C8" s="14" t="s">
         <v>108</v>
       </c>
-      <c r="D8" s="18" t="s">
+      <c r="D8" s="14" t="s">
         <v>109</v>
       </c>
-      <c r="E8" s="18" t="s">
+      <c r="E8" s="14" t="s">
         <v>110</v>
       </c>
-      <c r="F8" s="18" t="s">
+      <c r="F8" s="14" t="s">
         <v>111</v>
       </c>
-      <c r="G8" s="19" t="s">
+      <c r="G8" s="16" t="s">
         <v>112</v>
       </c>
-      <c r="H8" s="20" t="s">
+      <c r="H8" s="15" t="s">
         <v>113</v>
       </c>
       <c r="U8" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="9" ht="14.25">
-      <c r="C9" s="18" t="s">
+    <row r="9" spans="2:21" x14ac:dyDescent="0.3">
+      <c r="C9" s="14" t="s">
         <v>115</v>
       </c>
-      <c r="D9" s="18" t="s">
+      <c r="D9" s="14" t="s">
         <v>116</v>
       </c>
-      <c r="E9" s="18" t="s">
+      <c r="E9" s="14" t="s">
         <v>117</v>
       </c>
-      <c r="F9" s="18" t="s">
+      <c r="F9" s="14" t="s">
         <v>28</v>
       </c>
-      <c r="G9" s="19"/>
-      <c r="H9" s="20" t="s">
+      <c r="G9" s="16"/>
+      <c r="H9" s="15" t="s">
         <v>118</v>
       </c>
       <c r="U9" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="10" ht="14.25">
-      <c r="C10" s="18" t="s">
+    <row r="10" spans="2:21" x14ac:dyDescent="0.3">
+      <c r="C10" s="14" t="s">
         <v>120</v>
       </c>
-      <c r="D10" s="18" t="s">
+      <c r="D10" s="14" t="s">
         <v>121</v>
       </c>
-      <c r="E10" s="18" t="s">
+      <c r="E10" s="14" t="s">
         <v>122</v>
       </c>
-      <c r="F10" s="18" t="s">
+      <c r="F10" s="14" t="s">
         <v>33</v>
       </c>
-      <c r="G10" s="19"/>
-      <c r="H10" s="20" t="s">
+      <c r="G10" s="16"/>
+      <c r="H10" s="15" t="s">
         <v>123</v>
       </c>
       <c r="U10" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="11" ht="14.25">
-      <c r="C11" s="18" t="s">
+    <row r="11" spans="2:21" x14ac:dyDescent="0.3">
+      <c r="C11" s="14" t="s">
         <v>125</v>
       </c>
-      <c r="D11" s="18" t="s">
+      <c r="D11" s="14" t="s">
         <v>126</v>
       </c>
-      <c r="E11" s="18" t="s">
+      <c r="E11" s="14" t="s">
         <v>127</v>
       </c>
-      <c r="F11" s="18" t="s">
+      <c r="F11" s="14" t="s">
         <v>128</v>
       </c>
-      <c r="G11" s="19"/>
-      <c r="H11" s="20" t="s">
+      <c r="G11" s="16"/>
+      <c r="H11" s="15" t="s">
         <v>129</v>
       </c>
       <c r="I11" t="s">
         <v>130</v>
       </c>
-      <c r="J11" s="20" t="s">
+      <c r="J11" s="15" t="s">
         <v>131</v>
       </c>
       <c r="K11" t="s">
@@ -2206,28 +2741,28 @@
       <c r="L11" t="s">
         <v>133</v>
       </c>
-      <c r="U11" s="14" t="s">
+      <c r="U11" s="11" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="12" ht="14.25">
+    <row r="12" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B12" t="s">
         <v>135</v>
       </c>
-      <c r="C12" s="18" t="s">
+      <c r="C12" s="14" t="s">
         <v>136</v>
       </c>
-      <c r="D12" s="18" t="s">
+      <c r="D12" s="14" t="s">
         <v>137</v>
       </c>
-      <c r="E12" s="18" t="s">
+      <c r="E12" s="14" t="s">
         <v>138</v>
       </c>
-      <c r="F12" s="18" t="s">
+      <c r="F12" s="14" t="s">
         <v>139</v>
       </c>
-      <c r="G12" s="19"/>
-      <c r="H12" s="20" t="s">
+      <c r="G12" s="16"/>
+      <c r="H12" s="15" t="s">
         <v>140</v>
       </c>
       <c r="I12" t="s">
@@ -2243,24 +2778,24 @@
         <v>144</v>
       </c>
     </row>
-    <row r="13" ht="14.25">
+    <row r="13" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B13" t="s">
         <v>145</v>
       </c>
-      <c r="C13" s="18" t="s">
+      <c r="C13" s="14" t="s">
         <v>146</v>
       </c>
-      <c r="D13" s="18" t="s">
+      <c r="D13" s="14" t="s">
         <v>147</v>
       </c>
-      <c r="E13" s="18" t="s">
+      <c r="E13" s="14" t="s">
         <v>148</v>
       </c>
-      <c r="F13" s="18" t="s">
+      <c r="F13" s="14" t="s">
         <v>149</v>
       </c>
-      <c r="G13" s="19"/>
-      <c r="H13" s="20" t="s">
+      <c r="G13" s="16"/>
+      <c r="H13" s="15" t="s">
         <v>150</v>
       </c>
       <c r="I13" t="s">
@@ -2276,19 +2811,19 @@
         <v>154</v>
       </c>
     </row>
-    <row r="14" ht="14.25">
-      <c r="C14" s="18"/>
-      <c r="D14" s="18" t="s">
+    <row r="14" spans="2:21" x14ac:dyDescent="0.3">
+      <c r="C14" s="14"/>
+      <c r="D14" s="14" t="s">
         <v>155</v>
       </c>
-      <c r="E14" s="18" t="s">
+      <c r="E14" s="14" t="s">
         <v>156</v>
       </c>
-      <c r="F14" s="18" t="s">
+      <c r="F14" s="14" t="s">
         <v>157</v>
       </c>
-      <c r="G14" s="19"/>
-      <c r="H14" s="20" t="s">
+      <c r="G14" s="16"/>
+      <c r="H14" s="15" t="s">
         <v>158</v>
       </c>
       <c r="I14" t="s">
@@ -2298,83 +2833,83 @@
         <v>160</v>
       </c>
     </row>
-    <row r="17" ht="14.25">
-      <c r="O17" s="20"/>
-    </row>
-    <row r="18" ht="14.25">
+    <row r="17" spans="2:21" x14ac:dyDescent="0.3">
+      <c r="O17" s="15"/>
+    </row>
+    <row r="18" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B18" t="s">
         <v>161</v>
       </c>
-      <c r="D18" s="18" t="s">
+      <c r="D18" s="14" t="s">
         <v>109</v>
       </c>
       <c r="E18" t="s">
         <v>162</v>
       </c>
-      <c r="F18" s="18" t="s">
+      <c r="F18" s="14" t="s">
         <v>111</v>
       </c>
-      <c r="G18" s="19" t="s">
+      <c r="G18" s="16" t="s">
         <v>163</v>
       </c>
-      <c r="H18" s="20" t="s">
+      <c r="H18" s="15" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="19" ht="14.25">
+    <row r="19" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B19" t="s">
         <v>161</v>
       </c>
-      <c r="D19" s="18" t="s">
+      <c r="D19" s="14" t="s">
         <v>116</v>
       </c>
-      <c r="E19" s="15" t="s">
+      <c r="E19" t="s">
         <v>110</v>
       </c>
-      <c r="F19" s="18" t="s">
+      <c r="F19" s="14" t="s">
         <v>28</v>
       </c>
-      <c r="G19" s="19"/>
-      <c r="H19" s="20" t="s">
+      <c r="G19" s="16"/>
+      <c r="H19" s="15" t="s">
         <v>118</v>
       </c>
-      <c r="U19" s="15" t="s">
+      <c r="U19" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="20" ht="14.25">
+    <row r="20" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B20" t="s">
         <v>165</v>
       </c>
-      <c r="D20" s="18" t="s">
+      <c r="D20" s="14" t="s">
         <v>121</v>
       </c>
-      <c r="E20" s="15" t="s">
+      <c r="E20" t="s">
         <v>117</v>
       </c>
-      <c r="F20" s="18" t="s">
+      <c r="F20" s="14" t="s">
         <v>33</v>
       </c>
-      <c r="G20" s="19"/>
-      <c r="H20" s="20" t="s">
+      <c r="G20" s="16"/>
+      <c r="H20" s="15" t="s">
         <v>123</v>
       </c>
       <c r="U20" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="21" ht="14.25">
+    <row r="21" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B21" t="s">
         <v>167</v>
       </c>
       <c r="E21" t="s">
         <v>168</v>
       </c>
-      <c r="F21" s="18" t="s">
+      <c r="F21" s="14" t="s">
         <v>128</v>
       </c>
-      <c r="G21" s="19"/>
-      <c r="H21" s="20" t="s">
+      <c r="G21" s="16"/>
+      <c r="H21" s="15" t="s">
         <v>129</v>
       </c>
       <c r="I21" t="s">
@@ -2390,21 +2925,21 @@
         <v>171</v>
       </c>
     </row>
-    <row r="22" ht="14.25">
+    <row r="22" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B22" t="s">
         <v>172</v>
       </c>
-      <c r="C22" s="18" t="s">
+      <c r="C22" s="14" t="s">
         <v>136</v>
       </c>
       <c r="E22" t="s">
         <v>173</v>
       </c>
-      <c r="F22" s="18" t="s">
+      <c r="F22" s="14" t="s">
         <v>139</v>
       </c>
-      <c r="G22" s="19"/>
-      <c r="H22" s="20" t="s">
+      <c r="G22" s="16"/>
+      <c r="H22" s="15" t="s">
         <v>140</v>
       </c>
       <c r="I22" t="s">
@@ -2416,25 +2951,25 @@
       <c r="L22" t="s">
         <v>175</v>
       </c>
-      <c r="U22" s="14" t="s">
+      <c r="U22" s="11" t="s">
         <v>176</v>
       </c>
     </row>
-    <row r="23" ht="14.25">
+    <row r="23" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B23" t="s">
         <v>177</v>
       </c>
-      <c r="C23" s="18" t="s">
+      <c r="C23" s="14" t="s">
         <v>146</v>
       </c>
-      <c r="E23" s="15" t="s">
+      <c r="E23" t="s">
         <v>178</v>
       </c>
-      <c r="F23" s="18" t="s">
+      <c r="F23" s="14" t="s">
         <v>149</v>
       </c>
-      <c r="G23" s="19"/>
-      <c r="H23" s="20" t="s">
+      <c r="G23" s="16"/>
+      <c r="H23" s="15" t="s">
         <v>150</v>
       </c>
       <c r="I23" t="s">
@@ -2447,18 +2982,18 @@
         <v>180</v>
       </c>
     </row>
-    <row r="24" ht="14.25">
+    <row r="24" spans="2:21" x14ac:dyDescent="0.3">
       <c r="D24" t="s">
         <v>155</v>
       </c>
       <c r="E24" t="s">
         <v>181</v>
       </c>
-      <c r="F24" s="18" t="s">
+      <c r="F24" s="14" t="s">
         <v>157</v>
       </c>
-      <c r="G24" s="19"/>
-      <c r="H24" s="20" t="s">
+      <c r="G24" s="16"/>
+      <c r="H24" s="15" t="s">
         <v>158</v>
       </c>
       <c r="I24" t="s">
@@ -2474,13 +3009,11 @@
     <mergeCell ref="G18:G24"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink r:id="rId1" ref="U11"/>
-    <hyperlink r:id="rId2" ref="U22"/>
+    <hyperlink ref="U11" r:id="rId1" xr:uid="{00000000-0004-0000-0200-000000000000}"/>
+    <hyperlink ref="U22" r:id="rId2" xr:uid="{00000000-0004-0000-0200-000001000000}"/>
   </hyperlinks>
-  <printOptions headings="0" gridLines="0"/>
-  <pageMargins left="0.70078740157480324" right="0.70078740157480324" top="0.75196850393700787" bottom="0.75196850393700787" header="0.29999999999999999" footer="0.29999999999999999"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
-  <headerFooter/>
+  <pageMargins left="0.70078740157480324" right="0.70078740157480324" top="0.75196850393700787" bottom="0.75196850393700787" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
   <drawing r:id="rId3"/>
 </worksheet>
 </file>